--- a/docs/DIGITAL_CIRCUS_COMBAT_TRACKER.xlsx
+++ b/docs/DIGITAL_CIRCUS_COMBAT_TRACKER.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" r:id="R4d49f830b974480a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fonctionnalités" sheetId="2" r:id="R152e0a304f6b4914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combattants" sheetId="3" r:id="Re6bc0aa82e2c475a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Techniques" sheetId="4" r:id="Rd2fbd9791054496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arènes" sheetId="5" r:id="Reb1a1f9b0653426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlas" sheetId="6" r:id="Raea658a74bb347a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="7" r:id="Rc96e785ccfa7412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scénarios" sheetId="8" r:id="R367dcc59504047e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="9" r:id="R614b7af91d2541bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Références" sheetId="10" r:id="R431a99def44e46b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synthèse" sheetId="1" r:id="R967197f400f0436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fonctionnalités" sheetId="2" r:id="Rf1eef64afcf44501"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Combattants" sheetId="3" r:id="R8bd286d5fdbf417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Techniques" sheetId="4" r:id="R7ff3c4cfdcb44a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arènes" sheetId="5" r:id="Rb586eb74edeb400c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Atlas" sheetId="6" r:id="R0d2fcd3ec8674b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production" sheetId="7" r:id="Rb51e197e8e0540fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scénarios" sheetId="8" r:id="R88e1ba82f2b54b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="9" r:id="R314f6bbcd6d14402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Références" sheetId="10" r:id="Ra297524a9ca64a23"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1294,8 +1294,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EncoreFonctionnalites" displayName="EncoreFonctionnalites" ref="A5:I91" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:I91"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EncoreFonctionnalites" displayName="EncoreFonctionnalites" ref="A5:I93" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:I93"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Domaine"/>
@@ -1461,8 +1461,8 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="EncoreQA" displayName="EncoreQA" ref="A5:I198" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A5:I198"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="EncoreQA" displayName="EncoreQA" ref="A5:I227" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A5:I227"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="ID"/>
     <x:tableColumn id="2" name="Domaine"/>
@@ -1912,7 +1912,7 @@
       <x:c r="F13" s="2"/>
       <x:c r="G13" s="2"/>
       <x:c r="H13" s="2" t="str">
-        <x:v>122 tests Node dans 6 suites exécutées</x:v>
+        <x:v>141 tests Node dans 7 suites exécutées</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="31" customHeight="1">
@@ -1936,7 +1936,7 @@
       </x:c>
       <x:c r="G14" s="2"/>
       <x:c r="H14" s="2" t="str">
-        <x:v>40 contrôles navigateur réussis</x:v>
+        <x:v>48 contrôles navigateur réussis</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
@@ -1944,24 +1944,24 @@
         <x:v>Fonctionnalités</x:v>
       </x:c>
       <x:c r="B15" s="32" t="n">
-        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$91,B$14)</x:f>
-        <x:v>63</x:v>
+        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$93,B$14)</x:f>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C15" s="32" t="n">
-        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$91,C$14)</x:f>
+        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$93,C$14)</x:f>
         <x:v>6</x:v>
       </x:c>
       <x:c r="D15" s="32" t="n">
-        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$91,D$14)</x:f>
+        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$93,D$14)</x:f>
         <x:v>14</x:v>
       </x:c>
       <x:c r="E15" s="32" t="n">
-        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$91,E$14)</x:f>
+        <x:f>COUNTIFS('Fonctionnalités'!D$6:D$93,E$14)</x:f>
         <x:v>3</x:v>
       </x:c>
       <x:c r="F15" s="32" t="n">
-        <x:f>COUNTA('Fonctionnalités'!A6:A91)</x:f>
-        <x:v>86</x:v>
+        <x:f>COUNTA('Fonctionnalités'!A6:A93)</x:f>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G15" s="2"/>
       <x:c r="H15" s="2" t="str">
@@ -2109,24 +2109,24 @@
         <x:v>Cas documentés</x:v>
       </x:c>
       <x:c r="B22" s="33" t="n">
-        <x:f>COUNTIFS('QA'!D6:D198,B21)</x:f>
-        <x:v>179</x:v>
+        <x:f>COUNTIFS('QA'!D6:D227,B21)</x:f>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C22" s="33" t="n">
-        <x:f>COUNTIFS('QA'!D6:D198,C21)</x:f>
+        <x:f>COUNTIFS('QA'!D6:D227,C21)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D22" s="33" t="n">
-        <x:f>COUNTIFS('QA'!D6:D198,D21)</x:f>
+        <x:f>COUNTIFS('QA'!D6:D227,D21)</x:f>
         <x:v>5</x:v>
       </x:c>
       <x:c r="E22" s="33" t="n">
-        <x:f>COUNTIFS('QA'!D6:D198,E21)</x:f>
+        <x:f>COUNTIFS('QA'!D6:D227,E21)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="F22" s="33" t="n">
-        <x:f>COUNTA('QA'!A6:A198)</x:f>
-        <x:v>193</x:v>
+        <x:f>COUNTA('QA'!A6:A227)</x:f>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="G22" s="2"/>
       <x:c r="H22" s="2" t="str">
@@ -2666,7 +2666,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37a49a9540f54ca2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a6ee4416b8c40ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3040,15 +3040,15 @@
       </x:c>
       <x:c r="I16" s="20" t="str"/>
     </x:row>
-    <x:row r="17" ht="29" customHeight="1">
+    <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="19" t="str">
-        <x:v>CQC-01</x:v>
+        <x:v>INT-12</x:v>
       </x:c>
       <x:c r="B17" s="19" t="str">
-        <x:v>Moteur</x:v>
+        <x:v>Intégration</x:v>
       </x:c>
       <x:c r="C17" s="19" t="str">
-        <x:v>Port du moteur CQC réel</x:v>
+        <x:v>Reprise après échec de première installation</x:v>
       </x:c>
       <x:c r="D17" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3057,23 +3057,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F17" s="19" t="str">
-        <x:v>combat/engine.mjs</x:v>
+        <x:v>combat/offline.mjs / combat/app.mjs</x:v>
       </x:c>
       <x:c r="G17" s="19" t="str">
-        <x:v>La provenance identifie le commit et les modules copiés.</x:v>
-      </x:c>
-      <x:c r="H17" s="19" t="str"/>
+        <x:v>Afficher un échec explicite si la première installation du service worker échoue, libérer les attentes et permettre une nouvelle tentative depuis les réglages.</x:v>
+      </x:c>
+      <x:c r="H17" s="19" t="str">
+        <x:v>Le jeu en ligne reste accessible. La réussite hors ligne exige une installation et une préparation effectivement terminées.</x:v>
+      </x:c>
       <x:c r="I17" s="20" t="str"/>
     </x:row>
     <x:row r="18" ht="29" customHeight="1">
       <x:c r="A18" s="18" t="str">
-        <x:v>CQC-02</x:v>
+        <x:v>CQC-01</x:v>
       </x:c>
       <x:c r="B18" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C18" s="18" t="str">
-        <x:v>Simulation à pas fixe 60 Hz</x:v>
+        <x:v>Port du moteur CQC réel</x:v>
       </x:c>
       <x:c r="D18" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3085,20 +3087,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
-        <x:v>Résultats identiques à 30, 60 et 120 Hz de rendu.</x:v>
+        <x:v>La provenance identifie le commit et les modules copiés.</x:v>
       </x:c>
       <x:c r="H18" s="18" t="str"/>
       <x:c r="I18" s="20" t="str"/>
     </x:row>
     <x:row r="19" ht="29" customHeight="1">
       <x:c r="A19" s="19" t="str">
-        <x:v>CQC-03</x:v>
+        <x:v>CQC-02</x:v>
       </x:c>
       <x:c r="B19" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C19" s="19" t="str">
-        <x:v>Dix emplacements de techniques</x:v>
+        <x:v>Simulation à pas fixe 60 Hz</x:v>
       </x:c>
       <x:c r="D19" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3107,23 +3109,23 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F19" s="19" t="str">
-        <x:v>combat/data.mjs</x:v>
+        <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G19" s="19" t="str">
-        <x:v>Chaque combattant possède les dix actions CQC.</x:v>
+        <x:v>Résultats identiques à 30, 60 et 120 Hz de rendu.</x:v>
       </x:c>
       <x:c r="H19" s="19" t="str"/>
       <x:c r="I19" s="20" t="str"/>
     </x:row>
     <x:row r="20" ht="29" customHeight="1">
       <x:c r="A20" s="18" t="str">
-        <x:v>CQC-04</x:v>
+        <x:v>CQC-03</x:v>
       </x:c>
       <x:c r="B20" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C20" s="18" t="str">
-        <x:v>Démarrage, actif, récupération</x:v>
+        <x:v>Dix emplacements de techniques</x:v>
       </x:c>
       <x:c r="D20" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3132,23 +3134,23 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F20" s="18" t="str">
-        <x:v>combat/engine.mjs</x:v>
+        <x:v>combat/data.mjs</x:v>
       </x:c>
       <x:c r="G20" s="18" t="str">
-        <x:v>Le contact ne cause des dégâts que pendant les frames actives.</x:v>
+        <x:v>Chaque combattant possède les dix actions CQC.</x:v>
       </x:c>
       <x:c r="H20" s="18" t="str"/>
       <x:c r="I20" s="20" t="str"/>
     </x:row>
     <x:row r="21" ht="29" customHeight="1">
       <x:c r="A21" s="19" t="str">
-        <x:v>CQC-05</x:v>
+        <x:v>CQC-04</x:v>
       </x:c>
       <x:c r="B21" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C21" s="19" t="str">
-        <x:v>Hitboxes et hurtboxes distinctes</x:v>
+        <x:v>Démarrage, actif, récupération</x:v>
       </x:c>
       <x:c r="D21" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3160,20 +3162,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G21" s="19" t="str">
-        <x:v>La collision dépend du corps et du mouvement.</x:v>
+        <x:v>Le contact ne cause des dégâts que pendant les frames actives.</x:v>
       </x:c>
       <x:c r="H21" s="19" t="str"/>
       <x:c r="I21" s="20" t="str"/>
     </x:row>
     <x:row r="22" ht="29" customHeight="1">
       <x:c r="A22" s="18" t="str">
-        <x:v>CQC-06</x:v>
+        <x:v>CQC-05</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C22" s="18" t="str">
-        <x:v>Garde haute et basse</x:v>
+        <x:v>Hitboxes et hurtboxes distinctes</x:v>
       </x:c>
       <x:c r="D22" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3185,20 +3187,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
-        <x:v>La garde haute laisse passer les coups bas.</x:v>
+        <x:v>La collision dépend du corps et du mouvement.</x:v>
       </x:c>
       <x:c r="H22" s="18" t="str"/>
       <x:c r="I22" s="20" t="str"/>
     </x:row>
     <x:row r="23" ht="29" customHeight="1">
       <x:c r="A23" s="19" t="str">
-        <x:v>CQC-07</x:v>
+        <x:v>CQC-06</x:v>
       </x:c>
       <x:c r="B23" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C23" s="19" t="str">
-        <x:v>Brisure de garde</x:v>
+        <x:v>Garde haute et basse</x:v>
       </x:c>
       <x:c r="D23" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3210,20 +3212,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G23" s="19" t="str">
-        <x:v>Une garde épuisée ouvre une fenêtre de punition.</x:v>
+        <x:v>La garde haute laisse passer les coups bas.</x:v>
       </x:c>
       <x:c r="H23" s="19" t="str"/>
       <x:c r="I23" s="20" t="str"/>
     </x:row>
     <x:row r="24" ht="29" customHeight="1">
       <x:c r="A24" s="18" t="str">
-        <x:v>CQC-08</x:v>
+        <x:v>CQC-07</x:v>
       </x:c>
       <x:c r="B24" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C24" s="18" t="str">
-        <x:v>Saisies et déchopes</x:v>
+        <x:v>Brisure de garde</x:v>
       </x:c>
       <x:c r="D24" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3235,20 +3237,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
-        <x:v>La garde ne bloque pas une saisie. Une déchope juste annule la prise.</x:v>
+        <x:v>Une garde épuisée ouvre une fenêtre de punition.</x:v>
       </x:c>
       <x:c r="H24" s="18" t="str"/>
       <x:c r="I24" s="20" t="str"/>
     </x:row>
     <x:row r="25" ht="29" customHeight="1">
       <x:c r="A25" s="19" t="str">
-        <x:v>CQC-09</x:v>
+        <x:v>CQC-08</x:v>
       </x:c>
       <x:c r="B25" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C25" s="19" t="str">
-        <x:v>Parades et réflexion</x:v>
+        <x:v>Saisies et déchopes</x:v>
       </x:c>
       <x:c r="D25" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3260,20 +3262,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G25" s="19" t="str">
-        <x:v>Une parade activée annule la bonne catégorie d’attaque.</x:v>
+        <x:v>La garde ne bloque pas une saisie. Une déchope juste annule la prise.</x:v>
       </x:c>
       <x:c r="H25" s="19" t="str"/>
       <x:c r="I25" s="20" t="str"/>
     </x:row>
     <x:row r="26" ht="29" customHeight="1">
       <x:c r="A26" s="18" t="str">
-        <x:v>CQC-10</x:v>
+        <x:v>CQC-09</x:v>
       </x:c>
       <x:c r="B26" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C26" s="18" t="str">
-        <x:v>Projectiles à portée limitée</x:v>
+        <x:v>Parades et réflexion</x:v>
       </x:c>
       <x:c r="D26" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3285,70 +3287,70 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
-        <x:v>La distance parcourue reste bornée, même après réflexion.</x:v>
+        <x:v>Une parade activée annule la bonne catégorie d’attaque.</x:v>
       </x:c>
       <x:c r="H26" s="18" t="str"/>
       <x:c r="I26" s="20" t="str"/>
     </x:row>
     <x:row r="27" ht="29" customHeight="1">
       <x:c r="A27" s="19" t="str">
-        <x:v>CQC-11</x:v>
+        <x:v>CQC-10</x:v>
       </x:c>
       <x:c r="B27" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C27" s="19" t="str">
-        <x:v>Pièges temporaires</x:v>
+        <x:v>Projectiles à portée limitée</x:v>
       </x:c>
       <x:c r="D27" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E27" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F27" s="19" t="str">
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G27" s="19" t="str">
-        <x:v>Armement, limite de poses, durée et collision sont effectifs.</x:v>
+        <x:v>La distance parcourue reste bornée, même après réflexion.</x:v>
       </x:c>
       <x:c r="H27" s="19" t="str"/>
       <x:c r="I27" s="20" t="str"/>
     </x:row>
     <x:row r="28" ht="29" customHeight="1">
       <x:c r="A28" s="18" t="str">
-        <x:v>CQC-12</x:v>
+        <x:v>CQC-11</x:v>
       </x:c>
       <x:c r="B28" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C28" s="18" t="str">
-        <x:v>Ressource et jauge de finale</x:v>
+        <x:v>Pièges temporaires</x:v>
       </x:c>
       <x:c r="D28" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E28" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
-        <x:v>Un coût insuffisant refuse l’action sans dépense supplémentaire.</x:v>
+        <x:v>Armement, limite de poses, durée et collision sont effectifs.</x:v>
       </x:c>
       <x:c r="H28" s="18" t="str"/>
       <x:c r="I28" s="20" t="str"/>
     </x:row>
     <x:row r="29" ht="29" customHeight="1">
       <x:c r="A29" s="19" t="str">
-        <x:v>CQC-13</x:v>
+        <x:v>CQC-12</x:v>
       </x:c>
       <x:c r="B29" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C29" s="19" t="str">
-        <x:v>Combos et annulations confirmées</x:v>
+        <x:v>Ressource et jauge de finale</x:v>
       </x:c>
       <x:c r="D29" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3360,70 +3362,70 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G29" s="19" t="str">
-        <x:v>Une annulation exige un impact et un lien autorisé.</x:v>
+        <x:v>Un coût insuffisant refuse l’action sans dépense supplémentaire.</x:v>
       </x:c>
       <x:c r="H29" s="19" t="str"/>
       <x:c r="I29" s="20" t="str"/>
     </x:row>
     <x:row r="30" ht="29" customHeight="1">
       <x:c r="A30" s="18" t="str">
-        <x:v>CQC-14</x:v>
+        <x:v>CQC-13</x:v>
       </x:c>
       <x:c r="B30" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C30" s="18" t="str">
-        <x:v>Protection contre les boucles</x:v>
+        <x:v>Combos et annulations confirmées</x:v>
       </x:c>
       <x:c r="D30" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E30" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
-        <x:v>Dégradation des combos et protections post-saisie empêchent les verrouillages simples.</x:v>
+        <x:v>Une annulation exige un impact et un lien autorisé.</x:v>
       </x:c>
       <x:c r="H30" s="18" t="str"/>
       <x:c r="I30" s="20" t="str"/>
     </x:row>
     <x:row r="31" ht="29" customHeight="1">
       <x:c r="A31" s="19" t="str">
-        <x:v>CQC-15</x:v>
+        <x:v>CQC-14</x:v>
       </x:c>
       <x:c r="B31" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C31" s="19" t="str">
-        <x:v>Sauts, accroupissement, dash</x:v>
+        <x:v>Protection contre les boucles</x:v>
       </x:c>
       <x:c r="D31" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E31" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F31" s="19" t="str">
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G31" s="19" t="str">
-        <x:v>Les changements de hauteur et de direction sont utilisables.</x:v>
+        <x:v>Dégradation des combos et protections post-saisie empêchent les verrouillages simples.</x:v>
       </x:c>
       <x:c r="H31" s="19" t="str"/>
       <x:c r="I31" s="20" t="str"/>
     </x:row>
     <x:row r="32" ht="29" customHeight="1">
       <x:c r="A32" s="18" t="str">
-        <x:v>CQC-16</x:v>
+        <x:v>CQC-15</x:v>
       </x:c>
       <x:c r="B32" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C32" s="18" t="str">
-        <x:v>Rounds et victoire de match</x:v>
+        <x:v>Sauts, accroupissement, dash</x:v>
       </x:c>
       <x:c r="D32" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3435,20 +3437,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G32" s="18" t="str">
-        <x:v>Le nombre de manches choisies détermine la victoire.</x:v>
+        <x:v>Les changements de hauteur et de direction sont utilisables.</x:v>
       </x:c>
       <x:c r="H32" s="18" t="str"/>
       <x:c r="I32" s="20" t="str"/>
     </x:row>
     <x:row r="33" ht="29" customHeight="1">
       <x:c r="A33" s="19" t="str">
-        <x:v>CQC-17</x:v>
+        <x:v>CQC-16</x:v>
       </x:c>
       <x:c r="B33" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C33" s="19" t="str">
-        <x:v>Égalité et double KO</x:v>
+        <x:v>Rounds et victoire de match</x:v>
       </x:c>
       <x:c r="D33" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3460,20 +3462,20 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G33" s="19" t="str">
-        <x:v>Une égalité n’accorde pas arbitrairement la victoire au joueur 1.</x:v>
+        <x:v>Le nombre de manches choisies détermine la victoire.</x:v>
       </x:c>
       <x:c r="H33" s="19" t="str"/>
       <x:c r="I33" s="20" t="str"/>
     </x:row>
     <x:row r="34" ht="29" customHeight="1">
       <x:c r="A34" s="18" t="str">
-        <x:v>CQC-18</x:v>
+        <x:v>CQC-17</x:v>
       </x:c>
       <x:c r="B34" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C34" s="18" t="str">
-        <x:v>IA déterministe</x:v>
+        <x:v>Égalité et double KO</x:v>
       </x:c>
       <x:c r="D34" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3485,93 +3487,95 @@
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
-        <x:v>Une graine et les mêmes entrées reproduisent la simulation.</x:v>
+        <x:v>Une égalité n’accorde pas arbitrairement la victoire au joueur 1.</x:v>
       </x:c>
       <x:c r="H34" s="18" t="str"/>
       <x:c r="I34" s="20" t="str"/>
     </x:row>
     <x:row r="35" ht="29" customHeight="1">
       <x:c r="A35" s="19" t="str">
-        <x:v>CQC-19</x:v>
+        <x:v>CQC-18</x:v>
       </x:c>
       <x:c r="B35" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C35" s="19" t="str">
-        <x:v>Difficultés CPU</x:v>
+        <x:v>IA déterministe</x:v>
       </x:c>
       <x:c r="D35" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E35" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F35" s="19" t="str">
         <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G35" s="19" t="str">
-        <x:v>Trois réglages exposés et comportement effectif.</x:v>
+        <x:v>Une graine et les mêmes entrées reproduisent la simulation.</x:v>
       </x:c>
       <x:c r="H35" s="19" t="str"/>
       <x:c r="I35" s="20" t="str"/>
     </x:row>
     <x:row r="36" ht="29" customHeight="1">
       <x:c r="A36" s="18" t="str">
-        <x:v>CQC-20</x:v>
+        <x:v>CQC-19</x:v>
       </x:c>
       <x:c r="B36" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C36" s="18" t="str">
-        <x:v>Équilibrage compétitif complet</x:v>
+        <x:v>Difficultés CPU</x:v>
       </x:c>
       <x:c r="D36" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E36" s="18" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="F36" s="18" t="str"/>
+      <x:c r="F36" s="18" t="str">
+        <x:v>combat/engine.mjs</x:v>
+      </x:c>
       <x:c r="G36" s="18" t="str">
-        <x:v>Mesurer les matchs de chaque paire et corriger les avantages excessifs.</x:v>
-      </x:c>
-      <x:c r="H36" s="18" t="str">
-        <x:v>Les statistiques livrées sont un premier réglage.</x:v>
-      </x:c>
+        <x:v>Trois réglages exposés et comportement effectif.</x:v>
+      </x:c>
+      <x:c r="H36" s="18" t="str"/>
       <x:c r="I36" s="20" t="str"/>
     </x:row>
     <x:row r="37" ht="29" customHeight="1">
       <x:c r="A37" s="19" t="str">
-        <x:v>CQC-21</x:v>
+        <x:v>CQC-20</x:v>
       </x:c>
       <x:c r="B37" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C37" s="19" t="str">
-        <x:v>Réseau et rollback</x:v>
+        <x:v>Équilibrage compétitif complet</x:v>
       </x:c>
       <x:c r="D37" s="19" t="str">
         <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E37" s="19" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F37" s="19" t="str"/>
       <x:c r="G37" s="19" t="str">
-        <x:v>Synchronisation, latence et désynchronisations testées sur plusieurs machines.</x:v>
-      </x:c>
-      <x:c r="H37" s="19" t="str"/>
+        <x:v>Mesurer les matchs de chaque paire et corriger les avantages excessifs.</x:v>
+      </x:c>
+      <x:c r="H37" s="19" t="str">
+        <x:v>Les statistiques livrées sont un premier réglage.</x:v>
+      </x:c>
       <x:c r="I37" s="20" t="str"/>
     </x:row>
     <x:row r="38" ht="29" customHeight="1">
       <x:c r="A38" s="18" t="str">
-        <x:v>CQC-22</x:v>
+        <x:v>CQC-21</x:v>
       </x:c>
       <x:c r="B38" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C38" s="18" t="str">
-        <x:v>Tag team et assists</x:v>
+        <x:v>Réseau et rollback</x:v>
       </x:c>
       <x:c r="D38" s="18" t="str">
         <x:v>Prévu</x:v>
@@ -3581,97 +3585,95 @@
       </x:c>
       <x:c r="F38" s="18" t="str"/>
       <x:c r="G38" s="18" t="str">
-        <x:v>Gestion de remplaçants, entrées et jauges d’assistance.</x:v>
+        <x:v>Synchronisation, latence et désynchronisations testées sur plusieurs machines.</x:v>
       </x:c>
       <x:c r="H38" s="18" t="str"/>
       <x:c r="I38" s="20" t="str"/>
     </x:row>
-    <x:row r="39" ht="32" customHeight="1">
+    <x:row r="39" ht="29" customHeight="1">
       <x:c r="A39" s="19" t="str">
-        <x:v>CQC-23</x:v>
+        <x:v>CQC-22</x:v>
       </x:c>
       <x:c r="B39" s="19" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C39" s="19" t="str">
-        <x:v>Tournoi à tableau</x:v>
+        <x:v>Tag team et assists</x:v>
       </x:c>
       <x:c r="D39" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E39" s="19" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="F39" s="19" t="str">
-        <x:v>combat/progression.mjs / combat/app.mjs</x:v>
-      </x:c>
+      <x:c r="F39" s="19" t="str"/>
       <x:c r="G39" s="19" t="str">
-        <x:v>Huit participants distincts, sept rencontres de tableau et trois victoires joueur pour gagner. Graine et résultats reconstruisent le tournoi à la reprise.</x:v>
-      </x:c>
-      <x:c r="H39" s="19" t="str">
-        <x:v>Les rencontres sans le joueur sont simulées et affichées comme telles. Une défaite élimine le joueur.</x:v>
-      </x:c>
+        <x:v>Gestion de remplaçants, entrées et jauges d’assistance.</x:v>
+      </x:c>
+      <x:c r="H39" s="19" t="str"/>
       <x:c r="I39" s="20" t="str"/>
     </x:row>
-    <x:row r="40" ht="29" customHeight="1">
+    <x:row r="40" ht="32" customHeight="1">
       <x:c r="A40" s="18" t="str">
-        <x:v>CQC-24</x:v>
+        <x:v>CQC-23</x:v>
       </x:c>
       <x:c r="B40" s="18" t="str">
         <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C40" s="18" t="str">
-        <x:v>Finishers cinématiques propres</x:v>
+        <x:v>Tournoi à tableau</x:v>
       </x:c>
       <x:c r="D40" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E40" s="18" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="F40" s="18" t="str"/>
+      <x:c r="F40" s="18" t="str">
+        <x:v>combat/progression.mjs / combat/app.mjs</x:v>
+      </x:c>
       <x:c r="G40" s="18" t="str">
-        <x:v>Trois à cinq finales visuelles distinctes par personnage.</x:v>
+        <x:v>Huit participants distincts, sept rencontres de tableau et trois victoires joueur pour gagner. Graine et résultats reconstruisent le tournoi à la reprise.</x:v>
       </x:c>
       <x:c r="H40" s="18" t="str">
-        <x:v>La technique super actuelle est jouable, les cinématiques dédiées restent à produire.</x:v>
+        <x:v>Les rencontres sans le joueur sont simulées et affichées comme telles. Une défaite élimine le joueur.</x:v>
       </x:c>
       <x:c r="I40" s="20" t="str"/>
     </x:row>
     <x:row r="41" ht="29" customHeight="1">
       <x:c r="A41" s="19" t="str">
-        <x:v>MOD-01</x:v>
+        <x:v>CQC-24</x:v>
       </x:c>
       <x:c r="B41" s="19" t="str">
-        <x:v>Modes</x:v>
+        <x:v>Moteur</x:v>
       </x:c>
       <x:c r="C41" s="19" t="str">
-        <x:v>Versus libre contre CPU</x:v>
+        <x:v>Finishers cinématiques propres</x:v>
       </x:c>
       <x:c r="D41" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E41" s="19" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="F41" s="19" t="str">
-        <x:v>combat/app.mjs</x:v>
-      </x:c>
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F41" s="19" t="str"/>
       <x:c r="G41" s="19" t="str">
-        <x:v>Choisir deux personnages et une arène sans objectif imposé.</x:v>
-      </x:c>
-      <x:c r="H41" s="19" t="str"/>
+        <x:v>Trois à cinq finales visuelles distinctes par personnage.</x:v>
+      </x:c>
+      <x:c r="H41" s="19" t="str">
+        <x:v>La technique super actuelle est jouable, les cinématiques dédiées restent à produire.</x:v>
+      </x:c>
       <x:c r="I41" s="20" t="str"/>
     </x:row>
     <x:row r="42" ht="29" customHeight="1">
       <x:c r="A42" s="18" t="str">
-        <x:v>MOD-02</x:v>
+        <x:v>MOD-01</x:v>
       </x:c>
       <x:c r="B42" s="18" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C42" s="18" t="str">
-        <x:v>Duel local à deux</x:v>
+        <x:v>Versus libre contre CPU</x:v>
       </x:c>
       <x:c r="D42" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3680,23 +3682,23 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F42" s="18" t="str">
-        <x:v>combat/input.mjs</x:v>
+        <x:v>combat/app.mjs</x:v>
       </x:c>
       <x:c r="G42" s="18" t="str">
-        <x:v>Deux jeux d’entrées indépendants contrôlent les deux combattants.</x:v>
+        <x:v>Choisir deux personnages et une arène sans objectif imposé.</x:v>
       </x:c>
       <x:c r="H42" s="18" t="str"/>
       <x:c r="I42" s="20" t="str"/>
     </x:row>
     <x:row r="43" ht="29" customHeight="1">
       <x:c r="A43" s="19" t="str">
-        <x:v>MOD-03</x:v>
+        <x:v>MOD-02</x:v>
       </x:c>
       <x:c r="B43" s="19" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C43" s="19" t="str">
-        <x:v>Arcade en six matchs</x:v>
+        <x:v>Duel local à deux</x:v>
       </x:c>
       <x:c r="D43" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3705,48 +3707,48 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F43" s="19" t="str">
-        <x:v>combat/session.mjs</x:v>
+        <x:v>combat/input.mjs</x:v>
       </x:c>
       <x:c r="G43" s="19" t="str">
-        <x:v>Le résultat mène au match suivant jusqu’à Caine.</x:v>
+        <x:v>Deux jeux d’entrées indépendants contrôlent les deux combattants.</x:v>
       </x:c>
       <x:c r="H43" s="19" t="str"/>
       <x:c r="I43" s="20" t="str"/>
     </x:row>
     <x:row r="44" ht="29" customHeight="1">
       <x:c r="A44" s="18" t="str">
-        <x:v>MOD-04</x:v>
+        <x:v>MOD-03</x:v>
       </x:c>
       <x:c r="B44" s="18" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C44" s="18" t="str">
-        <x:v>Boss rush</x:v>
+        <x:v>Arcade en six matchs</x:v>
       </x:c>
       <x:c r="D44" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E44" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F44" s="18" t="str">
         <x:v>combat/session.mjs</x:v>
       </x:c>
       <x:c r="G44" s="18" t="str">
-        <x:v>Enchaîner la reine, The Fudge, l’abstraction et Caine.</x:v>
+        <x:v>Le résultat mène au match suivant jusqu’à Caine.</x:v>
       </x:c>
       <x:c r="H44" s="18" t="str"/>
       <x:c r="I44" s="20" t="str"/>
     </x:row>
-    <x:row r="45" ht="32" customHeight="1">
+    <x:row r="45" ht="29" customHeight="1">
       <x:c r="A45" s="19" t="str">
-        <x:v>MOD-05</x:v>
+        <x:v>MOD-04</x:v>
       </x:c>
       <x:c r="B45" s="19" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C45" s="19" t="str">
-        <x:v>Survie en dix vagues</x:v>
+        <x:v>Boss rush</x:v>
       </x:c>
       <x:c r="D45" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3755,171 +3757,171 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F45" s="19" t="str">
-        <x:v>combat/app.mjs / combat/session.mjs</x:v>
+        <x:v>combat/session.mjs</x:v>
       </x:c>
       <x:c r="G45" s="19" t="str">
-        <x:v>La vie restante est reportée avec une récupération de 1 200 PV après victoire, plafonnée à 10 000.</x:v>
+        <x:v>Enchaîner la reine, The Fudge, l’abstraction et Caine.</x:v>
       </x:c>
       <x:c r="H45" s="19" t="str"/>
       <x:c r="I45" s="20" t="str"/>
     </x:row>
-    <x:row r="46" ht="29" customHeight="1">
+    <x:row r="46" ht="32" customHeight="1">
       <x:c r="A46" s="18" t="str">
-        <x:v>MOD-06</x:v>
+        <x:v>MOD-05</x:v>
       </x:c>
       <x:c r="B46" s="18" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C46" s="18" t="str">
-        <x:v>Entraînement configurable</x:v>
+        <x:v>Survie en dix vagues</x:v>
       </x:c>
       <x:c r="D46" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E46" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F46" s="18" t="str">
-        <x:v>combat/app.mjs</x:v>
+        <x:v>combat/app.mjs / combat/session.mjs</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
-        <x:v>Tester les actions contre un dummy avec remise à zéro.</x:v>
+        <x:v>La vie restante est reportée avec une récupération de 1 200 PV après victoire, plafonnée à 10 000.</x:v>
       </x:c>
       <x:c r="H46" s="18" t="str"/>
       <x:c r="I46" s="20" t="str"/>
     </x:row>
     <x:row r="47" ht="29" customHeight="1">
       <x:c r="A47" s="19" t="str">
-        <x:v>MOD-07</x:v>
+        <x:v>MOD-06</x:v>
       </x:c>
       <x:c r="B47" s="19" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C47" s="19" t="str">
-        <x:v>Six défis mesurables</x:v>
+        <x:v>Entraînement configurable</x:v>
       </x:c>
       <x:c r="D47" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E47" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F47" s="19" t="str">
-        <x:v>combat/session.mjs</x:v>
+        <x:v>combat/app.mjs</x:v>
       </x:c>
       <x:c r="G47" s="19" t="str">
-        <x:v>Chaque défi possède un objectif et un résultat.</x:v>
+        <x:v>Tester les actions contre un dummy avec remise à zéro.</x:v>
       </x:c>
       <x:c r="H47" s="19" t="str"/>
       <x:c r="I47" s="20" t="str"/>
     </x:row>
     <x:row r="48" ht="29" customHeight="1">
       <x:c r="A48" s="18" t="str">
-        <x:v>MOD-08</x:v>
+        <x:v>MOD-07</x:v>
       </x:c>
       <x:c r="B48" s="18" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C48" s="18" t="str">
-        <x:v>Campagne scénarisée par épisode</x:v>
+        <x:v>Six défis mesurables</x:v>
       </x:c>
       <x:c r="D48" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E48" s="18" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="F48" s="18" t="str"/>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F48" s="18" t="str">
+        <x:v>combat/session.mjs</x:v>
+      </x:c>
       <x:c r="G48" s="18" t="str">
-        <x:v>Routes, dialogues, combats et événements propres à chaque épisode.</x:v>
+        <x:v>Chaque défi possède un objectif et un résultat.</x:v>
       </x:c>
       <x:c r="H48" s="18" t="str"/>
       <x:c r="I48" s="20" t="str"/>
     </x:row>
-    <x:row r="49" ht="32" customHeight="1">
+    <x:row r="49" ht="29" customHeight="1">
       <x:c r="A49" s="19" t="str">
-        <x:v>MOD-09</x:v>
+        <x:v>MOD-08</x:v>
       </x:c>
       <x:c r="B49" s="19" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C49" s="19" t="str">
-        <x:v>Histoire et fin par combattant</x:v>
+        <x:v>Campagne scénarisée par épisode</x:v>
       </x:c>
       <x:c r="D49" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E49" s="19" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="F49" s="19" t="str">
-        <x:v>combat/stories.mjs / combat/progression.mjs</x:v>
-      </x:c>
+      <x:c r="F49" s="19" t="str"/>
       <x:c r="G49" s="19" t="str">
-        <x:v>Quatorze routes individuelles : introduction, quatre rencontres avec dialogues et arènes propres, puis conclusion.</x:v>
-      </x:c>
-      <x:c r="H49" s="19" t="str">
-        <x:v>Scénarios originaux de fan-game. Les campagnes par épisode restent distinctes.</x:v>
-      </x:c>
+        <x:v>Routes, dialogues, combats et événements propres à chaque épisode.</x:v>
+      </x:c>
+      <x:c r="H49" s="19" t="str"/>
       <x:c r="I49" s="20" t="str"/>
     </x:row>
-    <x:row r="50" ht="29" customHeight="1">
+    <x:row r="50" ht="32" customHeight="1">
       <x:c r="A50" s="18" t="str">
-        <x:v>MOD-10</x:v>
+        <x:v>MOD-09</x:v>
       </x:c>
       <x:c r="B50" s="18" t="str">
         <x:v>Modes</x:v>
       </x:c>
       <x:c r="C50" s="18" t="str">
-        <x:v>Coopération contre boss</x:v>
+        <x:v>Histoire et fin par combattant</x:v>
       </x:c>
       <x:c r="D50" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E50" s="18" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="F50" s="18" t="str"/>
+      <x:c r="F50" s="18" t="str">
+        <x:v>combat/stories.mjs / combat/progression.mjs</x:v>
+      </x:c>
       <x:c r="G50" s="18" t="str">
-        <x:v>Deux joueurs actifs contre un adversaire commun.</x:v>
-      </x:c>
-      <x:c r="H50" s="18" t="str"/>
+        <x:v>Quatorze routes individuelles : introduction, quatre rencontres avec dialogues et arènes propres, puis conclusion.</x:v>
+      </x:c>
+      <x:c r="H50" s="18" t="str">
+        <x:v>Scénarios originaux de fan-game. Les campagnes par épisode restent distinctes.</x:v>
+      </x:c>
       <x:c r="I50" s="20" t="str"/>
     </x:row>
     <x:row r="51" ht="29" customHeight="1">
       <x:c r="A51" s="19" t="str">
-        <x:v>CTL-01</x:v>
+        <x:v>MOD-10</x:v>
       </x:c>
       <x:c r="B51" s="19" t="str">
-        <x:v>Commandes</x:v>
+        <x:v>Modes</x:v>
       </x:c>
       <x:c r="C51" s="19" t="str">
-        <x:v>Clavier AZERTY / QWERTY</x:v>
+        <x:v>Coopération contre boss</x:v>
       </x:c>
       <x:c r="D51" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E51" s="19" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="F51" s="19" t="str">
-        <x:v>combat/input.mjs</x:v>
-      </x:c>
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F51" s="19" t="str"/>
       <x:c r="G51" s="19" t="str">
-        <x:v>Commandes affichées en fonction du clavier.</x:v>
+        <x:v>Deux joueurs actifs contre un adversaire commun.</x:v>
       </x:c>
       <x:c r="H51" s="19" t="str"/>
       <x:c r="I51" s="20" t="str"/>
     </x:row>
     <x:row r="52" ht="29" customHeight="1">
       <x:c r="A52" s="18" t="str">
-        <x:v>CTL-02</x:v>
+        <x:v>CTL-01</x:v>
       </x:c>
       <x:c r="B52" s="18" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C52" s="18" t="str">
-        <x:v>Directions relatives des spéciaux</x:v>
+        <x:v>Clavier AZERTY / QWERTY</x:v>
       </x:c>
       <x:c r="D52" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -3931,20 +3933,20 @@
         <x:v>combat/input.mjs</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
-        <x:v>Avant et arrière changent avec l’orientation du personnage.</x:v>
+        <x:v>Commandes affichées en fonction du clavier.</x:v>
       </x:c>
       <x:c r="H52" s="18" t="str"/>
       <x:c r="I52" s="20" t="str"/>
     </x:row>
     <x:row r="53" ht="29" customHeight="1">
       <x:c r="A53" s="19" t="str">
-        <x:v>CTL-03</x:v>
+        <x:v>CTL-02</x:v>
       </x:c>
       <x:c r="B53" s="19" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C53" s="19" t="str">
-        <x:v>Commandes tactiles</x:v>
+        <x:v>Directions relatives des spéciaux</x:v>
       </x:c>
       <x:c r="D53" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -3956,97 +3958,97 @@
         <x:v>combat/input.mjs</x:v>
       </x:c>
       <x:c r="G53" s="19" t="str">
-        <x:v>Maintiens multiples et relâchements fonctionnent.</x:v>
+        <x:v>Avant et arrière changent avec l’orientation du personnage.</x:v>
       </x:c>
       <x:c r="H53" s="19" t="str"/>
       <x:c r="I53" s="20" t="str"/>
     </x:row>
     <x:row r="54" ht="29" customHeight="1">
       <x:c r="A54" s="18" t="str">
-        <x:v>CTL-04</x:v>
+        <x:v>CTL-03</x:v>
       </x:c>
       <x:c r="B54" s="18" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C54" s="18" t="str">
-        <x:v>Manettes standard</x:v>
+        <x:v>Commandes tactiles</x:v>
       </x:c>
       <x:c r="D54" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E54" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F54" s="18" t="str">
         <x:v>combat/input.mjs</x:v>
       </x:c>
       <x:c r="G54" s="18" t="str">
-        <x:v>Les axes et boutons commandent les deux joueurs locaux.</x:v>
-      </x:c>
-      <x:c r="H54" s="18" t="str">
-        <x:v>Vérification matérielle réelle encore à mener.</x:v>
-      </x:c>
+        <x:v>Maintiens multiples et relâchements fonctionnent.</x:v>
+      </x:c>
+      <x:c r="H54" s="18" t="str"/>
       <x:c r="I54" s="20" t="str"/>
     </x:row>
-    <x:row r="55" ht="32" customHeight="1">
+    <x:row r="55" ht="29" customHeight="1">
       <x:c r="A55" s="19" t="str">
-        <x:v>CTL-05</x:v>
+        <x:v>CTL-04</x:v>
       </x:c>
       <x:c r="B55" s="19" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C55" s="19" t="str">
-        <x:v>Remappage individuel des touches</x:v>
+        <x:v>Manettes standard</x:v>
       </x:c>
       <x:c r="D55" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E55" s="19" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F55" s="19" t="str">
-        <x:v>combat/bindings.mjs / combat/input.mjs / combat/app.mjs</x:v>
+        <x:v>combat/input.mjs</x:v>
       </x:c>
       <x:c r="G55" s="19" t="str">
-        <x:v>Éditer les liaisons des deux joueurs, refuser les conflits et sauvegarder le réglage. Les libellés affichés suivent les touches effectives.</x:v>
-      </x:c>
-      <x:c r="H55" s="19" t="str"/>
+        <x:v>Les axes et boutons commandent les deux joueurs locaux.</x:v>
+      </x:c>
+      <x:c r="H55" s="19" t="str">
+        <x:v>Vérification matérielle réelle encore à mener.</x:v>
+      </x:c>
       <x:c r="I55" s="20" t="str"/>
     </x:row>
-    <x:row r="56" ht="29" customHeight="1">
+    <x:row r="56" ht="32" customHeight="1">
       <x:c r="A56" s="18" t="str">
-        <x:v>CTL-06</x:v>
+        <x:v>CTL-05</x:v>
       </x:c>
       <x:c r="B56" s="18" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C56" s="18" t="str">
-        <x:v>Annulation des touches au blur</x:v>
+        <x:v>Remappage individuel des touches</x:v>
       </x:c>
       <x:c r="D56" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E56" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="F56" s="18" t="str">
-        <x:v>combat/input.mjs</x:v>
+        <x:v>combat/bindings.mjs / combat/input.mjs / combat/app.mjs</x:v>
       </x:c>
       <x:c r="G56" s="18" t="str">
-        <x:v>Aucune direction ne reste enfoncée après changement de fenêtre.</x:v>
+        <x:v>Éditer les liaisons des deux joueurs, refuser les conflits et sauvegarder le réglage. Les libellés affichés suivent les touches effectives.</x:v>
       </x:c>
       <x:c r="H56" s="18" t="str"/>
       <x:c r="I56" s="20" t="str"/>
     </x:row>
     <x:row r="57" ht="29" customHeight="1">
       <x:c r="A57" s="19" t="str">
-        <x:v>CTL-07</x:v>
+        <x:v>CTL-06</x:v>
       </x:c>
       <x:c r="B57" s="19" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C57" s="19" t="str">
-        <x:v>Pause et reprise explicites</x:v>
+        <x:v>Annulation des touches au blur</x:v>
       </x:c>
       <x:c r="D57" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -4055,75 +4057,75 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F57" s="19" t="str">
-        <x:v>combat/app.mjs</x:v>
+        <x:v>combat/input.mjs</x:v>
       </x:c>
       <x:c r="G57" s="19" t="str">
-        <x:v>Le temps et le combat sont figés pendant la pause.</x:v>
+        <x:v>Aucune direction ne reste enfoncée après changement de fenêtre.</x:v>
       </x:c>
       <x:c r="H57" s="19" t="str"/>
       <x:c r="I57" s="20" t="str"/>
     </x:row>
     <x:row r="58" ht="29" customHeight="1">
       <x:c r="A58" s="18" t="str">
-        <x:v>CTL-08</x:v>
+        <x:v>CTL-07</x:v>
       </x:c>
       <x:c r="B58" s="18" t="str">
         <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C58" s="18" t="str">
-        <x:v>Navigation intégrale au clavier</x:v>
+        <x:v>Pause et reprise explicites</x:v>
       </x:c>
       <x:c r="D58" s="18" t="str">
-        <x:v>Partiel</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E58" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F58" s="18" t="str">
-        <x:v>combat/index.html</x:v>
+        <x:v>combat/app.mjs</x:v>
       </x:c>
       <x:c r="G58" s="18" t="str">
-        <x:v>Parcourir et activer toutes les vues et options sans souris.</x:v>
-      </x:c>
-      <x:c r="H58" s="18" t="str">
-        <x:v>Audit d’accessibilité complet requis.</x:v>
-      </x:c>
+        <x:v>Le temps et le combat sont figés pendant la pause.</x:v>
+      </x:c>
+      <x:c r="H58" s="18" t="str"/>
       <x:c r="I58" s="20" t="str"/>
     </x:row>
     <x:row r="59" ht="29" customHeight="1">
       <x:c r="A59" s="19" t="str">
-        <x:v>PRE-01</x:v>
+        <x:v>CTL-08</x:v>
       </x:c>
       <x:c r="B59" s="19" t="str">
-        <x:v>Présentation</x:v>
+        <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C59" s="19" t="str">
-        <x:v>Sélection de 14 combattants</x:v>
+        <x:v>Navigation intégrale au clavier</x:v>
       </x:c>
       <x:c r="D59" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Partiel</x:v>
       </x:c>
       <x:c r="E59" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F59" s="19" t="str">
-        <x:v>combat/data.mjs</x:v>
+        <x:v>combat/index.html</x:v>
       </x:c>
       <x:c r="G59" s="19" t="str">
-        <x:v>Chaque combattant a une silhouette et un kit distincts.</x:v>
-      </x:c>
-      <x:c r="H59" s="19" t="str"/>
+        <x:v>Parcourir et activer toutes les vues et options sans souris.</x:v>
+      </x:c>
+      <x:c r="H59" s="19" t="str">
+        <x:v>Audit d’accessibilité complet requis.</x:v>
+      </x:c>
       <x:c r="I59" s="20" t="str"/>
     </x:row>
     <x:row r="60" ht="29" customHeight="1">
       <x:c r="A60" s="18" t="str">
-        <x:v>PRE-02</x:v>
+        <x:v>PRE-01</x:v>
       </x:c>
       <x:c r="B60" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C60" s="18" t="str">
-        <x:v>Douze arènes thématiques</x:v>
+        <x:v>Sélection de 14 combattants</x:v>
       </x:c>
       <x:c r="D60" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -4132,50 +4134,48 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F60" s="18" t="str">
-        <x:v>combat/render.mjs</x:v>
+        <x:v>combat/data.mjs</x:v>
       </x:c>
       <x:c r="G60" s="18" t="str">
-        <x:v>Chaque arène a une composition visuelle identifiable.</x:v>
+        <x:v>Chaque combattant a une silhouette et un kit distincts.</x:v>
       </x:c>
       <x:c r="H60" s="18" t="str"/>
       <x:c r="I60" s="20" t="str"/>
     </x:row>
-    <x:row r="61" ht="32" customHeight="1">
+    <x:row r="61" ht="29" customHeight="1">
       <x:c r="A61" s="19" t="str">
-        <x:v>PRE-03</x:v>
+        <x:v>PRE-02</x:v>
       </x:c>
       <x:c r="B61" s="19" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C61" s="19" t="str">
-        <x:v>Variantes visuelles existantes</x:v>
+        <x:v>Douze arènes thématiques</x:v>
       </x:c>
       <x:c r="D61" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E61" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F61" s="19" t="str">
-        <x:v>combat/data.mjs</x:v>
+        <x:v>combat/render.mjs</x:v>
       </x:c>
       <x:c r="G61" s="19" t="str">
-        <x:v>Choisir les 51 apparences approuvées sans changer les mécaniques.</x:v>
-      </x:c>
-      <x:c r="H61" s="19" t="str">
-        <x:v>Liste explicite par identité. Parents, PNJ rivaux, accessoires, VFX et projections restent dans les archives.</x:v>
-      </x:c>
+        <x:v>Chaque arène a une composition visuelle identifiable.</x:v>
+      </x:c>
+      <x:c r="H61" s="19" t="str"/>
       <x:c r="I61" s="20" t="str"/>
     </x:row>
-    <x:row r="62" ht="29" customHeight="1">
+    <x:row r="62" ht="32" customHeight="1">
       <x:c r="A62" s="18" t="str">
-        <x:v>PRE-04</x:v>
+        <x:v>PRE-03</x:v>
       </x:c>
       <x:c r="B62" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C62" s="18" t="str">
-        <x:v>Catalogue de 179 apparences</x:v>
+        <x:v>Variantes visuelles existantes</x:v>
       </x:c>
       <x:c r="D62" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -4184,277 +4184,279 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F62" s="18" t="str">
-        <x:v>combat/sprite-catalog.mjs</x:v>
+        <x:v>combat/data.mjs</x:v>
       </x:c>
       <x:c r="G62" s="18" t="str">
-        <x:v>Chaque atlas CainOS est listé et localisable.</x:v>
-      </x:c>
-      <x:c r="H62" s="18" t="str"/>
+        <x:v>Choisir les 51 apparences approuvées sans changer les mécaniques.</x:v>
+      </x:c>
+      <x:c r="H62" s="18" t="str">
+        <x:v>Liste explicite par identité. Parents, PNJ rivaux, accessoires, VFX et projections restent dans les archives.</x:v>
+      </x:c>
       <x:c r="I62" s="20" t="str"/>
     </x:row>
     <x:row r="63" ht="29" customHeight="1">
       <x:c r="A63" s="19" t="str">
-        <x:v>PRE-05</x:v>
+        <x:v>PRE-04</x:v>
       </x:c>
       <x:c r="B63" s="19" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C63" s="19" t="str">
-        <x:v>Sprites de combat dédiés</x:v>
+        <x:v>Catalogue de 179 apparences</x:v>
       </x:c>
       <x:c r="D63" s="19" t="str">
-        <x:v>Partiel</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E63" s="19" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F63" s="19" t="str">
-        <x:v>combat/render.mjs</x:v>
+        <x:v>combat/sprite-catalog.mjs</x:v>
       </x:c>
       <x:c r="G63" s="19" t="str">
-        <x:v>Chaque action possède des images cohérentes avec ses frames.</x:v>
-      </x:c>
-      <x:c r="H63" s="19" t="str">
-        <x:v>Sept planches existantes. Pose d’interaction réutilisée pour attaquer.</x:v>
-      </x:c>
+        <x:v>Chaque atlas CainOS est listé et localisable.</x:v>
+      </x:c>
+      <x:c r="H63" s="19" t="str"/>
       <x:c r="I63" s="20" t="str"/>
     </x:row>
     <x:row r="64" ht="29" customHeight="1">
       <x:c r="A64" s="18" t="str">
-        <x:v>PRE-06</x:v>
+        <x:v>PRE-05</x:v>
       </x:c>
       <x:c r="B64" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C64" s="18" t="str">
-        <x:v>Décors finalisés par artiste</x:v>
+        <x:v>Sprites de combat dédiés</x:v>
       </x:c>
       <x:c r="D64" s="18" t="str">
         <x:v>Partiel</x:v>
       </x:c>
       <x:c r="E64" s="18" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F64" s="18" t="str">
         <x:v>combat/render.mjs</x:v>
       </x:c>
       <x:c r="G64" s="18" t="str">
-        <x:v>Valider les décors et chaque couche de parallaxe.</x:v>
+        <x:v>Chaque action possède des images cohérentes avec ses frames.</x:v>
       </x:c>
       <x:c r="H64" s="18" t="str">
-        <x:v>Les arènes actuelles sont dessinées procéduralement.</x:v>
+        <x:v>Sept planches existantes. Pose d’interaction réutilisée pour attaquer.</x:v>
       </x:c>
       <x:c r="I64" s="20" t="str"/>
     </x:row>
     <x:row r="65" ht="29" customHeight="1">
       <x:c r="A65" s="19" t="str">
-        <x:v>PRE-07</x:v>
+        <x:v>PRE-06</x:v>
       </x:c>
       <x:c r="B65" s="19" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C65" s="19" t="str">
-        <x:v>Effets de contact et projectiles</x:v>
+        <x:v>Décors finalisés par artiste</x:v>
       </x:c>
       <x:c r="D65" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Partiel</x:v>
       </x:c>
       <x:c r="E65" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="F65" s="19" t="str">
         <x:v>combat/render.mjs</x:v>
       </x:c>
       <x:c r="G65" s="19" t="str">
-        <x:v>Lire impacts, gardes, parades et projectiles pendant le combat.</x:v>
-      </x:c>
-      <x:c r="H65" s="19" t="str"/>
+        <x:v>Valider les décors et chaque couche de parallaxe.</x:v>
+      </x:c>
+      <x:c r="H65" s="19" t="str">
+        <x:v>Les arènes actuelles sont dessinées procéduralement.</x:v>
+      </x:c>
       <x:c r="I65" s="20" t="str"/>
     </x:row>
-    <x:row r="66" ht="32" customHeight="1">
+    <x:row r="66" ht="29" customHeight="1">
       <x:c r="A66" s="18" t="str">
-        <x:v>PRE-08</x:v>
+        <x:v>PRE-07</x:v>
       </x:c>
       <x:c r="B66" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C66" s="18" t="str">
-        <x:v>Bruitages de combat</x:v>
+        <x:v>Effets de contact et projectiles</x:v>
       </x:c>
       <x:c r="D66" s="18" t="str">
-        <x:v>Partiel</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E66" s="18" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F66" s="18" t="str">
-        <x:v>combat/audio.mjs</x:v>
+        <x:v>combat/render.mjs</x:v>
       </x:c>
       <x:c r="G66" s="18" t="str">
-        <x:v>16 motifs synthétiques livrés ; finaliser les effets encore partagés et vérifier le mixage sur plusieurs appareils.</x:v>
-      </x:c>
-      <x:c r="H66" s="18" t="str">
-        <x:v>Les impacts léger/lourd et certains événements utilisent le même motif. Aucune voix officielle importée.</x:v>
-      </x:c>
+        <x:v>Lire impacts, gardes, parades et projectiles pendant le combat.</x:v>
+      </x:c>
+      <x:c r="H66" s="18" t="str"/>
       <x:c r="I66" s="20" t="str"/>
     </x:row>
     <x:row r="67" ht="32" customHeight="1">
       <x:c r="A67" s="19" t="str">
-        <x:v>PRE-09</x:v>
+        <x:v>PRE-08</x:v>
       </x:c>
       <x:c r="B67" s="19" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C67" s="19" t="str">
-        <x:v>Musique originale par arène</x:v>
+        <x:v>Bruitages de combat</x:v>
       </x:c>
       <x:c r="D67" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Partiel</x:v>
       </x:c>
       <x:c r="E67" s="19" t="str">
-        <x:v>P2</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F67" s="19" t="str">
         <x:v>combat/audio.mjs</x:v>
       </x:c>
       <x:c r="G67" s="19" t="str">
-        <x:v>12 thèmes procéduraux originaux, un par arène, avec mélodie, basse, rythme et tempo propres. Réglages musique et bruitages séparés.</x:v>
+        <x:v>16 motifs synthétiques livrés ; finaliser les effets encore partagés et vérifier le mixage sur plusieurs appareils.</x:v>
       </x:c>
       <x:c r="H67" s="19" t="str">
-        <x:v>Musique optionnelle, silencieuse par défaut. Le menu adapte le thème du chapiteau. Validation du mixage matériel encore requise.</x:v>
+        <x:v>Les impacts léger/lourd et certains événements utilisent le même motif. Aucune voix officielle importée.</x:v>
       </x:c>
       <x:c r="I67" s="20" t="str"/>
     </x:row>
-    <x:row r="68" ht="29" customHeight="1">
+    <x:row r="68" ht="32" customHeight="1">
       <x:c r="A68" s="18" t="str">
-        <x:v>PRE-10</x:v>
+        <x:v>PRE-09</x:v>
       </x:c>
       <x:c r="B68" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C68" s="18" t="str">
-        <x:v>Voix et dialogues de combat</x:v>
+        <x:v>Musique originale par arène</x:v>
       </x:c>
       <x:c r="D68" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E68" s="18" t="str">
         <x:v>P2</x:v>
       </x:c>
-      <x:c r="F68" s="18" t="str"/>
+      <x:c r="F68" s="18" t="str">
+        <x:v>combat/audio.mjs</x:v>
+      </x:c>
       <x:c r="G68" s="18" t="str">
-        <x:v>Banque de voix autorisée et dialogues originaux cohérents.</x:v>
-      </x:c>
-      <x:c r="H68" s="18" t="str"/>
+        <x:v>12 thèmes procéduraux originaux, un par arène, avec mélodie, basse, rythme et tempo propres. Réglages musique et bruitages séparés.</x:v>
+      </x:c>
+      <x:c r="H68" s="18" t="str">
+        <x:v>Musique optionnelle, silencieuse par défaut. Le menu adapte le thème du chapiteau. Validation du mixage matériel encore requise.</x:v>
+      </x:c>
       <x:c r="I68" s="20" t="str"/>
     </x:row>
     <x:row r="69" ht="29" customHeight="1">
       <x:c r="A69" s="19" t="str">
-        <x:v>PRE-11</x:v>
+        <x:v>PRE-10</x:v>
       </x:c>
       <x:c r="B69" s="19" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C69" s="19" t="str">
-        <x:v>Réduction des mouvements</x:v>
+        <x:v>Voix et dialogues de combat</x:v>
       </x:c>
       <x:c r="D69" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E69" s="19" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="F69" s="19" t="str">
-        <x:v>combat/render.mjs</x:v>
-      </x:c>
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F69" s="19" t="str"/>
       <x:c r="G69" s="19" t="str">
-        <x:v>Le réglage limite les effets non essentiels.</x:v>
+        <x:v>Banque de voix autorisée et dialogues originaux cohérents.</x:v>
       </x:c>
       <x:c r="H69" s="19" t="str"/>
       <x:c r="I69" s="20" t="str"/>
     </x:row>
     <x:row r="70" ht="29" customHeight="1">
       <x:c r="A70" s="18" t="str">
-        <x:v>PRE-12</x:v>
+        <x:v>PRE-11</x:v>
       </x:c>
       <x:c r="B70" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C70" s="18" t="str">
-        <x:v>Palette et lecture daltonisme</x:v>
+        <x:v>Réduction des mouvements</x:v>
       </x:c>
       <x:c r="D70" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E70" s="18" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="F70" s="18" t="str"/>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F70" s="18" t="str">
+        <x:v>combat/render.mjs</x:v>
+      </x:c>
       <x:c r="G70" s="18" t="str">
-        <x:v>Les signaux critiques sont distincts sans dépendre seulement des couleurs.</x:v>
+        <x:v>Le réglage limite les effets non essentiels.</x:v>
       </x:c>
       <x:c r="H70" s="18" t="str"/>
       <x:c r="I70" s="20" t="str"/>
     </x:row>
     <x:row r="71" ht="29" customHeight="1">
       <x:c r="A71" s="19" t="str">
-        <x:v>PRE-13</x:v>
+        <x:v>PRE-12</x:v>
       </x:c>
       <x:c r="B71" s="19" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C71" s="19" t="str">
-        <x:v>Données de techniques dans le jeu</x:v>
+        <x:v>Palette et lecture daltonisme</x:v>
       </x:c>
       <x:c r="D71" s="19" t="str">
-        <x:v>Implémenté</x:v>
+        <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E71" s="19" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="F71" s="19" t="str">
-        <x:v>combat/app.mjs</x:v>
-      </x:c>
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F71" s="19" t="str"/>
       <x:c r="G71" s="19" t="str">
-        <x:v>Afficher coût, portée, timing et effet des techniques.</x:v>
+        <x:v>Les signaux critiques sont distincts sans dépendre seulement des couleurs.</x:v>
       </x:c>
       <x:c r="H71" s="19" t="str"/>
       <x:c r="I71" s="20" t="str"/>
     </x:row>
     <x:row r="72" ht="29" customHeight="1">
       <x:c r="A72" s="18" t="str">
-        <x:v>PRE-14</x:v>
+        <x:v>PRE-13</x:v>
       </x:c>
       <x:c r="B72" s="18" t="str">
         <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C72" s="18" t="str">
-        <x:v>Échelle et collisions cohérentes</x:v>
+        <x:v>Données de techniques dans le jeu</x:v>
       </x:c>
       <x:c r="D72" s="18" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E72" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F72" s="18" t="str">
-        <x:v>combat/engine.mjs</x:v>
+        <x:v>combat/app.mjs</x:v>
       </x:c>
       <x:c r="G72" s="18" t="str">
-        <x:v>Les colosses et Bubble ont des corps de collision propres.</x:v>
+        <x:v>Afficher coût, portée, timing et effet des techniques.</x:v>
       </x:c>
       <x:c r="H72" s="18" t="str"/>
       <x:c r="I72" s="20" t="str"/>
     </x:row>
     <x:row r="73" ht="29" customHeight="1">
       <x:c r="A73" s="19" t="str">
-        <x:v>PRO-01</x:v>
+        <x:v>PRE-14</x:v>
       </x:c>
       <x:c r="B73" s="19" t="str">
-        <x:v>Progression</x:v>
+        <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C73" s="19" t="str">
-        <x:v>Profil local versionné</x:v>
+        <x:v>Échelle et collisions cohérentes</x:v>
       </x:c>
       <x:c r="D73" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -4463,23 +4465,23 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F73" s="19" t="str">
-        <x:v>combat/session.mjs</x:v>
+        <x:v>combat/engine.mjs</x:v>
       </x:c>
       <x:c r="G73" s="19" t="str">
-        <x:v>Les paramètres et statistiques persistent localement.</x:v>
+        <x:v>Les colosses et Bubble ont des corps de collision propres.</x:v>
       </x:c>
       <x:c r="H73" s="19" t="str"/>
       <x:c r="I73" s="20" t="str"/>
     </x:row>
     <x:row r="74" ht="29" customHeight="1">
       <x:c r="A74" s="18" t="str">
-        <x:v>PRO-02</x:v>
+        <x:v>PRO-01</x:v>
       </x:c>
       <x:c r="B74" s="18" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C74" s="18" t="str">
-        <x:v>Import et export de sauvegarde</x:v>
+        <x:v>Profil local versionné</x:v>
       </x:c>
       <x:c r="D74" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -4491,45 +4493,45 @@
         <x:v>combat/session.mjs</x:v>
       </x:c>
       <x:c r="G74" s="18" t="str">
-        <x:v>Refuser les formats invalides et restaurer les données valides.</x:v>
+        <x:v>Les paramètres et statistiques persistent localement.</x:v>
       </x:c>
       <x:c r="H74" s="18" t="str"/>
       <x:c r="I74" s="20" t="str"/>
     </x:row>
     <x:row r="75" ht="29" customHeight="1">
       <x:c r="A75" s="19" t="str">
-        <x:v>PRO-03</x:v>
+        <x:v>PRO-02</x:v>
       </x:c>
       <x:c r="B75" s="19" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C75" s="19" t="str">
-        <x:v>Historique de matchs</x:v>
+        <x:v>Import et export de sauvegarde</x:v>
       </x:c>
       <x:c r="D75" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E75" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F75" s="19" t="str">
         <x:v>combat/session.mjs</x:v>
       </x:c>
       <x:c r="G75" s="19" t="str">
-        <x:v>Garder un historique borné des derniers résultats.</x:v>
+        <x:v>Refuser les formats invalides et restaurer les données valides.</x:v>
       </x:c>
       <x:c r="H75" s="19" t="str"/>
       <x:c r="I75" s="20" t="str"/>
     </x:row>
     <x:row r="76" ht="29" customHeight="1">
       <x:c r="A76" s="18" t="str">
-        <x:v>PRO-04</x:v>
+        <x:v>PRO-03</x:v>
       </x:c>
       <x:c r="B76" s="18" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C76" s="18" t="str">
-        <x:v>Défis et médailles</x:v>
+        <x:v>Historique de matchs</x:v>
       </x:c>
       <x:c r="D76" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -4541,20 +4543,20 @@
         <x:v>combat/session.mjs</x:v>
       </x:c>
       <x:c r="G76" s="18" t="str">
-        <x:v>Sauvegarder les défis réellement accomplis.</x:v>
+        <x:v>Garder un historique borné des derniers résultats.</x:v>
       </x:c>
       <x:c r="H76" s="18" t="str"/>
       <x:c r="I76" s="20" t="str"/>
     </x:row>
     <x:row r="77" ht="29" customHeight="1">
       <x:c r="A77" s="19" t="str">
-        <x:v>PRO-05</x:v>
+        <x:v>PRO-04</x:v>
       </x:c>
       <x:c r="B77" s="19" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C77" s="19" t="str">
-        <x:v>Replays déterministes locaux</x:v>
+        <x:v>Défis et médailles</x:v>
       </x:c>
       <x:c r="D77" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -4566,45 +4568,45 @@
         <x:v>combat/session.mjs</x:v>
       </x:c>
       <x:c r="G77" s="19" t="str">
-        <x:v>Relire les entrées avec la même graine et la même version.</x:v>
+        <x:v>Sauvegarder les défis réellement accomplis.</x:v>
       </x:c>
       <x:c r="H77" s="19" t="str"/>
       <x:c r="I77" s="20" t="str"/>
     </x:row>
     <x:row r="78" ht="29" customHeight="1">
       <x:c r="A78" s="18" t="str">
-        <x:v>PRO-06</x:v>
+        <x:v>PRO-05</x:v>
       </x:c>
       <x:c r="B78" s="18" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C78" s="18" t="str">
-        <x:v>Synchronisation cloud des combats</x:v>
+        <x:v>Replays déterministes locaux</x:v>
       </x:c>
       <x:c r="D78" s="18" t="str">
-        <x:v>Prévu</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E78" s="18" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="F78" s="18" t="str"/>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F78" s="18" t="str">
+        <x:v>combat/session.mjs</x:v>
+      </x:c>
       <x:c r="G78" s="18" t="str">
-        <x:v>Conflits et synchronisation de profils gérés.</x:v>
-      </x:c>
-      <x:c r="H78" s="18" t="str">
-        <x:v>Le compte cloud CainOS existant ne suffit pas à établir cette fonctionnalité.</x:v>
-      </x:c>
+        <x:v>Relire les entrées avec la même graine et la même version.</x:v>
+      </x:c>
+      <x:c r="H78" s="18" t="str"/>
       <x:c r="I78" s="20" t="str"/>
     </x:row>
     <x:row r="79" ht="29" customHeight="1">
       <x:c r="A79" s="19" t="str">
-        <x:v>PRO-07</x:v>
+        <x:v>PRO-06</x:v>
       </x:c>
       <x:c r="B79" s="19" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C79" s="19" t="str">
-        <x:v>Déblocages et économie</x:v>
+        <x:v>Synchronisation cloud des combats</x:v>
       </x:c>
       <x:c r="D79" s="19" t="str">
         <x:v>Prévu</x:v>
@@ -4614,70 +4616,68 @@
       </x:c>
       <x:c r="F79" s="19" t="str"/>
       <x:c r="G79" s="19" t="str">
-        <x:v>Définir des conditions de déblocage lisibles et sans perte de contenu.</x:v>
-      </x:c>
-      <x:c r="H79" s="19" t="str"/>
+        <x:v>Conflits et synchronisation de profils gérés.</x:v>
+      </x:c>
+      <x:c r="H79" s="19" t="str">
+        <x:v>Le compte cloud CainOS existant ne suffit pas à établir cette fonctionnalité.</x:v>
+      </x:c>
       <x:c r="I79" s="20" t="str"/>
     </x:row>
     <x:row r="80" ht="29" customHeight="1">
       <x:c r="A80" s="18" t="str">
-        <x:v>PRO-08</x:v>
+        <x:v>PRO-07</x:v>
       </x:c>
       <x:c r="B80" s="18" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C80" s="18" t="str">
-        <x:v>Personnalisation de profils</x:v>
+        <x:v>Déblocages et économie</x:v>
       </x:c>
       <x:c r="D80" s="18" t="str">
         <x:v>Prévu</x:v>
       </x:c>
       <x:c r="E80" s="18" t="str">
-        <x:v>P3</x:v>
+        <x:v>P2</x:v>
       </x:c>
       <x:c r="F80" s="18" t="str"/>
       <x:c r="G80" s="18" t="str">
-        <x:v>Noms, emblèmes et préférences par joueur.</x:v>
+        <x:v>Définir des conditions de déblocage lisibles et sans perte de contenu.</x:v>
       </x:c>
       <x:c r="H80" s="18" t="str"/>
       <x:c r="I80" s="20" t="str"/>
     </x:row>
-    <x:row r="81" ht="32" customHeight="1">
+    <x:row r="81" ht="29" customHeight="1">
       <x:c r="A81" s="19" t="str">
-        <x:v>PRO-09</x:v>
+        <x:v>PRO-08</x:v>
       </x:c>
       <x:c r="B81" s="19" t="str">
         <x:v>Progression</x:v>
       </x:c>
       <x:c r="C81" s="19" t="str">
+        <x:v>Personnalisation de profils</x:v>
+      </x:c>
+      <x:c r="D81" s="19" t="str">
+        <x:v>Prévu</x:v>
+      </x:c>
+      <x:c r="E81" s="19" t="str">
+        <x:v>P3</x:v>
+      </x:c>
+      <x:c r="F81" s="19" t="str"/>
+      <x:c r="G81" s="19" t="str">
+        <x:v>Noms, emblèmes et préférences par joueur.</x:v>
+      </x:c>
+      <x:c r="H81" s="19" t="str"/>
+      <x:c r="I81" s="20" t="str"/>
+    </x:row>
+    <x:row r="82" ht="32" customHeight="1">
+      <x:c r="A82" s="18" t="str">
+        <x:v>PRO-09</x:v>
+      </x:c>
+      <x:c r="B82" s="18" t="str">
+        <x:v>Progression</x:v>
+      </x:c>
+      <x:c r="C82" s="18" t="str">
         <x:v>Reprise des programmes en cours</x:v>
-      </x:c>
-      <x:c r="D81" s="19" t="str">
-        <x:v>Implémenté</x:v>
-      </x:c>
-      <x:c r="E81" s="19" t="str">
-        <x:v>P0</x:v>
-      </x:c>
-      <x:c r="F81" s="19" t="str">
-        <x:v>combat/progression.mjs / combat/session.mjs</x:v>
-      </x:c>
-      <x:c r="G81" s="19" t="str">
-        <x:v>Arcade, boss, survie, histoire et tournoi reprennent la rencontre courante avec la même graine, les mêmes règles et la santé de départ enregistrée.</x:v>
-      </x:c>
-      <x:c r="H81" s="19" t="str">
-        <x:v>Le point de reprise est le début du duel, sans restauration d’une frame de simulation intermédiaire.</x:v>
-      </x:c>
-      <x:c r="I81" s="20" t="str"/>
-    </x:row>
-    <x:row r="82" ht="29" customHeight="1">
-      <x:c r="A82" s="18" t="str">
-        <x:v>PRD-01</x:v>
-      </x:c>
-      <x:c r="B82" s="18" t="str">
-        <x:v>Production</x:v>
-      </x:c>
-      <x:c r="C82" s="18" t="str">
-        <x:v>Excel relié aux données du jeu</x:v>
       </x:c>
       <x:c r="D82" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -4686,23 +4686,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F82" s="18" t="str">
-        <x:v>scripts/build-combat-workbook.mjs</x:v>
+        <x:v>combat/progression.mjs / combat/session.mjs</x:v>
       </x:c>
       <x:c r="G82" s="18" t="str">
-        <x:v>Régénérer les onglets depuis les définitions et conserver les preuves.</x:v>
-      </x:c>
-      <x:c r="H82" s="18" t="str"/>
+        <x:v>Arcade, boss, survie, histoire et tournoi reprennent la rencontre courante avec la même graine, les mêmes règles et la santé de départ enregistrée.</x:v>
+      </x:c>
+      <x:c r="H82" s="18" t="str">
+        <x:v>Le point de reprise est le début du duel, sans restauration d’une frame de simulation intermédiaire.</x:v>
+      </x:c>
       <x:c r="I82" s="20" t="str"/>
     </x:row>
-    <x:row r="83" ht="29" customHeight="1">
+    <x:row r="83" ht="32" customHeight="1">
       <x:c r="A83" s="19" t="str">
-        <x:v>PRD-02</x:v>
+        <x:v>PRO-10</x:v>
       </x:c>
       <x:c r="B83" s="19" t="str">
-        <x:v>Production</x:v>
+        <x:v>Progression</x:v>
       </x:c>
       <x:c r="C83" s="19" t="str">
-        <x:v>Inventaire reproductible des sprites</x:v>
+        <x:v>Récupération du profil après checkpoint invalide</x:v>
       </x:c>
       <x:c r="D83" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -4711,23 +4713,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F83" s="19" t="str">
-        <x:v>scripts/build-combat-catalog.mjs</x:v>
+        <x:v>combat/session.mjs / combat/app.mjs</x:v>
       </x:c>
       <x:c r="G83" s="19" t="str">
-        <x:v>Extraction de toutes les entrées sans exécuter CainOS.</x:v>
-      </x:c>
-      <x:c r="H83" s="19" t="str"/>
+        <x:v>Au chargement local, abandonner uniquement le programme actif invalide et conserver les réglages, statistiques, défis, médailles, fins narratives et historique encore valides.</x:v>
+      </x:c>
+      <x:c r="H83" s="19" t="str">
+        <x:v>La prochaine sauvegarde conserve le profil normalisé. L’import manuel reste strict et refuse le fichier invalide sans remplacer le profil courant.</x:v>
+      </x:c>
       <x:c r="I83" s="20" t="str"/>
     </x:row>
     <x:row r="84" ht="29" customHeight="1">
       <x:c r="A84" s="18" t="str">
-        <x:v>PRD-03</x:v>
+        <x:v>PRD-01</x:v>
       </x:c>
       <x:c r="B84" s="18" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C84" s="18" t="str">
-        <x:v>Tests déterministes du moteur</x:v>
+        <x:v>Excel relié aux données du jeu</x:v>
       </x:c>
       <x:c r="D84" s="18" t="str">
         <x:v>Implémenté</x:v>
@@ -4736,23 +4740,23 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F84" s="18" t="str">
-        <x:v>tests/combat-engine.test.mjs</x:v>
+        <x:v>scripts/build-combat-workbook.mjs</x:v>
       </x:c>
       <x:c r="G84" s="18" t="str">
-        <x:v>Les cas automatisés doivent tous passer dans le commit publié.</x:v>
+        <x:v>Régénérer les onglets depuis les définitions et conserver les preuves.</x:v>
       </x:c>
       <x:c r="H84" s="18" t="str"/>
       <x:c r="I84" s="20" t="str"/>
     </x:row>
     <x:row r="85" ht="29" customHeight="1">
       <x:c r="A85" s="19" t="str">
-        <x:v>PRD-04</x:v>
+        <x:v>PRD-02</x:v>
       </x:c>
       <x:c r="B85" s="19" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C85" s="19" t="str">
-        <x:v>Contrôles navigateur OS / autonome</x:v>
+        <x:v>Inventaire reproductible des sprites</x:v>
       </x:c>
       <x:c r="D85" s="19" t="str">
         <x:v>Implémenté</x:v>
@@ -4761,100 +4765,100 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F85" s="19" t="str">
-        <x:v>docs/combat-qa-evidence.json</x:v>
+        <x:v>scripts/build-combat-catalog.mjs</x:v>
       </x:c>
       <x:c r="G85" s="19" t="str">
-        <x:v>Vérifier les parcours réels et consigner les résultats.</x:v>
+        <x:v>Extraction de toutes les entrées sans exécuter CainOS.</x:v>
       </x:c>
       <x:c r="H85" s="19" t="str"/>
       <x:c r="I85" s="20" t="str"/>
     </x:row>
     <x:row r="86" ht="29" customHeight="1">
       <x:c r="A86" s="18" t="str">
-        <x:v>PRD-05</x:v>
+        <x:v>PRD-03</x:v>
       </x:c>
       <x:c r="B86" s="18" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C86" s="18" t="str">
-        <x:v>Validation de lore du catalogue étendu</x:v>
+        <x:v>Tests déterministes du moteur</x:v>
       </x:c>
       <x:c r="D86" s="18" t="str">
-        <x:v>Partiel</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E86" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F86" s="18" t="str">
-        <x:v>combat/data.mjs</x:v>
+        <x:v>tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G86" s="18" t="str">
-        <x:v>Lier chaque entrée étendue à une source primaire vérifiée.</x:v>
-      </x:c>
-      <x:c r="H86" s="18" t="str">
-        <x:v>Les anciens textes CainOS restent identifiés comme archives du projet.</x:v>
-      </x:c>
+        <x:v>Les cas automatisés doivent tous passer dans le commit publié.</x:v>
+      </x:c>
+      <x:c r="H86" s="18" t="str"/>
       <x:c r="I86" s="20" t="str"/>
     </x:row>
     <x:row r="87" ht="29" customHeight="1">
       <x:c r="A87" s="19" t="str">
-        <x:v>PRD-06</x:v>
+        <x:v>PRD-04</x:v>
       </x:c>
       <x:c r="B87" s="19" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C87" s="19" t="str">
-        <x:v>Validation visuelle de chaque costume</x:v>
+        <x:v>Contrôles navigateur OS / autonome</x:v>
       </x:c>
       <x:c r="D87" s="19" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Implémenté</x:v>
       </x:c>
       <x:c r="E87" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F87" s="19" t="str">
-        <x:v>combat/sprite-catalog.mjs</x:v>
+        <x:v>docs/combat-qa-evidence.json</x:v>
       </x:c>
       <x:c r="G87" s="19" t="str">
-        <x:v>Contrôler recadrage, transparence et lisibilité des 51 variantes.</x:v>
-      </x:c>
-      <x:c r="H87" s="19" t="str">
-        <x:v>Le contrôle de classification ne remplace pas la revue artistique de chaque apparence.</x:v>
-      </x:c>
+        <x:v>Vérifier les parcours réels et consigner les résultats.</x:v>
+      </x:c>
+      <x:c r="H87" s="19" t="str"/>
       <x:c r="I87" s="20" t="str"/>
     </x:row>
     <x:row r="88" ht="29" customHeight="1">
       <x:c r="A88" s="18" t="str">
-        <x:v>PRD-07</x:v>
+        <x:v>PRD-05</x:v>
       </x:c>
       <x:c r="B88" s="18" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C88" s="18" t="str">
-        <x:v>Tests matériels mobiles</x:v>
+        <x:v>Validation de lore du catalogue étendu</x:v>
       </x:c>
       <x:c r="D88" s="18" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Partiel</x:v>
       </x:c>
       <x:c r="E88" s="18" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="F88" s="18" t="str"/>
+      <x:c r="F88" s="18" t="str">
+        <x:v>combat/data.mjs</x:v>
+      </x:c>
       <x:c r="G88" s="18" t="str">
-        <x:v>Tester les gestes sur téléphone et tablette physiques.</x:v>
-      </x:c>
-      <x:c r="H88" s="18" t="str"/>
+        <x:v>Lier chaque entrée étendue à une source primaire vérifiée.</x:v>
+      </x:c>
+      <x:c r="H88" s="18" t="str">
+        <x:v>Les anciens textes CainOS restent identifiés comme archives du projet.</x:v>
+      </x:c>
       <x:c r="I88" s="20" t="str"/>
     </x:row>
     <x:row r="89" ht="29" customHeight="1">
       <x:c r="A89" s="19" t="str">
-        <x:v>PRD-08</x:v>
+        <x:v>PRD-06</x:v>
       </x:c>
       <x:c r="B89" s="19" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C89" s="19" t="str">
-        <x:v>Tests multi-manettes matériels</x:v>
+        <x:v>Validation visuelle de chaque costume</x:v>
       </x:c>
       <x:c r="D89" s="19" t="str">
         <x:v>À vérifier</x:v>
@@ -4862,69 +4866,119 @@
       <x:c r="E89" s="19" t="str">
         <x:v>P1</x:v>
       </x:c>
-      <x:c r="F89" s="19" t="str"/>
+      <x:c r="F89" s="19" t="str">
+        <x:v>combat/sprite-catalog.mjs</x:v>
+      </x:c>
       <x:c r="G89" s="19" t="str">
-        <x:v>Tester deux manettes et leur déconnexion.</x:v>
-      </x:c>
-      <x:c r="H89" s="19" t="str"/>
+        <x:v>Contrôler recadrage, transparence et lisibilité des 51 variantes.</x:v>
+      </x:c>
+      <x:c r="H89" s="19" t="str">
+        <x:v>Le contrôle de classification ne remplace pas la revue artistique de chaque apparence.</x:v>
+      </x:c>
       <x:c r="I89" s="20" t="str"/>
     </x:row>
     <x:row r="90" ht="29" customHeight="1">
       <x:c r="A90" s="18" t="str">
-        <x:v>PRD-09</x:v>
+        <x:v>PRD-07</x:v>
       </x:c>
       <x:c r="B90" s="18" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C90" s="18" t="str">
-        <x:v>Parité de tous les modules CQC</x:v>
+        <x:v>Tests matériels mobiles</x:v>
       </x:c>
       <x:c r="D90" s="18" t="str">
-        <x:v>Partiel</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E90" s="18" t="str">
-        <x:v>P2</x:v>
-      </x:c>
-      <x:c r="F90" s="18" t="str">
-        <x:v>combat/engine.mjs</x:v>
-      </x:c>
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F90" s="18" t="str"/>
       <x:c r="G90" s="18" t="str">
-        <x:v>Comparer explicitement chaque module du CQC de référence.</x:v>
-      </x:c>
-      <x:c r="H90" s="18" t="str">
-        <x:v>Le moteur et la structure sont repris. Toutes les extensions MGS ne sont pas portées.</x:v>
-      </x:c>
+        <x:v>Tester les gestes sur téléphone et tablette physiques.</x:v>
+      </x:c>
+      <x:c r="H90" s="18" t="str"/>
       <x:c r="I90" s="20" t="str"/>
     </x:row>
-    <x:row r="91" ht="32" customHeight="1">
+    <x:row r="91" ht="29" customHeight="1">
       <x:c r="A91" s="19" t="str">
-        <x:v>PRD-10</x:v>
+        <x:v>PRD-08</x:v>
       </x:c>
       <x:c r="B91" s="19" t="str">
         <x:v>Production</x:v>
       </x:c>
       <x:c r="C91" s="19" t="str">
+        <x:v>Tests multi-manettes matériels</x:v>
+      </x:c>
+      <x:c r="D91" s="19" t="str">
+        <x:v>À vérifier</x:v>
+      </x:c>
+      <x:c r="E91" s="19" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="F91" s="19" t="str"/>
+      <x:c r="G91" s="19" t="str">
+        <x:v>Tester deux manettes et leur déconnexion.</x:v>
+      </x:c>
+      <x:c r="H91" s="19" t="str"/>
+      <x:c r="I91" s="20" t="str"/>
+    </x:row>
+    <x:row r="92" ht="29" customHeight="1">
+      <x:c r="A92" s="18" t="str">
+        <x:v>PRD-09</x:v>
+      </x:c>
+      <x:c r="B92" s="18" t="str">
+        <x:v>Production</x:v>
+      </x:c>
+      <x:c r="C92" s="18" t="str">
+        <x:v>Parité de tous les modules CQC</x:v>
+      </x:c>
+      <x:c r="D92" s="18" t="str">
+        <x:v>Partiel</x:v>
+      </x:c>
+      <x:c r="E92" s="18" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="F92" s="18" t="str">
+        <x:v>combat/engine.mjs</x:v>
+      </x:c>
+      <x:c r="G92" s="18" t="str">
+        <x:v>Comparer explicitement chaque module du CQC de référence.</x:v>
+      </x:c>
+      <x:c r="H92" s="18" t="str">
+        <x:v>Le moteur et la structure sont repris. Toutes les extensions MGS ne sont pas portées.</x:v>
+      </x:c>
+      <x:c r="I92" s="20" t="str"/>
+    </x:row>
+    <x:row r="93" ht="32" customHeight="1">
+      <x:c r="A93" s="19" t="str">
+        <x:v>PRD-10</x:v>
+      </x:c>
+      <x:c r="B93" s="19" t="str">
+        <x:v>Production</x:v>
+      </x:c>
+      <x:c r="C93" s="19" t="str">
         <x:v>Classement explicite de toutes les apparences</x:v>
       </x:c>
-      <x:c r="D91" s="19" t="str">
+      <x:c r="D93" s="19" t="str">
         <x:v>Implémenté</x:v>
       </x:c>
-      <x:c r="E91" s="19" t="str">
+      <x:c r="E93" s="19" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="F91" s="19" t="str">
+      <x:c r="F93" s="19" t="str">
         <x:v>combat/data.mjs / tests/combat-catalog.test.mjs</x:v>
       </x:c>
-      <x:c r="G91" s="19" t="str">
+      <x:c r="G93" s="19" t="str">
         <x:v>Réconcilier 14 combattants, 51 variantes compatibles et 114 archives sans kit, soit 179 entrées conservées.</x:v>
       </x:c>
-      <x:c r="H91" s="19" t="str">
+      <x:c r="H93" s="19" t="str">
         <x:v>Tout nouvel identifiant reste sans kit tant que sa classification n’a pas été revue.</x:v>
       </x:c>
-      <x:c r="I91" s="20" t="str"/>
+      <x:c r="I93" s="20" t="str"/>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D6:D91">
+  <x:conditionalFormatting sqref="D6:D93">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Implémenté"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Partiel"/>
     <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="Prévu"/>
@@ -4934,13 +4988,13 @@
     <x:cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="Non exécuté"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="D6:D91">
+    <x:dataValidation type="list" sqref="D6:D93">
       <x:formula1>"Implémenté,Partiel,Prévu,À vérifier,Hors périmètre"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6117ac9fd97b4f45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc84c1ef9fb0344fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6056,7 +6110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c0904457b2b4377"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re05c63ee38ab4dea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13814,7 +13868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbad20511f85a45b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad5ed55945b94a3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14552,7 +14606,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red5df2fe805a4650"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8feea3acbec145b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25278,7 +25332,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6d43e3b3ca743e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4694d84a57f4a21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37014,7 +37068,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcb54bcf61154300"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R683582c4eb704b2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40121,7 +40175,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93a3e229b00f43bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a2fd858b31246d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40238,7 +40292,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H6" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40265,7 +40319,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G7" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H7" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40292,7 +40346,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H8" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40319,7 +40373,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G9" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H9" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40346,7 +40400,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H10" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40373,7 +40427,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G11" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H11" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40400,7 +40454,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G12" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H12" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40427,7 +40481,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G13" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H13" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40454,7 +40508,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G14" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H14" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40481,7 +40535,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G15" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H15" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40508,7 +40562,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H16" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40535,7 +40589,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G17" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H17" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40562,7 +40616,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H18" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40589,7 +40643,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G19" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H19" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40616,7 +40670,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G20" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H20" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40643,7 +40697,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G21" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H21" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40670,7 +40724,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H22" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40697,7 +40751,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G23" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H23" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40724,7 +40778,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G24" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H24" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40751,7 +40805,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G25" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H25" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40778,7 +40832,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G26" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H26" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40805,7 +40859,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G27" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H27" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40832,7 +40886,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H28" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40859,7 +40913,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G29" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H29" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40886,7 +40940,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H30" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40913,7 +40967,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G31" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H31" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40940,7 +40994,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G32" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H32" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40967,7 +41021,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G33" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H33" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -40994,7 +41048,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G34" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H34" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41021,7 +41075,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G35" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H35" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41048,7 +41102,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G36" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H36" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41075,7 +41129,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G37" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H37" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41102,7 +41156,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G38" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H38" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41129,7 +41183,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G39" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H39" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41156,7 +41210,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G40" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H40" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41183,7 +41237,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G41" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H41" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41210,7 +41264,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G42" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H42" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41237,7 +41291,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G43" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H43" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41264,7 +41318,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G44" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H44" s="18" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41291,7 +41345,7 @@
         <x:v>node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G45" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-engine.test.mjs — 40/40 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-engine.test.tap)</x:v>
       </x:c>
       <x:c r="H45" s="19" t="str">
         <x:v>Vérification déterministe de mécanique</x:v>
@@ -41318,7 +41372,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H46" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41345,7 +41399,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G47" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H47" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41372,7 +41426,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H48" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41399,7 +41453,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G49" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H49" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41426,7 +41480,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G50" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H50" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41453,7 +41507,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G51" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H51" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41468,7 +41522,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C52" s="18" t="str">
-        <x:v>every selectable fighter receives complete arcade, boss and survival routes</x:v>
+        <x:v>local recovery drops only a malformed checkpoint and preserves the full saved profile</x:v>
       </x:c>
       <x:c r="D52" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41480,7 +41534,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H52" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41495,7 +41549,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C53" s="19" t="str">
-        <x:v>challenge first-impact can be completed from normal spawns within 60 seconds</x:v>
+        <x:v>old programme versions, changed routes and retired costumes do not erase local achievements or bindings</x:v>
       </x:c>
       <x:c r="D53" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41507,7 +41561,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G53" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H53" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41522,7 +41576,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C54" s="18" t="str">
-        <x:v>challenge guard can be completed from normal spawns within 60 seconds</x:v>
+        <x:v>a recovered local profile can be saved and reloaded without losing previous progress or settings</x:v>
       </x:c>
       <x:c r="D54" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41534,7 +41588,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G54" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H54" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41549,7 +41603,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C55" s="19" t="str">
-        <x:v>challenge combo can be completed from normal spawns within 60 seconds</x:v>
+        <x:v>profile imports and direct saves remain strict unless programme recovery is explicitly requested</x:v>
       </x:c>
       <x:c r="D55" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41561,7 +41615,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G55" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H55" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41576,7 +41630,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C56" s="18" t="str">
-        <x:v>challenge throw can be completed from normal spawns within 60 seconds</x:v>
+        <x:v>tolerant local reading preserves valid checkpoints and never accepts another profile format or version</x:v>
       </x:c>
       <x:c r="D56" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41588,7 +41642,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G56" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H56" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41603,7 +41657,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C57" s="19" t="str">
-        <x:v>challenge specialist can be completed from normal spawns within 60 seconds</x:v>
+        <x:v>every selectable fighter receives complete arcade, boss and survival routes</x:v>
       </x:c>
       <x:c r="D57" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41615,7 +41669,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G57" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H57" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41630,7 +41684,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C58" s="18" t="str">
-        <x:v>challenge super can be completed from normal spawns within 60 seconds</x:v>
+        <x:v>challenge first-impact can be completed from normal spawns within 60 seconds</x:v>
       </x:c>
       <x:c r="D58" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41642,7 +41696,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G58" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H58" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41657,7 +41711,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C59" s="19" t="str">
-        <x:v>actual blocked, throw and multi-projectile super events credit the correct player and technique</x:v>
+        <x:v>challenge guard can be completed from normal spawns within 60 seconds</x:v>
       </x:c>
       <x:c r="D59" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41669,7 +41723,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G59" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H59" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41684,7 +41738,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C60" s="18" t="str">
-        <x:v>a complete multi-round human-versus-CPU recording replays identical state and results</x:v>
+        <x:v>challenge combo can be completed from normal spawns within 60 seconds</x:v>
       </x:c>
       <x:c r="D60" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41696,7 +41750,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G60" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H60" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41711,7 +41765,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C61" s="19" t="str">
-        <x:v>native edge pulses remain deterministic when a pause separates adjacent recorded throw-tech inputs</x:v>
+        <x:v>challenge throw can be completed from normal spawns within 60 seconds</x:v>
       </x:c>
       <x:c r="D61" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41723,7 +41777,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G61" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H61" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41738,7 +41792,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C62" s="18" t="str">
-        <x:v>a keyboard attack pressed and released between polls starts exactly once in the combat engine</x:v>
+        <x:v>challenge specialist can be completed from normal spawns within 60 seconds</x:v>
       </x:c>
       <x:c r="D62" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41750,7 +41804,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G62" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H62" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41765,7 +41819,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C63" s="19" t="str">
-        <x:v>keyboard direction plus special follows facing and a held action is not retriggered</x:v>
+        <x:v>challenge super can be completed from normal spawns within 60 seconds</x:v>
       </x:c>
       <x:c r="D63" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41777,7 +41831,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G63" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H63" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41792,7 +41846,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C64" s="18" t="str">
-        <x:v>two local keyboard maps remain independent and form fields do not trigger attacks</x:v>
+        <x:v>actual blocked, throw and multi-projectile super events credit the correct player and technique</x:v>
       </x:c>
       <x:c r="D64" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41804,7 +41858,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G64" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H64" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41819,7 +41873,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C65" s="19" t="str">
-        <x:v>quick touch attacks retain directional specials and the dedicated throw-tech button</x:v>
+        <x:v>a complete multi-round human-versus-CPU recording replays identical state and results</x:v>
       </x:c>
       <x:c r="D65" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41831,7 +41885,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G65" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H65" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41846,7 +41900,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C66" s="18" t="str">
-        <x:v>multitouch releases only the matching pointer and inactive controls cannot queue an attack</x:v>
+        <x:v>native edge pulses remain deterministic when a pause separates adjacent recorded throw-tech inputs</x:v>
       </x:c>
       <x:c r="D66" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41858,7 +41912,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G66" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H66" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41873,7 +41927,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C67" s="19" t="str">
-        <x:v>blur and tab hiding release movement and queued attacks without affecting key bindings</x:v>
+        <x:v>a keyboard attack pressed and released between polls starts exactly once in the combat engine</x:v>
       </x:c>
       <x:c r="D67" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41885,7 +41939,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G67" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H67" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41900,7 +41954,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C68" s="18" t="str">
-        <x:v>standard gamepads provide separate player inputs and one action edge per physical press</x:v>
+        <x:v>keyboard direction plus special follows facing and a held action is not retriggered</x:v>
       </x:c>
       <x:c r="D68" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41912,7 +41966,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G68" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H68" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41927,7 +41981,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C69" s="19" t="str">
-        <x:v>version one profiles migrate with safe bindings, quiet music and no invented progress</x:v>
+        <x:v>two local keyboard maps remain independent and form fields do not trigger attacks</x:v>
       </x:c>
       <x:c r="D69" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41939,7 +41993,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G69" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H69" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41954,7 +42008,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C70" s="18" t="str">
-        <x:v>profile exports preserve canonical progress, costumes and individually earned endings</x:v>
+        <x:v>quick touch attacks retain directional specials and the dedicated throw-tech button</x:v>
       </x:c>
       <x:c r="D70" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -41966,7 +42020,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G70" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H70" s="18" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -41981,7 +42035,7 @@
         <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C71" s="19" t="str">
-        <x:v>replays retain known costumes and reject unrelated variants while keeping 0.1 compatibility</x:v>
+        <x:v>multitouch releases only the matching pointer and inactive controls cannot queue an attack</x:v>
       </x:c>
       <x:c r="D71" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -41993,7 +42047,7 @@
         <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G71" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 26/26 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H71" s="19" t="str">
         <x:v>Vérification de parcours, entrées ou persistance</x:v>
@@ -42002,13 +42056,13 @@
     </x:row>
     <x:row r="72" ht="32" customHeight="1">
       <x:c r="A72" s="18" t="str">
-        <x:v>QA-AUD-01</x:v>
+        <x:v>QA-SES-27</x:v>
       </x:c>
       <x:c r="B72" s="18" t="str">
-        <x:v>Audio synthétique</x:v>
+        <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C72" s="18" t="str">
-        <x:v>every playable stage has a distinct frozen original arrangement</x:v>
+        <x:v>blur and tab hiding release movement and queued attacks without affecting key bindings</x:v>
       </x:c>
       <x:c r="D72" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42017,25 +42071,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F72" s="18" t="str">
-        <x:v>node tests/combat-audio.test.mjs</x:v>
+        <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G72" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H72" s="18" t="str">
-        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
+        <x:v>Vérification de parcours, entrées ou persistance</x:v>
       </x:c>
       <x:c r="I72" s="20" t="str"/>
     </x:row>
     <x:row r="73" ht="32" customHeight="1">
       <x:c r="A73" s="19" t="str">
-        <x:v>QA-AUD-02</x:v>
+        <x:v>QA-SES-28</x:v>
       </x:c>
       <x:c r="B73" s="19" t="str">
-        <x:v>Audio synthétique</x:v>
+        <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C73" s="19" t="str">
-        <x:v>missing or denied audio remains an optional no-op</x:v>
+        <x:v>standard gamepads provide separate player inputs and one action edge per physical press</x:v>
       </x:c>
       <x:c r="D73" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42044,25 +42098,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F73" s="19" t="str">
-        <x:v>node tests/combat-audio.test.mjs</x:v>
+        <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G73" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H73" s="19" t="str">
-        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
+        <x:v>Vérification de parcours, entrées ou persistance</x:v>
       </x:c>
       <x:c r="I73" s="20" t="str"/>
     </x:row>
     <x:row r="74" ht="32" customHeight="1">
       <x:c r="A74" s="18" t="str">
-        <x:v>QA-AUD-03</x:v>
+        <x:v>QA-SES-29</x:v>
       </x:c>
       <x:c r="B74" s="18" t="str">
-        <x:v>Audio synthétique</x:v>
+        <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C74" s="18" t="str">
-        <x:v>settings, themes and effects never construct audio before explicit unlock</x:v>
+        <x:v>version one profiles migrate with safe bindings, quiet music and no invented progress</x:v>
       </x:c>
       <x:c r="D74" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42071,25 +42125,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F74" s="18" t="str">
-        <x:v>node tests/combat-audio.test.mjs</x:v>
+        <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G74" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H74" s="18" t="str">
-        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
+        <x:v>Vérification de parcours, entrées ou persistance</x:v>
       </x:c>
       <x:c r="I74" s="20" t="str"/>
     </x:row>
     <x:row r="75" ht="32" customHeight="1">
       <x:c r="A75" s="19" t="str">
-        <x:v>QA-AUD-04</x:v>
+        <x:v>QA-SES-30</x:v>
       </x:c>
       <x:c r="B75" s="19" t="str">
-        <x:v>Audio synthétique</x:v>
+        <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C75" s="19" t="str">
-        <x:v>concurrent unlock gestures share one context and one pending resume</x:v>
+        <x:v>profile exports preserve canonical progress, costumes and individually earned endings</x:v>
       </x:c>
       <x:c r="D75" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42098,25 +42152,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F75" s="19" t="str">
-        <x:v>node tests/combat-audio.test.mjs</x:v>
+        <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G75" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H75" s="19" t="str">
-        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
+        <x:v>Vérification de parcours, entrées ou persistance</x:v>
       </x:c>
       <x:c r="I75" s="20" t="str"/>
     </x:row>
     <x:row r="76" ht="32" customHeight="1">
       <x:c r="A76" s="18" t="str">
-        <x:v>QA-AUD-05</x:v>
+        <x:v>QA-SES-31</x:v>
       </x:c>
       <x:c r="B76" s="18" t="str">
-        <x:v>Audio synthétique</x:v>
+        <x:v>Session automatisée</x:v>
       </x:c>
       <x:c r="C76" s="18" t="str">
-        <x:v>a denied resume can be retried only through another unlock gesture</x:v>
+        <x:v>replays retain known costumes and reject unrelated variants while keeping 0.1 compatibility</x:v>
       </x:c>
       <x:c r="D76" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42125,25 +42179,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F76" s="18" t="str">
-        <x:v>node tests/combat-audio.test.mjs</x:v>
+        <x:v>node tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G76" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-session.test.mjs — 31/31 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-session.test.tap)</x:v>
       </x:c>
       <x:c r="H76" s="18" t="str">
-        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
+        <x:v>Vérification de parcours, entrées ou persistance</x:v>
       </x:c>
       <x:c r="I76" s="20" t="str"/>
     </x:row>
     <x:row r="77" ht="32" customHeight="1">
       <x:c r="A77" s="19" t="str">
-        <x:v>QA-AUD-06</x:v>
+        <x:v>QA-AUD-01</x:v>
       </x:c>
       <x:c r="B77" s="19" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C77" s="19" t="str">
-        <x:v>twelve themes and the light menu arrangement share a single bounded scheduler</x:v>
+        <x:v>every playable stage has a distinct frozen original arrangement</x:v>
       </x:c>
       <x:c r="D77" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42155,7 +42209,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G77" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H77" s="19" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42164,13 +42218,13 @@
     </x:row>
     <x:row r="78" ht="32" customHeight="1">
       <x:c r="A78" s="18" t="str">
-        <x:v>QA-AUD-07</x:v>
+        <x:v>QA-AUD-02</x:v>
       </x:c>
       <x:c r="B78" s="18" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C78" s="18" t="str">
-        <x:v>a delayed clock schedules only the next notes instead of a burst of missed music</x:v>
+        <x:v>missing or denied audio remains an optional no-op</x:v>
       </x:c>
       <x:c r="D78" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42182,7 +42236,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G78" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H78" s="18" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42191,13 +42245,13 @@
     </x:row>
     <x:row r="79" ht="32" customHeight="1">
       <x:c r="A79" s="19" t="str">
-        <x:v>QA-AUD-08</x:v>
+        <x:v>QA-AUD-03</x:v>
       </x:c>
       <x:c r="B79" s="19" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C79" s="19" t="str">
-        <x:v>effects and music honor independent mute and volume controls</x:v>
+        <x:v>settings, themes and effects never construct audio before explicit unlock</x:v>
       </x:c>
       <x:c r="D79" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42209,7 +42263,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G79" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H79" s="19" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42218,13 +42272,13 @@
     </x:row>
     <x:row r="80" ht="32" customHeight="1">
       <x:c r="A80" s="18" t="str">
-        <x:v>QA-AUD-09</x:v>
+        <x:v>QA-AUD-04</x:v>
       </x:c>
       <x:c r="B80" s="18" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C80" s="18" t="str">
-        <x:v>effect bursts stay bounded and ended voices disconnect their nodes</x:v>
+        <x:v>concurrent unlock gestures share one context and one pending resume</x:v>
       </x:c>
       <x:c r="D80" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42236,7 +42290,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G80" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H80" s="18" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42245,13 +42299,13 @@
     </x:row>
     <x:row r="81" ht="32" customHeight="1">
       <x:c r="A81" s="19" t="str">
-        <x:v>QA-AUD-10</x:v>
+        <x:v>QA-AUD-05</x:v>
       </x:c>
       <x:c r="B81" s="19" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C81" s="19" t="str">
-        <x:v>pause immediately clears scheduled voices and resumes without old effects</x:v>
+        <x:v>a denied resume can be retried only through another unlock gesture</x:v>
       </x:c>
       <x:c r="D81" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42263,7 +42317,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G81" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H81" s="19" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42272,13 +42326,13 @@
     </x:row>
     <x:row r="82" ht="32" customHeight="1">
       <x:c r="A82" s="18" t="str">
-        <x:v>QA-AUD-11</x:v>
+        <x:v>QA-AUD-06</x:v>
       </x:c>
       <x:c r="B82" s="18" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C82" s="18" t="str">
-        <x:v>an interrupted context stops its clock and waits for an explicit unlock</x:v>
+        <x:v>twelve themes and the light menu arrangement share a single bounded scheduler</x:v>
       </x:c>
       <x:c r="D82" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42290,7 +42344,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G82" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H82" s="18" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42299,13 +42353,13 @@
     </x:row>
     <x:row r="83" ht="32" customHeight="1">
       <x:c r="A83" s="19" t="str">
-        <x:v>QA-AUD-12</x:v>
+        <x:v>QA-AUD-07</x:v>
       </x:c>
       <x:c r="B83" s="19" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C83" s="19" t="str">
-        <x:v>destroy is idempotent and a late resume cannot resurrect audio resources</x:v>
+        <x:v>a delayed clock schedules only the next notes instead of a burst of missed music</x:v>
       </x:c>
       <x:c r="D83" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42317,7 +42371,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G83" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H83" s="19" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42326,13 +42380,13 @@
     </x:row>
     <x:row r="84" ht="32" customHeight="1">
       <x:c r="A84" s="18" t="str">
-        <x:v>QA-AUD-13</x:v>
+        <x:v>QA-AUD-08</x:v>
       </x:c>
       <x:c r="B84" s="18" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C84" s="18" t="str">
-        <x:v>node allocation failure does not leak or prevent a later valid effect</x:v>
+        <x:v>effects and music honor independent mute and volume controls</x:v>
       </x:c>
       <x:c r="D84" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42344,7 +42398,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G84" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H84" s="18" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42353,13 +42407,13 @@
     </x:row>
     <x:row r="85" ht="32" customHeight="1">
       <x:c r="A85" s="19" t="str">
-        <x:v>QA-AUD-14</x:v>
+        <x:v>QA-AUD-09</x:v>
       </x:c>
       <x:c r="B85" s="19" t="str">
         <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C85" s="19" t="str">
-        <x:v>legacy WebKit contexts and missing settings keep safe defaults</x:v>
+        <x:v>effect bursts stay bounded and ended voices disconnect their nodes</x:v>
       </x:c>
       <x:c r="D85" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42371,7 +42425,7 @@
         <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G85" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H85" s="19" t="str">
         <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
@@ -42380,13 +42434,13 @@
     </x:row>
     <x:row r="86" ht="32" customHeight="1">
       <x:c r="A86" s="18" t="str">
-        <x:v>QA-BIND-01</x:v>
+        <x:v>QA-AUD-10</x:v>
       </x:c>
       <x:c r="B86" s="18" t="str">
-        <x:v>Commandes personnalisables</x:v>
+        <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C86" s="18" t="str">
-        <x:v>all 24 player actions remain bound and independent after a JSON round trip</x:v>
+        <x:v>pause immediately clears scheduled voices and resumes without old effects</x:v>
       </x:c>
       <x:c r="D86" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42395,25 +42449,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F86" s="18" t="str">
-        <x:v>node tests/combat-bindings.test.mjs</x:v>
+        <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G86" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H86" s="18" t="str">
-        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
+        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
       </x:c>
       <x:c r="I86" s="20" t="str"/>
     </x:row>
     <x:row r="87" ht="32" customHeight="1">
       <x:c r="A87" s="19" t="str">
-        <x:v>QA-BIND-02</x:v>
+        <x:v>QA-AUD-11</x:v>
       </x:c>
       <x:c r="B87" s="19" t="str">
-        <x:v>Commandes personnalisables</x:v>
+        <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C87" s="19" t="str">
-        <x:v>reassignment rejects conflicts across players and alternative keys without changing the saved map</x:v>
+        <x:v>an interrupted context stops its clock and waits for an explicit unlock</x:v>
       </x:c>
       <x:c r="D87" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42422,25 +42476,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F87" s="19" t="str">
-        <x:v>node tests/combat-bindings.test.mjs</x:v>
+        <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G87" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H87" s="19" t="str">
-        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
+        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
       </x:c>
       <x:c r="I87" s="20" t="str"/>
     </x:row>
     <x:row r="88" ht="32" customHeight="1">
       <x:c r="A88" s="18" t="str">
-        <x:v>QA-BIND-03</x:v>
+        <x:v>QA-AUD-12</x:v>
       </x:c>
       <x:c r="B88" s="18" t="str">
-        <x:v>Commandes personnalisables</x:v>
+        <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C88" s="18" t="str">
-        <x:v>reserved navigation and browser keys cannot replace gameplay bindings</x:v>
+        <x:v>destroy is idempotent and a late resume cannot resurrect audio resources</x:v>
       </x:c>
       <x:c r="D88" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42449,25 +42503,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F88" s="18" t="str">
-        <x:v>node tests/combat-bindings.test.mjs</x:v>
+        <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G88" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H88" s="18" t="str">
-        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
+        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
       </x:c>
       <x:c r="I88" s="20" t="str"/>
     </x:row>
     <x:row r="89" ht="32" customHeight="1">
       <x:c r="A89" s="19" t="str">
-        <x:v>QA-BIND-04</x:v>
+        <x:v>QA-AUD-13</x:v>
       </x:c>
       <x:c r="B89" s="19" t="str">
-        <x:v>Commandes personnalisables</x:v>
+        <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C89" s="19" t="str">
-        <x:v>corrupt imported maps restore reachable defaults and do not share mutable arrays</x:v>
+        <x:v>node allocation failure does not leak or prevent a later valid effect</x:v>
       </x:c>
       <x:c r="D89" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42476,25 +42530,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F89" s="19" t="str">
-        <x:v>node tests/combat-bindings.test.mjs</x:v>
+        <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G89" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H89" s="19" t="str">
-        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
+        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
       </x:c>
       <x:c r="I89" s="20" t="str"/>
     </x:row>
     <x:row r="90" ht="32" customHeight="1">
       <x:c r="A90" s="18" t="str">
-        <x:v>QA-BIND-05</x:v>
+        <x:v>QA-AUD-14</x:v>
       </x:c>
       <x:c r="B90" s="18" t="str">
-        <x:v>Commandes personnalisables</x:v>
+        <x:v>Audio synthétique</x:v>
       </x:c>
       <x:c r="C90" s="18" t="str">
-        <x:v>secondary bindings can be added and removed while a primary action stays reachable</x:v>
+        <x:v>legacy WebKit contexts and missing settings keep safe defaults</x:v>
       </x:c>
       <x:c r="D90" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42503,25 +42557,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F90" s="18" t="str">
-        <x:v>node tests/combat-bindings.test.mjs</x:v>
+        <x:v>node tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G90" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-audio.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-audio.test.tap)</x:v>
       </x:c>
       <x:c r="H90" s="18" t="str">
-        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
+        <x:v>Thèmes et effets définis ; cycle de vie du son vérifié</x:v>
       </x:c>
       <x:c r="I90" s="20" t="str"/>
     </x:row>
     <x:row r="91" ht="32" customHeight="1">
       <x:c r="A91" s="19" t="str">
-        <x:v>QA-BIND-06</x:v>
+        <x:v>QA-BIND-01</x:v>
       </x:c>
       <x:c r="B91" s="19" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C91" s="19" t="str">
-        <x:v>physical positions receive correct AZERTY and QWERTY labels for both players</x:v>
+        <x:v>all 24 player actions remain bound and independent after a JSON round trip</x:v>
       </x:c>
       <x:c r="D91" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42533,7 +42587,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G91" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H91" s="19" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42542,13 +42596,13 @@
     </x:row>
     <x:row r="92" ht="32" customHeight="1">
       <x:c r="A92" s="18" t="str">
-        <x:v>QA-BIND-07</x:v>
+        <x:v>QA-BIND-02</x:v>
       </x:c>
       <x:c r="B92" s="18" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C92" s="18" t="str">
-        <x:v>a remapped short press activates the real combat engine exactly once and releases the old key</x:v>
+        <x:v>reassignment rejects conflicts across players and alternative keys without changing the saved map</x:v>
       </x:c>
       <x:c r="D92" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42560,7 +42614,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G92" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H92" s="18" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42569,13 +42623,13 @@
     </x:row>
     <x:row r="93" ht="32" customHeight="1">
       <x:c r="A93" s="19" t="str">
-        <x:v>QA-BIND-08</x:v>
+        <x:v>QA-BIND-03</x:v>
       </x:c>
       <x:c r="B93" s="19" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C93" s="19" t="str">
-        <x:v>custom local mappings stay independent and rebinding clears a held direction</x:v>
+        <x:v>reserved navigation and browser keys cannot replace gameplay bindings</x:v>
       </x:c>
       <x:c r="D93" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42587,7 +42641,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G93" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H93" s="19" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42596,13 +42650,13 @@
     </x:row>
     <x:row r="94" ht="32" customHeight="1">
       <x:c r="A94" s="18" t="str">
-        <x:v>QA-BIND-09</x:v>
+        <x:v>QA-BIND-04</x:v>
       </x:c>
       <x:c r="B94" s="18" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C94" s="18" t="str">
-        <x:v>editing and browser shortcuts do not queue custom attacks while pause/help remain available</x:v>
+        <x:v>corrupt imported maps restore reachable defaults and do not share mutable arrays</x:v>
       </x:c>
       <x:c r="D94" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42614,7 +42668,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G94" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H94" s="18" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42623,13 +42677,13 @@
     </x:row>
     <x:row r="95" ht="32" customHeight="1">
       <x:c r="A95" s="19" t="str">
-        <x:v>QA-BIND-10</x:v>
+        <x:v>QA-BIND-05</x:v>
       </x:c>
       <x:c r="B95" s="19" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C95" s="19" t="str">
-        <x:v>gamepad menus use a dead zone, bounded repeats and single select/back edges</x:v>
+        <x:v>secondary bindings can be added and removed while a primary action stays reachable</x:v>
       </x:c>
       <x:c r="D95" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42641,7 +42695,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G95" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H95" s="19" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42650,13 +42704,13 @@
     </x:row>
     <x:row r="96" ht="32" customHeight="1">
       <x:c r="A96" s="18" t="str">
-        <x:v>QA-BIND-11</x:v>
+        <x:v>QA-BIND-06</x:v>
       </x:c>
       <x:c r="B96" s="18" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C96" s="18" t="str">
-        <x:v>menu capture and focused text fields suppress gamepad actions until controls return to neutral</x:v>
+        <x:v>physical positions receive correct AZERTY and QWERTY labels for both players</x:v>
       </x:c>
       <x:c r="D96" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42668,7 +42722,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G96" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H96" s="18" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42677,13 +42731,13 @@
     </x:row>
     <x:row r="97" ht="32" customHeight="1">
       <x:c r="A97" s="19" t="str">
-        <x:v>QA-BIND-12</x:v>
+        <x:v>QA-BIND-07</x:v>
       </x:c>
       <x:c r="B97" s="19" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C97" s="19" t="str">
-        <x:v>selects, sliders, checkboxes and radios retain gamepad navigation without native clicks</x:v>
+        <x:v>a remapped short press activates the real combat engine exactly once and releases the old key</x:v>
       </x:c>
       <x:c r="D97" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42695,7 +42749,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G97" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H97" s="19" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42704,13 +42758,13 @@
     </x:row>
     <x:row r="98" ht="32" customHeight="1">
       <x:c r="A98" s="18" t="str">
-        <x:v>QA-BIND-13</x:v>
+        <x:v>QA-BIND-08</x:v>
       </x:c>
       <x:c r="B98" s="18" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C98" s="18" t="str">
-        <x:v>a held gamepad button cannot leak from combat into menus or from Select into a new match</x:v>
+        <x:v>custom local mappings stay independent and rebinding clears a held direction</x:v>
       </x:c>
       <x:c r="D98" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42722,7 +42776,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G98" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H98" s="18" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42731,13 +42785,13 @@
     </x:row>
     <x:row r="99" ht="32" customHeight="1">
       <x:c r="A99" s="19" t="str">
-        <x:v>QA-BIND-14</x:v>
+        <x:v>QA-BIND-09</x:v>
       </x:c>
       <x:c r="B99" s="19" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C99" s="19" t="str">
-        <x:v>an optional menu poll during combat does not consume its jump or attack edges</x:v>
+        <x:v>editing and browser shortcuts do not queue custom attacks while pause/help remain available</x:v>
       </x:c>
       <x:c r="D99" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42749,7 +42803,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G99" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H99" s="19" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42758,13 +42812,13 @@
     </x:row>
     <x:row r="100" ht="32" customHeight="1">
       <x:c r="A100" s="18" t="str">
-        <x:v>QA-BIND-15</x:v>
+        <x:v>QA-BIND-10</x:v>
       </x:c>
       <x:c r="B100" s="18" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C100" s="18" t="str">
-        <x:v>disconnecting player one keeps player two on its original controls</x:v>
+        <x:v>gamepad menus use a dead zone, bounded repeats and single select/back edges</x:v>
       </x:c>
       <x:c r="D100" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42776,7 +42830,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G100" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H100" s="18" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42785,13 +42839,13 @@
     </x:row>
     <x:row r="101" ht="32" customHeight="1">
       <x:c r="A101" s="19" t="str">
-        <x:v>QA-BIND-16</x:v>
+        <x:v>QA-BIND-11</x:v>
       </x:c>
       <x:c r="B101" s="19" t="str">
         <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C101" s="19" t="str">
-        <x:v>denied Gamepad access leaves keyboard play available</x:v>
+        <x:v>menu capture and focused text fields suppress gamepad actions until controls return to neutral</x:v>
       </x:c>
       <x:c r="D101" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42803,7 +42857,7 @@
         <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G101" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026, après correction du focus manette)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H101" s="19" t="str">
         <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
@@ -42812,13 +42866,13 @@
     </x:row>
     <x:row r="102" ht="32" customHeight="1">
       <x:c r="A102" s="18" t="str">
-        <x:v>QA-CAT-01</x:v>
+        <x:v>QA-BIND-12</x:v>
       </x:c>
       <x:c r="B102" s="18" t="str">
-        <x:v>Classification du catalogue</x:v>
+        <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C102" s="18" t="str">
-        <x:v>classification preserves all 179 source records and their historical provenance</x:v>
+        <x:v>selects, sliders, checkboxes and radios retain gamepad navigation without native clicks</x:v>
       </x:c>
       <x:c r="D102" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42827,25 +42881,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F102" s="18" t="str">
-        <x:v>node tests/combat-catalog.test.mjs</x:v>
+        <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G102" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H102" s="18" t="str">
-        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
+        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
       </x:c>
       <x:c r="I102" s="20" t="str"/>
     </x:row>
     <x:row r="103" ht="32" customHeight="1">
       <x:c r="A103" s="19" t="str">
-        <x:v>QA-CAT-02</x:v>
+        <x:v>QA-BIND-13</x:v>
       </x:c>
       <x:c r="B103" s="19" t="str">
-        <x:v>Classification du catalogue</x:v>
+        <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C103" s="19" t="str">
-        <x:v>every current archive entry has exactly one reviewed classification with no stale declarations</x:v>
+        <x:v>a held gamepad button cannot leak from combat into menus or from Select into a new match</x:v>
       </x:c>
       <x:c r="D103" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42854,25 +42908,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F103" s="19" t="str">
-        <x:v>node tests/combat-catalog.test.mjs</x:v>
+        <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G103" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H103" s="19" t="str">
-        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
+        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
       </x:c>
       <x:c r="I103" s="20" t="str"/>
     </x:row>
     <x:row r="104" ht="32" customHeight="1">
       <x:c r="A104" s="18" t="str">
-        <x:v>QA-CAT-03</x:v>
+        <x:v>QA-BIND-14</x:v>
       </x:c>
       <x:c r="B104" s="18" t="str">
-        <x:v>Classification du catalogue</x:v>
+        <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C104" s="18" t="str">
-        <x:v>every playable identity retains its own kit including the distinct Kaufmo abstraction</x:v>
+        <x:v>an optional menu poll during combat does not consume its jump or attack edges</x:v>
       </x:c>
       <x:c r="D104" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42881,25 +42935,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F104" s="18" t="str">
-        <x:v>node tests/combat-catalog.test.mjs</x:v>
+        <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G104" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H104" s="18" t="str">
-        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
+        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
       </x:c>
       <x:c r="I104" s="20" t="str"/>
     </x:row>
     <x:row r="105" ht="32" customHeight="1">
       <x:c r="A105" s="19" t="str">
-        <x:v>QA-CAT-04</x:v>
+        <x:v>QA-BIND-15</x:v>
       </x:c>
       <x:c r="B105" s="19" t="str">
-        <x:v>Classification du catalogue</x:v>
+        <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C105" s="19" t="str">
-        <x:v>names shared with relatives, rivals, props and effects never grant a costume kit</x:v>
+        <x:v>disconnecting player one keeps player two on its original controls</x:v>
       </x:c>
       <x:c r="D105" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42908,25 +42962,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F105" s="19" t="str">
-        <x:v>node tests/combat-catalog.test.mjs</x:v>
+        <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G105" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H105" s="19" t="str">
-        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
+        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
       </x:c>
       <x:c r="I105" s="20" t="str"/>
     </x:row>
     <x:row r="106" ht="32" customHeight="1">
       <x:c r="A106" s="18" t="str">
-        <x:v>QA-CAT-05</x:v>
+        <x:v>QA-BIND-16</x:v>
       </x:c>
       <x:c r="B106" s="18" t="str">
-        <x:v>Classification du catalogue</x:v>
+        <x:v>Commandes personnalisables</x:v>
       </x:c>
       <x:c r="C106" s="18" t="str">
-        <x:v>reviewed outfits and visual states reuse the same existing fighter without adding a kit</x:v>
+        <x:v>denied Gamepad access leaves keyboard play available</x:v>
       </x:c>
       <x:c r="D106" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42935,25 +42989,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F106" s="18" t="str">
-        <x:v>node tests/combat-catalog.test.mjs</x:v>
+        <x:v>node tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G106" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-bindings.test.mjs — 16/16 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-bindings.test.tap)</x:v>
       </x:c>
       <x:c r="H106" s="18" t="str">
-        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
+        <x:v>Liaisons indépendantes, conflits rejetés et entrées cohérentes après remappage</x:v>
       </x:c>
       <x:c r="I106" s="20" t="str"/>
     </x:row>
     <x:row r="107" ht="32" customHeight="1">
       <x:c r="A107" s="19" t="str">
-        <x:v>QA-CAT-06</x:v>
+        <x:v>QA-CAT-01</x:v>
       </x:c>
       <x:c r="B107" s="19" t="str">
         <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C107" s="19" t="str">
-        <x:v>future and prototype-like IDs fail closed even when they contain a fighter name</x:v>
+        <x:v>classification preserves all 179 source records and their historical provenance</x:v>
       </x:c>
       <x:c r="D107" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -42965,7 +43019,7 @@
         <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G107" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H107" s="19" t="str">
         <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
@@ -42974,13 +43028,13 @@
     </x:row>
     <x:row r="108" ht="32" customHeight="1">
       <x:c r="A108" s="18" t="str">
-        <x:v>QA-CAT-07</x:v>
+        <x:v>QA-CAT-02</x:v>
       </x:c>
       <x:c r="B108" s="18" t="str">
         <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C108" s="18" t="str">
-        <x:v>every classified appearance still points at a bounded source atlas cell</x:v>
+        <x:v>every current archive entry has exactly one reviewed classification with no stale declarations</x:v>
       </x:c>
       <x:c r="D108" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -42992,7 +43046,7 @@
         <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G108" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H108" s="18" t="str">
         <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
@@ -43001,13 +43055,13 @@
     </x:row>
     <x:row r="109" ht="32" customHeight="1">
       <x:c r="A109" s="19" t="str">
-        <x:v>QA-PROG-01</x:v>
+        <x:v>QA-CAT-03</x:v>
       </x:c>
       <x:c r="B109" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C109" s="19" t="str">
-        <x:v>the complete roster has fourteen individually authored four-scene routes with playable references</x:v>
+        <x:v>every playable identity retains its own kit including the distinct Kaufmo abstraction</x:v>
       </x:c>
       <x:c r="D109" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43016,25 +43070,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F109" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G109" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H109" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
       </x:c>
       <x:c r="I109" s="20" t="str"/>
     </x:row>
     <x:row r="110" ht="32" customHeight="1">
       <x:c r="A110" s="18" t="str">
-        <x:v>QA-PROG-02</x:v>
+        <x:v>QA-CAT-04</x:v>
       </x:c>
       <x:c r="B110" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C110" s="18" t="str">
-        <x:v>story helpers reject absent/prototype IDs and protect shared authored text</x:v>
+        <x:v>names shared with relatives, rivals, props and effects never grant a costume kit</x:v>
       </x:c>
       <x:c r="D110" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43043,25 +43097,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F110" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G110" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H110" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
       </x:c>
       <x:c r="I110" s="20" t="str"/>
     </x:row>
     <x:row r="111" ht="32" customHeight="1">
       <x:c r="A111" s="19" t="str">
-        <x:v>QA-PROG-03</x:v>
+        <x:v>QA-CAT-05</x:v>
       </x:c>
       <x:c r="B111" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C111" s="19" t="str">
-        <x:v>all fourteen story routes finish through four actual player results and preserve their authored stage order</x:v>
+        <x:v>reviewed outfits and visual states reuse the same existing fighter without adding a kit</x:v>
       </x:c>
       <x:c r="D111" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43070,25 +43124,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F111" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G111" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H111" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
       </x:c>
       <x:c r="I111" s="20" t="str"/>
     </x:row>
     <x:row r="112" ht="32" customHeight="1">
       <x:c r="A112" s="18" t="str">
-        <x:v>QA-PROG-04</x:v>
+        <x:v>QA-CAT-06</x:v>
       </x:c>
       <x:c r="B112" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C112" s="18" t="str">
-        <x:v>arcade, boss rush and survival retain their six, four and ten encounter objectives</x:v>
+        <x:v>future and prototype-like IDs fail closed even when they contain a fighter name</x:v>
       </x:c>
       <x:c r="D112" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43097,25 +43151,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F112" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G112" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H112" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
       </x:c>
       <x:c r="I112" s="20" t="str"/>
     </x:row>
     <x:row r="113" ht="32" customHeight="1">
       <x:c r="A113" s="19" t="str">
-        <x:v>QA-PROG-05</x:v>
+        <x:v>QA-CAT-07</x:v>
       </x:c>
       <x:c r="B113" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Classification du catalogue</x:v>
       </x:c>
       <x:c r="C113" s="19" t="str">
-        <x:v>survival carries bounded integer health, adds the stated recovery and preserves the next encounter checkpoint</x:v>
+        <x:v>every classified appearance still points at a bounded source atlas cell</x:v>
       </x:c>
       <x:c r="D113" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43124,25 +43178,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F113" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-catalog.test.mjs</x:v>
       </x:c>
       <x:c r="G113" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-catalog.test.mjs — 7/7 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-catalog.test.tap)</x:v>
       </x:c>
       <x:c r="H113" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>179 archives préservées ; identités, costumes et exclusions explicitement validés</x:v>
       </x:c>
       <x:c r="I113" s="20" t="str"/>
     </x:row>
     <x:row r="114" ht="32" customHeight="1">
       <x:c r="A114" s="18" t="str">
-        <x:v>QA-PROG-06</x:v>
+        <x:v>QA-OFFLINE-01</x:v>
       </x:c>
       <x:c r="B114" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C114" s="18" t="str">
-        <x:v>seeded draws repeat exactly, distinguish seeds and accept unsigned seed boundaries</x:v>
+        <x:v>unsupported or insecure contexts do not start offline initialization</x:v>
       </x:c>
       <x:c r="D114" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43151,25 +43205,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F114" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G114" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H114" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I114" s="20" t="str"/>
     </x:row>
     <x:row r="115" ht="32" customHeight="1">
       <x:c r="A115" s="19" t="str">
-        <x:v>QA-PROG-07</x:v>
+        <x:v>QA-OFFLINE-02</x:v>
       </x:c>
       <x:c r="B115" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C115" s="19" t="str">
-        <x:v>tournaments draw eight unique participants across every player slot, regardless of selected artist</x:v>
+        <x:v>concurrent init calls share one attempt and use the active worker directly</x:v>
       </x:c>
       <x:c r="D115" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43178,25 +43232,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F115" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G115" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H115" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I115" s="20" t="str"/>
     </x:row>
     <x:row r="116" ht="32" customHeight="1">
       <x:c r="A116" s="18" t="str">
-        <x:v>QA-PROG-08</x:v>
+        <x:v>QA-OFFLINE-03</x:v>
       </x:c>
       <x:c r="B116" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C116" s="18" t="str">
-        <x:v>a tournament requires three real victories and propagates winners through all seven matches</x:v>
+        <x:v>a first installation becomes ready only after its worker is activated</x:v>
       </x:c>
       <x:c r="D116" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43205,25 +43259,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F116" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G116" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H116" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I116" s="20" t="str"/>
     </x:row>
     <x:row r="117" ht="32" customHeight="1">
       <x:c r="A117" s="19" t="str">
-        <x:v>QA-PROG-09</x:v>
+        <x:v>QA-OFFLINE-04</x:v>
       </x:c>
       <x:c r="B117" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C117" s="19" t="str">
-        <x:v>a loss in any tournament round eliminates the player and labels every remaining CPU result as simulated</x:v>
+        <x:v>an abandoned first installation reports a retryable error and removes its listeners</x:v>
       </x:c>
       <x:c r="D117" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43232,25 +43286,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F117" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G117" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H117" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I117" s="20" t="str"/>
     </x:row>
     <x:row r="118" ht="32" customHeight="1">
       <x:c r="A118" s="18" t="str">
-        <x:v>QA-PROG-10</x:v>
+        <x:v>QA-OFFLINE-05</x:v>
       </x:c>
       <x:c r="B118" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C118" s="18" t="str">
-        <x:v>CPU bracket simulations and future opponents are deterministic across save/reload at every round</x:v>
+        <x:v>a registration with a redundant worker already present fails without waiting</x:v>
       </x:c>
       <x:c r="D118" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43259,25 +43313,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F118" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G118" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H118" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I118" s="20" t="str"/>
     </x:row>
     <x:row r="119" ht="32" customHeight="1">
       <x:c r="A119" s="19" t="str">
-        <x:v>QA-PROG-11</x:v>
+        <x:v>QA-OFFLINE-06</x:v>
       </x:c>
       <x:c r="B119" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C119" s="19" t="str">
-        <x:v>checkpoints save and resume every programme with the same costume, rules, encounter seed and starting health</x:v>
+        <x:v>an initially empty registration waits for updatefound and can activate normally</x:v>
       </x:c>
       <x:c r="D119" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43286,25 +43340,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F119" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G119" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H119" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I119" s="20" t="str"/>
     </x:row>
     <x:row r="120" ht="32" customHeight="1">
       <x:c r="A120" s="18" t="str">
-        <x:v>QA-PROG-12</x:v>
+        <x:v>QA-OFFLINE-07</x:v>
       </x:c>
       <x:c r="B120" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C120" s="18" t="str">
-        <x:v>resumed survival checkpoints restart the real CQC engine reproducibly, with carried health</x:v>
+        <x:v>both synchronous registration denial and promise rejection can be retried</x:v>
       </x:c>
       <x:c r="D120" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43313,25 +43367,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F120" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G120" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H120" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I120" s="20" t="str"/>
     </x:row>
     <x:row r="121" ht="32" customHeight="1">
       <x:c r="A121" s="19" t="str">
-        <x:v>QA-PROG-13</x:v>
+        <x:v>QA-OFFLINE-08</x:v>
       </x:c>
       <x:c r="B121" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C121" s="19" t="str">
-        <x:v>retry preserves prior story/arcade/boss victories while survival and tournament begin a new attempt</x:v>
+        <x:v>a stalled installation times out and a late activation cannot change the failed state</x:v>
       </x:c>
       <x:c r="D121" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43340,25 +43394,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F121" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G121" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H121" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I121" s="20" t="str"/>
     </x:row>
     <x:row r="122" ht="32" customHeight="1">
       <x:c r="A122" s="18" t="str">
-        <x:v>QA-PROG-14</x:v>
+        <x:v>QA-OFFLINE-09</x:v>
       </x:c>
       <x:c r="B122" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C122" s="18" t="str">
-        <x:v>untrusted import rejects malformed identity, rules, bounds, stage/opponent references and status</x:v>
+        <x:v>a late register result after timeout cannot overwrite a successful retry</x:v>
       </x:c>
       <x:c r="D122" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43367,25 +43421,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F122" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G122" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H122" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I122" s="20" t="str"/>
     </x:row>
     <x:row r="123" ht="32" customHeight="1">
       <x:c r="A123" s="19" t="str">
-        <x:v>QA-PROG-15</x:v>
+        <x:v>QA-OFFLINE-10</x:v>
       </x:c>
       <x:c r="B123" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C123" s="19" t="str">
-        <x:v>import cannot introduce impossible, fractional or additional results beyond a defeat or programme completion</x:v>
+        <x:v>the initialization deadline also closes a silent status message channel</x:v>
       </x:c>
       <x:c r="D123" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43394,25 +43448,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F123" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G123" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H123" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I123" s="20" t="str"/>
     </x:row>
     <x:row r="124" ht="32" customHeight="1">
       <x:c r="A124" s="18" t="str">
-        <x:v>QA-PROG-16</x:v>
+        <x:v>QA-OFFLINE-11</x:v>
       </x:c>
       <x:c r="B124" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C124" s="18" t="str">
-        <x:v>tournament import verifies participants, round ancestry, CPU results, champion and real player outcome provenance</x:v>
+        <x:v>status failures close ports and clear busy before an explicit retry</x:v>
       </x:c>
       <x:c r="D124" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43421,25 +43475,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F124" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G124" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H124" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I124" s="20" t="str"/>
     </x:row>
     <x:row r="125" ht="32" customHeight="1">
       <x:c r="A125" s="19" t="str">
-        <x:v>QA-PROG-17</x:v>
+        <x:v>QA-OFFLINE-12</x:v>
       </x:c>
       <x:c r="B125" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C125" s="19" t="str">
-        <x:v>normalized imports discard unknown fields without sharing arrays or polluting object prototypes</x:v>
+        <x:v>a failed replacement worker leaves the existing active worker ready</x:v>
       </x:c>
       <x:c r="D125" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43448,25 +43502,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F125" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G125" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H125" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I125" s="20" t="str"/>
     </x:row>
     <x:row r="126" ht="32" customHeight="1">
       <x:c r="A126" s="18" t="str">
-        <x:v>QA-PROG-18</x:v>
+        <x:v>QA-OFFLINE-13</x:v>
       </x:c>
       <x:c r="B126" s="18" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C126" s="18" t="str">
-        <x:v>program construction rejects invalid catalogues, unsupported modes and costumes belonging to another fighter</x:v>
+        <x:v>future updates are observed once and are never activated automatically</x:v>
       </x:c>
       <x:c r="D126" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43475,25 +43529,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F126" s="18" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G126" s="18" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H126" s="18" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I126" s="20" t="str"/>
     </x:row>
     <x:row r="127" ht="32" customHeight="1">
       <x:c r="A127" s="19" t="str">
-        <x:v>QA-PROG-19</x:v>
+        <x:v>QA-OFFLINE-14</x:v>
       </x:c>
       <x:c r="B127" s="19" t="str">
-        <x:v>Programmes et reprise</x:v>
+        <x:v>Installation web</x:v>
       </x:c>
       <x:c r="C127" s="19" t="str">
-        <x:v>missing, inaccessible, oversized or corrupt storage fails safely without resuming bad state</x:v>
+        <x:v>init during an art download does not clear its busy state or launch another registration</x:v>
       </x:c>
       <x:c r="D127" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43502,25 +43556,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F127" s="19" t="str">
-        <x:v>node tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-offline.test.mjs</x:v>
       </x:c>
       <x:c r="G127" s="19" t="str">
-        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026)</x:v>
+        <x:v>node --test-reporter=tap tests/combat-offline.test.mjs — 14/14 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-offline.test.tap)</x:v>
       </x:c>
       <x:c r="H127" s="19" t="str">
-        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
+        <x:v>Échecs explicites, nouvelle tentative, délais bornés et ressources libérées</x:v>
       </x:c>
       <x:c r="I127" s="20" t="str"/>
     </x:row>
     <x:row r="128" ht="32" customHeight="1">
       <x:c r="A128" s="18" t="str">
-        <x:v>QA-boot</x:v>
+        <x:v>QA-PROG-01</x:v>
       </x:c>
       <x:c r="B128" s="18" t="str">
-        <x:v>Intégration</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C128" s="18" t="str">
-        <x:v>Démarrer CainOS et ouvrir le combat</x:v>
+        <x:v>the complete roster has fourteen individually authored four-scene routes with playable references</x:v>
       </x:c>
       <x:c r="D128" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43529,25 +43583,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F128" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G128" s="18" t="str">
-        <x:v>Calibration existante réellement jouée, démarrage du bureau, lancement de Combat par double-clic. L’interface autonome expose neuf modes et le même moteur est chargé dans la fenêtre CainOS.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H128" s="18" t="str">
-        <x:v>Le bureau et les applications existantes restent utilisables.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I128" s="20" t="str"/>
     </x:row>
     <x:row r="129" ht="32" customHeight="1">
       <x:c r="A129" s="19" t="str">
-        <x:v>QA-standalone</x:v>
+        <x:v>QA-PROG-02</x:v>
       </x:c>
       <x:c r="B129" s="19" t="str">
-        <x:v>Intégration</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C129" s="19" t="str">
-        <x:v>Ouvrir le standalone sans CainOS</x:v>
+        <x:v>story helpers reject absent/prototype IDs and protect shared authored text</x:v>
       </x:c>
       <x:c r="D129" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43556,158 +43610,160 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F129" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs / tests/combat-offline-browser.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G129" s="19" t="str">
-        <x:v>Le build isolé charge 26 ressources locales sans /app.js CainOS. Préparation complète de 42 planches, puis rechargement hors ligne et combat sur une autre arène également réussis.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H129" s="19" t="str">
-        <x:v>Le menu et le combat se chargent directement.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I129" s="20" t="str"/>
     </x:row>
     <x:row r="130" ht="32" customHeight="1">
       <x:c r="A130" s="18" t="str">
-        <x:v>QA-pause-window</x:v>
+        <x:v>QA-PROG-03</x:v>
       </x:c>
       <x:c r="B130" s="18" t="str">
-        <x:v>Intégration</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C130" s="18" t="str">
-        <x:v>Réduire et fermer la fenêtre Combat</x:v>
+        <x:v>all fourteen story routes finish through four actual player results and preserve their authored stage order</x:v>
       </x:c>
       <x:c r="D130" s="18" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E130" s="18" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F130" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs / tests/combat-offline-browser.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G130" s="18" t="str">
-        <x:v>Réduction de la fenêtre : frame figée et pause confirmées ; pause du jeu : voix WebAudio libérées. La fermeture de fenêtre par la croix reste un parcours à tester séparément.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H130" s="18" t="str">
-        <x:v>Le combat et le son se mettent en pause.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I130" s="20" t="str"/>
     </x:row>
     <x:row r="131" ht="32" customHeight="1">
       <x:c r="A131" s="19" t="str">
-        <x:v>QA-reopen</x:v>
+        <x:v>QA-PROG-04</x:v>
       </x:c>
       <x:c r="B131" s="19" t="str">
-        <x:v>Intégration</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C131" s="19" t="str">
-        <x:v>Rouvrir la fenêtre Combat</x:v>
+        <x:v>arcade, boss rush and survival retain their six, four and ten encounter objectives</x:v>
       </x:c>
       <x:c r="D131" s="19" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E131" s="19" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F131" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G131" s="19" t="str">
-        <x:v>Réouverture après réduction : bouton Reprendre présent. Le parcours fermeture par la croix puis réouvertures répétées n’est pas revendiqué.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H131" s="19" t="str">
-        <x:v>Reprise contrôlée, aucune boucle doublée.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I131" s="20" t="str"/>
     </x:row>
     <x:row r="132" ht="32" customHeight="1">
       <x:c r="A132" s="18" t="str">
-        <x:v>QA-roster</x:v>
+        <x:v>QA-PROG-05</x:v>
       </x:c>
       <x:c r="B132" s="18" t="str">
-        <x:v>Présentation</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C132" s="18" t="str">
-        <x:v>Choisir chacun des 14 combattants</x:v>
+        <x:v>survival carries bounded integer health, adds the stated recovery and preserves the next encounter checkpoint</x:v>
       </x:c>
       <x:c r="D132" s="18" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E132" s="18" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F132" s="18" t="str">
-        <x:v>Tests de données, moteur, préchargement et sélection navigateur</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G132" s="18" t="str">
-        <x:v>14 combattants présents et préchargés ; 140 techniques activées. La sélection manuelle de chaque costume reste distincte.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H132" s="18" t="str">
-        <x:v>Le nom, le sprite et le kit correspondent.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I132" s="20" t="str"/>
     </x:row>
-    <x:row r="133" ht="29" customHeight="1">
+    <x:row r="133" ht="32" customHeight="1">
       <x:c r="A133" s="19" t="str">
-        <x:v>QA-costumes</x:v>
+        <x:v>QA-PROG-06</x:v>
       </x:c>
       <x:c r="B133" s="19" t="str">
-        <x:v>Présentation</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C133" s="19" t="str">
-        <x:v>Vérifier les 51 variantes</x:v>
+        <x:v>seeded draws repeat exactly, distinguish seeds and accept unsigned seed boundaries</x:v>
       </x:c>
       <x:c r="D133" s="19" t="str">
-        <x:v>Non exécuté</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E133" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F133" s="19" t="str">
-        <x:v>Parcours navigateur ou matériel réel</x:v>
-      </x:c>
-      <x:c r="G133" s="19" t="str"/>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
+      </x:c>
+      <x:c r="G133" s="19" t="str">
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
+      </x:c>
       <x:c r="H133" s="19" t="str">
-        <x:v>Silhouette complète, pas de bordure ni de recadrage incorrect.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I133" s="20" t="str"/>
     </x:row>
     <x:row r="134" ht="32" customHeight="1">
       <x:c r="A134" s="18" t="str">
-        <x:v>QA-stages</x:v>
+        <x:v>QA-PROG-07</x:v>
       </x:c>
       <x:c r="B134" s="18" t="str">
-        <x:v>Présentation</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C134" s="18" t="str">
-        <x:v>Vérifier les 12 arènes</x:v>
+        <x:v>tournaments draw eight unique participants across every player slot, regardless of selected artist</x:v>
       </x:c>
       <x:c r="D134" s="18" t="str">
         <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E134" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F134" s="18" t="str">
-        <x:v>Préchargement du renderer et 12 captures Canvas</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G134" s="18" t="str">
-        <x:v>Douze thèmes rendus. Préchargement des 14 combattants sans erreur ; les décors restent des compositions procédurales.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H134" s="18" t="str">
-        <x:v>Décors distincts, aucun combattant masqué.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I134" s="20" t="str"/>
     </x:row>
     <x:row r="135" ht="32" customHeight="1">
       <x:c r="A135" s="19" t="str">
-        <x:v>QA-local</x:v>
+        <x:v>QA-PROG-08</x:v>
       </x:c>
       <x:c r="B135" s="19" t="str">
-        <x:v>Commandes</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C135" s="19" t="str">
-        <x:v>Jouer un duel local complet</x:v>
+        <x:v>a tournament requires three real victories and propagates winners through all seven matches</x:v>
       </x:c>
       <x:c r="D135" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43716,79 +43772,79 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F135" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G135" s="19" t="str">
-        <x:v>Duel local réellement terminé en 2 282 frames, résultat sauvegardé et replay de 611 séquences d’entrées. Les commandes de J2 sont indépendantes.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H135" s="19" t="str">
-        <x:v>Deux joueurs et résultat sans conflit d’entrées.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I135" s="20" t="str"/>
     </x:row>
-    <x:row r="136" ht="45" customHeight="1">
+    <x:row r="136" ht="32" customHeight="1">
       <x:c r="A136" s="18" t="str">
-        <x:v>QA-arcade</x:v>
+        <x:v>QA-PROG-09</x:v>
       </x:c>
       <x:c r="B136" s="18" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C136" s="18" t="str">
-        <x:v>Terminer un arcade de six matchs</x:v>
+        <x:v>a loss in any tournament round eliminates the player and labels every remaining CPU result as simulated</x:v>
       </x:c>
       <x:c r="D136" s="18" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E136" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F136" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G136" s="18" t="str">
-        <x:v>Première victoire réelle contre Kaufmo abstrait puis passage à Gangle, acte 2/6. La longueur et la reprise sont couvertes par contrat ; le parcours complet et sa médaille ne sont pas revendiqués dans le navigateur.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H136" s="18" t="str">
-        <x:v>Progression et fin de parcours fonctionnelles.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I136" s="20" t="str"/>
     </x:row>
     <x:row r="137" ht="32" customHeight="1">
       <x:c r="A137" s="19" t="str">
-        <x:v>QA-boss</x:v>
+        <x:v>QA-PROG-10</x:v>
       </x:c>
       <x:c r="B137" s="19" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C137" s="19" t="str">
-        <x:v>Terminer le boss rush</x:v>
+        <x:v>CPU bracket simulations and future opponents are deterministic across save/reload at every round</x:v>
       </x:c>
       <x:c r="D137" s="19" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E137" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F137" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G137" s="19" t="str">
-        <x:v>Première victoire réelle contre Gloink Queen puis passage à The Fudge, acte 2/4. Le parcours intégral et sa médaille restent à jouer dans le navigateur.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H137" s="19" t="str">
-        <x:v>Tous les adversaires prévus apparaissent.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I137" s="20" t="str"/>
     </x:row>
     <x:row r="138" ht="32" customHeight="1">
       <x:c r="A138" s="18" t="str">
-        <x:v>QA-survival</x:v>
+        <x:v>QA-PROG-11</x:v>
       </x:c>
       <x:c r="B138" s="18" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C138" s="18" t="str">
-        <x:v>Vérifier le report de vie en survie</x:v>
+        <x:v>checkpoints save and resume every programme with the same costume, rules, encounter seed and starting health</x:v>
       </x:c>
       <x:c r="D138" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43797,25 +43853,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F138" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G138" s="18" t="str">
-        <x:v>Victoire réelle contre le Baron : 6 921 PV deviennent 8 121 au duel contre Loolilalu. Le bonus de 1 200 PV est appliqué ; le plafond de 10 000 et les dix vagues sont couverts par contrats Node.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H138" s="18" t="str">
-        <x:v>Le prochain match conserve les PV restants + 1 200 de récupération, sans dépasser 10 000.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I138" s="20" t="str"/>
     </x:row>
-    <x:row r="139" ht="45" customHeight="1">
+    <x:row r="139" ht="32" customHeight="1">
       <x:c r="A139" s="19" t="str">
-        <x:v>QA-story</x:v>
+        <x:v>QA-PROG-12</x:v>
       </x:c>
       <x:c r="B139" s="19" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C139" s="19" t="str">
-        <x:v>Jouer une route narrative jusqu’à sa conclusion</x:v>
+        <x:v>resumed survival checkpoints restart the real CQC engine reproducibly, with carried health</x:v>
       </x:c>
       <x:c r="D139" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43824,25 +43880,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F139" s="19" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G139" s="19" t="str">
-        <x:v>Route Jax intégralement jouée : quatre victoires réelles contre Gangle, Zooble, Ragatha puis Caine ; quatre scènes, fin individuelle et médaille acquise. Les treize autres routes sont vérifiées par contrats Node, sans revendication d’une partie intégrale dans le navigateur.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H139" s="19" t="str">
-        <x:v>Les quatre rencontres suivent leurs arènes, dialogues et adversaires ; la fin correspond au combattant choisi.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I139" s="20" t="str"/>
     </x:row>
-    <x:row r="140" ht="45" customHeight="1">
+    <x:row r="140" ht="32" customHeight="1">
       <x:c r="A140" s="18" t="str">
-        <x:v>QA-tournament</x:v>
+        <x:v>QA-PROG-13</x:v>
       </x:c>
       <x:c r="B140" s="18" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C140" s="18" t="str">
-        <x:v>Terminer un tournoi et vérifier son tableau</x:v>
+        <x:v>retry preserves prior story/arcade/boss victories while survival and tournament begin a new attempt</x:v>
       </x:c>
       <x:c r="D140" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43851,25 +43907,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F140" s="18" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G140" s="18" t="str">
-        <x:v>Huit participants et sept cases de tableau. Trois victoires clavier remportent la coupe ; trois résultats joués et quatre résultats CPU simulés sont distingués. Une défaite réelle provoque l’élimination, sans médaille, puis un nouvel essai réinitialise la tentative.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H140" s="18" t="str">
-        <x:v>Huit participants, quatre quarts, deux demies et une finale ; les résultats joués et simulés sont distingués.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I140" s="20" t="str"/>
     </x:row>
-    <x:row r="141" ht="45" customHeight="1">
+    <x:row r="141" ht="32" customHeight="1">
       <x:c r="A141" s="19" t="str">
-        <x:v>QA-program-resume</x:v>
+        <x:v>QA-PROG-14</x:v>
       </x:c>
       <x:c r="B141" s="19" t="str">
-        <x:v>Persistance</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C141" s="19" t="str">
-        <x:v>Recharger puis reprendre un programme actif</x:v>
+        <x:v>untrusted import rejects malformed identity, rules, bounds, stage/opponent references and status</x:v>
       </x:c>
       <x:c r="D141" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43878,25 +43934,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F141" s="19" t="str">
-        <x:v>node tests/combat-encore-browser.mjs / tests/combat-progression.test.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G141" s="19" t="str">
-        <x:v>Rechargement après victoire réelle en histoire puis quart de finale de tournoi : adversaire, règle, graine et santé du prochain duel sont conservés sans double comptage. Reprise après défaite d’histoire également vérifiée. Les cinq modes sont couverts par contrats unitaires.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H141" s="19" t="str">
-        <x:v>Le même combat recommence au point de reprise documenté, avec sa graine, son adversaire et sa santé de départ.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I141" s="20" t="str"/>
     </x:row>
-    <x:row r="142" ht="45" customHeight="1">
+    <x:row r="142" ht="32" customHeight="1">
       <x:c r="A142" s="18" t="str">
-        <x:v>QA-bindings</x:v>
+        <x:v>QA-PROG-15</x:v>
       </x:c>
       <x:c r="B142" s="18" t="str">
-        <x:v>Commandes</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C142" s="18" t="str">
-        <x:v>Remapper les deux joueurs et refuser un conflit</x:v>
+        <x:v>import cannot introduce impossible, fractional or additional results beyond a defeat or programme completion</x:v>
       </x:c>
       <x:c r="D142" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -43905,25 +43961,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F142" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs / tests/combat-bindings.test.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G142" s="18" t="str">
-        <x:v>La touche F remplace l’attaque légère de J1, agit dans le moteur et apparaît dans la liste des techniques ; ancienne touche inactive. Conflits et raccourcis réservés refusés, alternatives acceptées, étiquettes AZERTY/QWERTY et réglages persistants après rechargement.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H142" s="18" t="str">
-        <x:v>Une touche personnalisée fonctionne en combat ; les doublons sont refusés ; les réglages survivent au rechargement.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I142" s="20" t="str"/>
     </x:row>
-    <x:row r="143" ht="58" customHeight="1">
+    <x:row r="143" ht="32" customHeight="1">
       <x:c r="A143" s="19" t="str">
-        <x:v>QA-offline</x:v>
+        <x:v>QA-PROG-16</x:v>
       </x:c>
       <x:c r="B143" s="19" t="str">
-        <x:v>Distribution</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C143" s="19" t="str">
-        <x:v>Recharger le standalone sans réseau après préparation</x:v>
+        <x:v>tournament import verifies participants, round ancestry, CPU results, champion and real player outcome provenance</x:v>
       </x:c>
       <x:c r="D143" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -43932,133 +43988,133 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F143" s="19" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · serveur HTTP du build autonome + réseau Chromium désactivé</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G143" s="19" t="str">
-        <x:v>Les 42 planches (47 345 031 octets) sont téléchargées par action explicite. Rechargement à froid sans réseau, changement de combattant/arène et déplacement clavier réussis. Mise à jour via l’UI conserve le pack inchangé et le profil ; portée limitée à /combat/ ; suppression des illustrations préserve les données.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H143" s="19" t="str">
-        <x:v>Après mise en cache réussie, le menu et un combat chargé restent disponibles hors ligne sans l’environnement CainOS.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I143" s="20" t="str"/>
     </x:row>
-    <x:row r="144" ht="45" customHeight="1">
+    <x:row r="144" ht="32" customHeight="1">
       <x:c r="A144" s="18" t="str">
-        <x:v>QA-audio</x:v>
+        <x:v>QA-PROG-17</x:v>
       </x:c>
       <x:c r="B144" s="18" t="str">
-        <x:v>Présentation</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C144" s="18" t="str">
-        <x:v>Vérifier thèmes, mixage et pause sonore</x:v>
+        <x:v>normalized imports discard unknown fields without sharing arrays or polluting object prototypes</x:v>
       </x:c>
       <x:c r="D144" s="18" t="str">
         <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E144" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F144" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs / tests/combat-audio.test.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G144" s="18" t="str">
-        <x:v>Contexte WebAudio réel ouvert après geste, musique active avec bruitages coupés, voix bornées. Pause : simulation figée et voix libérées ; reprise du thème d’arène. Les douze arrangements et le cycle de vie sont aussi vérifiés par contexte/horloge simulés. Écoute sur matériel physique non effectuée.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H144" s="18" t="str">
-        <x:v>Chaque arène possède son thème ; la musique suit le réglage, se suspend pendant la pause et n’empile pas de boucles à la reprise.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I144" s="20" t="str"/>
     </x:row>
     <x:row r="145" ht="32" customHeight="1">
       <x:c r="A145" s="19" t="str">
-        <x:v>QA-training</x:v>
+        <x:v>QA-PROG-18</x:v>
       </x:c>
       <x:c r="B145" s="19" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C145" s="19" t="str">
-        <x:v>Tester chaque dummy d’entraînement</x:v>
+        <x:v>program construction rejects invalid catalogues, unsupported modes and costumes belonging to another fighter</x:v>
       </x:c>
       <x:c r="D145" s="19" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E145" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F145" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs / node tests/combat-engine.test.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G145" s="19" t="str">
-        <x:v>Clavier, attaque, garde du dummy et hitboxes utilisés dans le navigateur. Les six comportements sont couverts par le moteur ; leur parcours UI complet reste à vérifier.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H145" s="19" t="str">
-        <x:v>Comportement, réglage et reset réels.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I145" s="20" t="str"/>
     </x:row>
     <x:row r="146" ht="32" customHeight="1">
       <x:c r="A146" s="18" t="str">
-        <x:v>QA-challenges</x:v>
+        <x:v>QA-PROG-19</x:v>
       </x:c>
       <x:c r="B146" s="18" t="str">
-        <x:v>Parcours</x:v>
+        <x:v>Programmes et reprise</x:v>
       </x:c>
       <x:c r="C146" s="18" t="str">
-        <x:v>Terminer les six défis</x:v>
+        <x:v>missing, inaccessible, oversized or corrupt storage fails safely without resuming bad state</x:v>
       </x:c>
       <x:c r="D146" s="18" t="str">
         <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E146" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F146" s="18" t="str">
-        <x:v>node tests/combat-session.test.mjs / tests/combat-browser.mjs</x:v>
+        <x:v>node tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G146" s="18" t="str">
-        <x:v>Les six défis sont accomplis depuis les positions initiales dans la simulation. Le défi Spécialiste est aussi gagné et sauvegardé dans le navigateur.</x:v>
+        <x:v>node --test-reporter=tap tests/combat-progression.test.mjs — 19/19 cas réussis, 0 échec, 0 ignoré (22 octobre 2026 ; rapport audit-combat/combat-progression.test.tap)</x:v>
       </x:c>
       <x:c r="H146" s="18" t="str">
-        <x:v>Chaque métrique déclenche uniquement son objectif.</x:v>
+        <x:v>Routes, tournoi déterministe et points de reprise validés</x:v>
       </x:c>
       <x:c r="I146" s="20" t="str"/>
     </x:row>
-    <x:row r="147" ht="45" customHeight="1">
+    <x:row r="147" ht="32" customHeight="1">
       <x:c r="A147" s="19" t="str">
-        <x:v>QA-save</x:v>
+        <x:v>QA-boot</x:v>
       </x:c>
       <x:c r="B147" s="19" t="str">
-        <x:v>Persistance</x:v>
+        <x:v>Intégration</x:v>
       </x:c>
       <x:c r="C147" s="19" t="str">
-        <x:v>Exporter puis importer un profil</x:v>
+        <x:v>Démarrer CainOS et ouvrir le combat</x:v>
       </x:c>
       <x:c r="D147" s="19" t="str">
-        <x:v>À vérifier</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E147" s="19" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F147" s="19" t="str">
-        <x:v>tests/combat-progression-browser.mjs / tests/combat-encore-browser.mjs / tests/combat-session.test.mjs</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G147" s="19" t="str">
-        <x:v>Export UI réel conservant deux récompenses malgré un stockage refusé ; import UI d’un profil de tournoi neuf validé par confirmation et comparaison complète ; progression/rechargement conservés. Réimporter dans le navigateur exactement le fichier qui vient d’être exporté reste une vérification séparée.</x:v>
+        <x:v>Calibration existante réellement jouée, démarrage du bureau, lancement de Combat par double-clic. L’interface autonome expose neuf modes et le même moteur est chargé dans la fenêtre CainOS.</x:v>
       </x:c>
       <x:c r="H147" s="19" t="str">
-        <x:v>Les réglages et statistiques sont restaurés.</x:v>
+        <x:v>Le bureau et les applications existantes restent utilisables.</x:v>
       </x:c>
       <x:c r="I147" s="20" t="str"/>
     </x:row>
     <x:row r="148" ht="32" customHeight="1">
       <x:c r="A148" s="18" t="str">
-        <x:v>QA-replay</x:v>
+        <x:v>QA-standalone</x:v>
       </x:c>
       <x:c r="B148" s="18" t="str">
-        <x:v>Persistance</x:v>
+        <x:v>Intégration</x:v>
       </x:c>
       <x:c r="C148" s="18" t="str">
-        <x:v>Enregistrer puis relire un match</x:v>
+        <x:v>Ouvrir le standalone sans CainOS</x:v>
       </x:c>
       <x:c r="D148" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44067,104 +44123,106 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F148" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs / tests/combat-offline-browser.mjs</x:v>
       </x:c>
       <x:c r="G148" s="18" t="str">
-        <x:v>Le replay reproduit exactement tout le snapshot final du duel réel sans modifier les statistiques ni l’historique. La régression de profil version 1 et les apparences valides sont couvertes par Node.</x:v>
+        <x:v>Le build isolé charge 26 ressources locales sans /app.js CainOS. Préparation complète de 42 planches, puis rechargement hors ligne et combat sur une autre arène également réussis.</x:v>
       </x:c>
       <x:c r="H148" s="18" t="str">
-        <x:v>Gagnant, vie et positions finales concordent.</x:v>
+        <x:v>Le menu et le combat se chargent directement.</x:v>
       </x:c>
       <x:c r="I148" s="20" t="str"/>
     </x:row>
     <x:row r="149" ht="32" customHeight="1">
       <x:c r="A149" s="19" t="str">
-        <x:v>QA-bad-save</x:v>
+        <x:v>QA-pause-window</x:v>
       </x:c>
       <x:c r="B149" s="19" t="str">
-        <x:v>Persistance</x:v>
+        <x:v>Intégration</x:v>
       </x:c>
       <x:c r="C149" s="19" t="str">
-        <x:v>Importer JSON invalide et mauvais format</x:v>
+        <x:v>Réduire et fermer la fenêtre Combat</x:v>
       </x:c>
       <x:c r="D149" s="19" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E149" s="19" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F149" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs / tests/combat-offline-browser.mjs</x:v>
       </x:c>
       <x:c r="G149" s="19" t="str">
-        <x:v>Profil au mauvais format, JSON malformé et bits invalides du replay refusés sans perte du profil existant. Les importations de programme/tournoi corrompues sont aussi rejetées dans les contrats Node.</x:v>
+        <x:v>Réduction de la fenêtre : frame figée et pause confirmées ; pause du jeu : voix WebAudio libérées. La fermeture de fenêtre par la croix reste un parcours à tester séparément.</x:v>
       </x:c>
       <x:c r="H149" s="19" t="str">
-        <x:v>Message clair, profil existant préservé.</x:v>
+        <x:v>Le combat et le son se mettent en pause.</x:v>
       </x:c>
       <x:c r="I149" s="20" t="str"/>
     </x:row>
-    <x:row r="150" ht="45" customHeight="1">
+    <x:row r="150" ht="32" customHeight="1">
       <x:c r="A150" s="18" t="str">
-        <x:v>QA-mobile-layout</x:v>
+        <x:v>QA-reopen</x:v>
       </x:c>
       <x:c r="B150" s="18" t="str">
-        <x:v>Accessibilité</x:v>
+        <x:v>Intégration</x:v>
       </x:c>
       <x:c r="C150" s="18" t="str">
-        <x:v>Parcourir le jeu en petit viewport</x:v>
+        <x:v>Rouvrir la fenêtre Combat</x:v>
       </x:c>
       <x:c r="D150" s="18" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E150" s="18" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F150" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs / tests/combat-offline-browser.mjs · émulation Chromium</x:v>
+        <x:v>node tests/combat-browser.mjs</x:v>
       </x:c>
       <x:c r="G150" s="18" t="str">
-        <x:v>Accueil et combat 390 × 844 sans débordement horizontal ; tactiles détectés automatiquement et attaque par vrai événement tap. Les réglages étendus et le remappage tiennent aussi à 390 px. Aucun appareil physique testé.</x:v>
+        <x:v>Réouverture après réduction : bouton Reprendre présent. Le parcours fermeture par la croix puis réouvertures répétées n’est pas revendiqué.</x:v>
       </x:c>
       <x:c r="H150" s="18" t="str">
-        <x:v>Aucun contrôle essentiel hors écran.</x:v>
+        <x:v>Reprise contrôlée, aucune boucle doublée.</x:v>
       </x:c>
       <x:c r="I150" s="20" t="str"/>
     </x:row>
-    <x:row r="151" ht="29" customHeight="1">
+    <x:row r="151" ht="32" customHeight="1">
       <x:c r="A151" s="19" t="str">
-        <x:v>QA-mobile-device</x:v>
+        <x:v>QA-roster</x:v>
       </x:c>
       <x:c r="B151" s="19" t="str">
-        <x:v>Matériel</x:v>
+        <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C151" s="19" t="str">
-        <x:v>Jouer sur téléphone physique</x:v>
+        <x:v>Choisir chacun des 14 combattants</x:v>
       </x:c>
       <x:c r="D151" s="19" t="str">
-        <x:v>Non exécuté</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E151" s="19" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="F151" s="19" t="str">
-        <x:v>Parcours navigateur ou matériel réel</x:v>
-      </x:c>
-      <x:c r="G151" s="19" t="str"/>
+        <x:v>Tests de données, moteur, préchargement et sélection navigateur</x:v>
+      </x:c>
+      <x:c r="G151" s="19" t="str">
+        <x:v>14 combattants présents et préchargés ; 140 techniques activées. La sélection manuelle de chaque costume reste distincte.</x:v>
+      </x:c>
       <x:c r="H151" s="19" t="str">
-        <x:v>Gestes multiples, rotation et volume fonctionnent.</x:v>
+        <x:v>Le nom, le sprite et le kit correspondent.</x:v>
       </x:c>
       <x:c r="I151" s="20" t="str"/>
     </x:row>
     <x:row r="152" ht="29" customHeight="1">
       <x:c r="A152" s="18" t="str">
-        <x:v>QA-gamepads</x:v>
+        <x:v>QA-costumes</x:v>
       </x:c>
       <x:c r="B152" s="18" t="str">
-        <x:v>Matériel</x:v>
+        <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C152" s="18" t="str">
-        <x:v>Jouer avec deux manettes physiques</x:v>
+        <x:v>Vérifier les 51 variantes</x:v>
       </x:c>
       <x:c r="D152" s="18" t="str">
         <x:v>Non exécuté</x:v>
@@ -44177,123 +44235,127 @@
       </x:c>
       <x:c r="G152" s="18" t="str"/>
       <x:c r="H152" s="18" t="str">
-        <x:v>Assignation et déconnexion testées.</x:v>
+        <x:v>Silhouette complète, pas de bordure ni de recadrage incorrect.</x:v>
       </x:c>
       <x:c r="I152" s="20" t="str"/>
     </x:row>
-    <x:row r="153" ht="29" customHeight="1">
+    <x:row r="153" ht="32" customHeight="1">
       <x:c r="A153" s="19" t="str">
-        <x:v>QA-focus</x:v>
+        <x:v>QA-stages</x:v>
       </x:c>
       <x:c r="B153" s="19" t="str">
-        <x:v>Accessibilité</x:v>
+        <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C153" s="19" t="str">
-        <x:v>Naviguer dans tous les menus au clavier</x:v>
+        <x:v>Vérifier les 12 arènes</x:v>
       </x:c>
       <x:c r="D153" s="19" t="str">
-        <x:v>Non exécuté</x:v>
+        <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E153" s="19" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F153" s="19" t="str">
-        <x:v>Parcours navigateur ou matériel réel</x:v>
-      </x:c>
-      <x:c r="G153" s="19" t="str"/>
+        <x:v>Préchargement du renderer et 12 captures Canvas</x:v>
+      </x:c>
+      <x:c r="G153" s="19" t="str">
+        <x:v>Douze thèmes rendus. Préchargement des 14 combattants sans erreur ; les décors restent des compositions procédurales.</x:v>
+      </x:c>
       <x:c r="H153" s="19" t="str">
-        <x:v>Focus visible et ordre cohérent.</x:v>
+        <x:v>Décors distincts, aucun combattant masqué.</x:v>
       </x:c>
       <x:c r="I153" s="20" t="str"/>
     </x:row>
     <x:row r="154" ht="32" customHeight="1">
       <x:c r="A154" s="18" t="str">
-        <x:v>QA-motion</x:v>
+        <x:v>QA-local</x:v>
       </x:c>
       <x:c r="B154" s="18" t="str">
-        <x:v>Accessibilité</x:v>
+        <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C154" s="18" t="str">
-        <x:v>Activer réduction des mouvements</x:v>
+        <x:v>Jouer un duel local complet</x:v>
       </x:c>
       <x:c r="D154" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E154" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F154" s="18" t="str">
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G154" s="18" t="str">
+        <x:v>Duel local réellement terminé en 2 282 frames, résultat sauvegardé et replay de 611 séquences d’entrées. Les commandes de J2 sont indépendantes.</x:v>
+      </x:c>
+      <x:c r="H154" s="18" t="str">
+        <x:v>Deux joueurs et résultat sans conflit d’entrées.</x:v>
+      </x:c>
+      <x:c r="I154" s="20" t="str"/>
+    </x:row>
+    <x:row r="155" ht="32" customHeight="1">
+      <x:c r="A155" s="19" t="str">
+        <x:v>QA-arcade</x:v>
+      </x:c>
+      <x:c r="B155" s="19" t="str">
+        <x:v>Parcours</x:v>
+      </x:c>
+      <x:c r="C155" s="19" t="str">
+        <x:v>Terminer un arcade de six matchs</x:v>
+      </x:c>
+      <x:c r="D155" s="19" t="str">
         <x:v>À vérifier</x:v>
-      </x:c>
-      <x:c r="E154" s="18" t="str">
-        <x:v>P1</x:v>
-      </x:c>
-      <x:c r="F154" s="18" t="str">
-        <x:v>Réglage sauvegardé et implémentation du renderer</x:v>
-      </x:c>
-      <x:c r="G154" s="18" t="str">
-        <x:v>Le réglage réduit les oscillations et tremblements dans le code. Comparaison visuelle complète encore à mener.</x:v>
-      </x:c>
-      <x:c r="H154" s="18" t="str">
-        <x:v>Effets réduits sans perte de signaux de combat.</x:v>
-      </x:c>
-      <x:c r="I154" s="20" t="str"/>
-    </x:row>
-    <x:row r="155" ht="29" customHeight="1">
-      <x:c r="A155" s="19" t="str">
-        <x:v>QA-fps</x:v>
-      </x:c>
-      <x:c r="B155" s="19" t="str">
-        <x:v>Performance</x:v>
-      </x:c>
-      <x:c r="C155" s="19" t="str">
-        <x:v>Mesurer plusieurs matchs sur matériel modeste</x:v>
-      </x:c>
-      <x:c r="D155" s="19" t="str">
-        <x:v>Non exécuté</x:v>
       </x:c>
       <x:c r="E155" s="19" t="str">
         <x:v>P1</x:v>
       </x:c>
       <x:c r="F155" s="19" t="str">
-        <x:v>Parcours navigateur ou matériel réel</x:v>
-      </x:c>
-      <x:c r="G155" s="19" t="str"/>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G155" s="19" t="str">
+        <x:v>Première victoire réelle contre Bubble, puis passage à Pomni, acte 2/6. La longueur et la reprise sont couvertes par contrat ; le parcours intégral et sa médaille ne sont pas revendiqués dans le navigateur.</x:v>
+      </x:c>
       <x:c r="H155" s="19" t="str">
-        <x:v>Cadence et mémoire stables après plusieurs reprises.</x:v>
+        <x:v>Progression et fin de parcours fonctionnelles.</x:v>
       </x:c>
       <x:c r="I155" s="20" t="str"/>
     </x:row>
-    <x:row r="156" ht="32" customHeight="1">
+    <x:row r="156" ht="45" customHeight="1">
       <x:c r="A156" s="18" t="str">
-        <x:v>QA-build</x:v>
+        <x:v>QA-boss</x:v>
       </x:c>
       <x:c r="B156" s="18" t="str">
-        <x:v>Distribution</x:v>
+        <x:v>Parcours</x:v>
       </x:c>
       <x:c r="C156" s="18" t="str">
-        <x:v>Servir les deux builds générés</x:v>
+        <x:v>Terminer le boss rush</x:v>
       </x:c>
       <x:c r="D156" s="18" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E156" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F156" s="18" t="str">
-        <x:v>npm run qa / tests/combat-progression-browser.mjs / tests/combat-offline-browser.mjs</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G156" s="18" t="str">
-        <x:v>Deux builds générés. Le standalone compilé est servi sur une origine séparée, testé en ligne puis hors ligne. CainOS est vérifié depuis le répertoire source ; le dossier dist OS reste à servir séparément.</x:v>
+        <x:v>Première victoire réelle contre Gloink Queen, puis passage à The Fudge, acte 2/4. La longueur et la reprise sont couvertes par contrat ; le parcours intégral et sa médaille ne sont pas revendiqués dans le navigateur.</x:v>
       </x:c>
       <x:c r="H156" s="18" t="str">
-        <x:v>Aucune ressource requise absente.</x:v>
+        <x:v>Tous les adversaires prévus apparaissent.</x:v>
       </x:c>
       <x:c r="I156" s="20" t="str"/>
     </x:row>
-    <x:row r="157" ht="45" customHeight="1">
+    <x:row r="157" ht="32" customHeight="1">
       <x:c r="A157" s="19" t="str">
-        <x:v>QA-regression</x:v>
+        <x:v>QA-survival</x:v>
       </x:c>
       <x:c r="B157" s="19" t="str">
-        <x:v>Régression</x:v>
+        <x:v>Parcours</x:v>
       </x:c>
       <x:c r="C157" s="19" t="str">
-        <x:v>Exécuter les audits CainOS existants</x:v>
+        <x:v>Vérifier le report de vie en survie</x:v>
       </x:c>
       <x:c r="D157" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44302,25 +44364,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F157" s="19" t="str">
-        <x:v>npm run qa · audit-combat/qa-0.2.0.log + six TAP individuels</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G157" s="19" t="str">
-        <x:v>22 octobre 2026 : audits CainOS et deux builds réussis ; 122 cas Node réussis dans six suites (121 à la QA globale, puis 16/16 commandes après correction ciblée du focus). Pack : 42 planches originales, 47 345 031 octets.</x:v>
+        <x:v>Victoire réelle contre Pomni : 8 656 PV deviennent 9 856 au duel contre Kaufmo — abstraction. Le bonus de 1 200 PV est appliqué ; le plafond de 10 000 et les dix vagues sont couverts par contrats Node.</x:v>
       </x:c>
       <x:c r="H157" s="19" t="str">
-        <x:v>Aucune régression des contrats existants.</x:v>
+        <x:v>Le prochain match conserve les PV restants + 1 200 de récupération, sans dépasser 10 000.</x:v>
       </x:c>
       <x:c r="I157" s="20" t="str"/>
     </x:row>
     <x:row r="158" ht="45" customHeight="1">
       <x:c r="A158" s="18" t="str">
-        <x:v>QA-tracker-proof</x:v>
+        <x:v>QA-story</x:v>
       </x:c>
       <x:c r="B158" s="18" t="str">
-        <x:v>Production du suivi</x:v>
+        <x:v>Parcours</x:v>
       </x:c>
       <x:c r="C158" s="18" t="str">
-        <x:v>Refuser une preuve corrompue avant génération</x:v>
+        <x:v>Jouer une route narrative jusqu’à sa conclusion</x:v>
       </x:c>
       <x:c r="D158" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44329,25 +44391,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F158" s="18" t="str">
-        <x:v>Builder exécuté avec un répertoire temporaire isolé et un classeur sentinelle existant</x:v>
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G158" s="18" t="str">
-        <x:v>22 octobre 2026 : JSON malformé (SyntaxError), valeur null (schéma invalide) et lecture d’un répertoire (EISDIR) rejetés. Le fichier Excel préexistant est inchangé dans les trois cas. Seule l’absence ENOENT est facultative.</x:v>
+        <x:v>Route Jax intégralement jouée : quatre victoires réelles contre Gangle, Zooble, Ragatha puis Caine ; quatre scènes, fin individuelle et médaille acquise. Les treize autres routes sont vérifiées par contrats Node, sans revendication d’une partie intégrale dans le navigateur.</x:v>
       </x:c>
       <x:c r="H158" s="18" t="str">
-        <x:v>JSON invalide, type invalide et erreurs de lecture sont rejetés ; le fichier Excel existant est préservé.</x:v>
+        <x:v>Les quatre rencontres suivent leurs arènes, dialogues et adversaires ; la fin correspond au combattant choisi.</x:v>
       </x:c>
       <x:c r="I158" s="20" t="str"/>
     </x:row>
-    <x:row r="159" ht="29" customHeight="1">
+    <x:row r="159" ht="45" customHeight="1">
       <x:c r="A159" s="19" t="str">
-        <x:v>QA-UI-01</x:v>
+        <x:v>QA-tournament</x:v>
       </x:c>
       <x:c r="B159" s="19" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Parcours</x:v>
       </x:c>
       <x:c r="C159" s="19" t="str">
-        <x:v>Nine modes and standalone home render</x:v>
+        <x:v>Terminer un tournoi et vérifier son tableau</x:v>
       </x:c>
       <x:c r="D159" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44356,25 +44418,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F159" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G159" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Huit participants et sept cases de tableau. Trois victoires clavier remportent la coupe ; trois résultats joués et quatre résultats CPU simulés sont distingués. Une défaite réelle provoque l’élimination, sans médaille, puis un nouvel essai réinitialise la tentative.</x:v>
       </x:c>
       <x:c r="H159" s="19" t="str">
-        <x:v>Nine modes and standalone home render</x:v>
+        <x:v>Huit participants, quatre quarts, deux demies et une finale ; les résultats joués et simulés sont distingués.</x:v>
       </x:c>
       <x:c r="I159" s="20" t="str"/>
     </x:row>
-    <x:row r="160" ht="29" customHeight="1">
+    <x:row r="160" ht="45" customHeight="1">
       <x:c r="A160" s="18" t="str">
-        <x:v>QA-UI-02</x:v>
+        <x:v>QA-program-resume</x:v>
       </x:c>
       <x:c r="B160" s="18" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Persistance</x:v>
       </x:c>
       <x:c r="C160" s="18" t="str">
-        <x:v>Codex changes fighter and shows ten authored moves</x:v>
+        <x:v>Recharger puis reprendre un programme actif</x:v>
       </x:c>
       <x:c r="D160" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44383,25 +44445,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F160" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-encore-browser.mjs / tests/combat-progression.test.mjs</x:v>
       </x:c>
       <x:c r="G160" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Rechargement après victoire réelle en histoire puis quart de finale de tournoi : adversaire, règle, graine et santé du prochain duel sont conservés sans double comptage. Reprise après défaite d’histoire également vérifiée. Les cinq modes sont couverts par contrats unitaires.</x:v>
       </x:c>
       <x:c r="H160" s="18" t="str">
-        <x:v>Codex changes fighter and shows ten authored moves</x:v>
+        <x:v>Le même combat recommence au point de reprise documenté, avec sa graine, son adversaire et sa santé de départ.</x:v>
       </x:c>
       <x:c r="I160" s="20" t="str"/>
     </x:row>
-    <x:row r="161" ht="29" customHeight="1">
+    <x:row r="161" ht="71" customHeight="1">
       <x:c r="A161" s="19" t="str">
-        <x:v>QA-UI-03</x:v>
+        <x:v>QA-profile-recovery</x:v>
       </x:c>
       <x:c r="B161" s="19" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Persistance</x:v>
       </x:c>
       <x:c r="C161" s="19" t="str">
-        <x:v>Archive search filters real records</x:v>
+        <x:v>Récupérer un profil local dont le programme est invalide</x:v>
       </x:c>
       <x:c r="D161" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44410,25 +44472,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F161" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>tests/combat-session.test.mjs / tests/combat-profile-recovery-browser.mjs</x:v>
       </x:c>
       <x:c r="G161" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Chargement local d’une fixture de migration dont seul le checkpoint est invalide : programme abandonné et autres données valides conservées. Conservation après changement de réglage et rechargement, vrai événement storage depuis un second onglet et import UI invalide refusé sans remplacement du profil. Le défi Spécialiste est réellement accompli au clavier pendant le contrôle de rafraîchissement ; les autres récompenses sont des données de migration.</x:v>
       </x:c>
       <x:c r="H161" s="19" t="str">
-        <x:v>Archive search filters real records</x:v>
+        <x:v>Seul le checkpoint invalide est abandonné ; les autres données valides survivent aux réglages, au rechargement et aux événements inter-onglets. L’import manuel demeure strict.</x:v>
       </x:c>
       <x:c r="I161" s="20" t="str"/>
     </x:row>
-    <x:row r="162" ht="29" customHeight="1">
+    <x:row r="162" ht="45" customHeight="1">
       <x:c r="A162" s="18" t="str">
-        <x:v>QA-UI-04</x:v>
+        <x:v>QA-bindings</x:v>
       </x:c>
       <x:c r="B162" s="18" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Commandes</x:v>
       </x:c>
       <x:c r="C162" s="18" t="str">
-        <x:v>Settings persist across reload</x:v>
+        <x:v>Remapper les deux joueurs et refuser un conflit</x:v>
       </x:c>
       <x:c r="D162" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44437,25 +44499,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F162" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-offline-browser.mjs / tests/combat-bindings.test.mjs</x:v>
       </x:c>
       <x:c r="G162" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>La touche F remplace l’attaque légère de J1, agit dans le moteur et apparaît dans la liste des techniques ; ancienne touche inactive. Conflits et raccourcis réservés refusés, alternatives acceptées, étiquettes AZERTY/QWERTY et réglages persistants après rechargement.</x:v>
       </x:c>
       <x:c r="H162" s="18" t="str">
-        <x:v>Settings persist across reload</x:v>
+        <x:v>Une touche personnalisée fonctionne en combat ; les doublons sont refusés ; les réglages survivent au rechargement.</x:v>
       </x:c>
       <x:c r="I162" s="20" t="str"/>
     </x:row>
-    <x:row r="163" ht="29" customHeight="1">
+    <x:row r="163" ht="58" customHeight="1">
       <x:c r="A163" s="19" t="str">
-        <x:v>QA-UI-05</x:v>
+        <x:v>QA-offline</x:v>
       </x:c>
       <x:c r="B163" s="19" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Distribution</x:v>
       </x:c>
       <x:c r="C163" s="19" t="str">
-        <x:v>Training loads and responds to keyboard movement/attack</x:v>
+        <x:v>Recharger le standalone sans réseau après préparation</x:v>
       </x:c>
       <x:c r="D163" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44464,25 +44526,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F163" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-offline-browser.mjs · serveur HTTP du build autonome + réseau Chromium désactivé</x:v>
       </x:c>
       <x:c r="G163" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Les 42 planches (47 345 031 octets) sont téléchargées par action explicite. Rechargement à froid sans réseau, changement de combattant/arène et déplacement clavier réussis. Mise à jour via l’UI conserve le pack inchangé et le profil ; portée limitée à /combat/ ; suppression des illustrations préserve les données.</x:v>
       </x:c>
       <x:c r="H163" s="19" t="str">
-        <x:v>Training loads and responds to keyboard movement/attack</x:v>
+        <x:v>Après mise en cache réussie, le menu et un combat chargé restent disponibles hors ligne sans l’environnement CainOS.</x:v>
       </x:c>
       <x:c r="I163" s="20" t="str"/>
     </x:row>
-    <x:row r="164" ht="29" customHeight="1">
+    <x:row r="164" ht="58" customHeight="1">
       <x:c r="A164" s="18" t="str">
-        <x:v>QA-UI-06</x:v>
+        <x:v>QA-offline-install-recovery</x:v>
       </x:c>
       <x:c r="B164" s="18" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Distribution</x:v>
       </x:c>
       <x:c r="C164" s="18" t="str">
-        <x:v>Pause stops simulation and resume restarts</x:v>
+        <x:v>Échouer puis relancer la première installation hors ligne</x:v>
       </x:c>
       <x:c r="D164" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44491,133 +44553,133 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F164" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>tests/combat-offline.test.mjs / tests/combat-recovery-browser.mjs</x:v>
       </x:c>
       <x:c r="G164" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Une première installation volontairement interrompue affiche une erreur et une commande Réessayer. Après rétablissement des ressources, une nouvelle tentative aboutit depuis l’interface. Les délais, appels concurrents et libérations d’écouteurs sont vérifiés par les contrats Node ; les mises à jour conservent le worker actif.</x:v>
       </x:c>
       <x:c r="H164" s="18" t="str">
-        <x:v>Pause stops simulation and resume restarts</x:v>
+        <x:v>Un téléchargement essentiel en erreur produit un état explicite ; Réessayer démarre une nouvelle installation après retour du réseau, sans attente ni écouteur abandonné.</x:v>
       </x:c>
       <x:c r="I164" s="20" t="str"/>
     </x:row>
-    <x:row r="165" ht="29" customHeight="1">
+    <x:row r="165" ht="45" customHeight="1">
       <x:c r="A165" s="19" t="str">
-        <x:v>QA-UI-07</x:v>
+        <x:v>QA-audio</x:v>
       </x:c>
       <x:c r="B165" s="19" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Présentation</x:v>
       </x:c>
       <x:c r="C165" s="19" t="str">
-        <x:v>Move list pauses and resumes the current encounter</x:v>
+        <x:v>Vérifier thèmes, mixage et pause sonore</x:v>
       </x:c>
       <x:c r="D165" s="19" t="str">
         <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E165" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F165" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-offline-browser.mjs / tests/combat-audio.test.mjs</x:v>
       </x:c>
       <x:c r="G165" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Contexte WebAudio réel ouvert après geste, musique active avec bruitages coupés, voix bornées. Pause : simulation figée et voix libérées ; reprise du thème d’arène. Les douze arrangements et le cycle de vie sont aussi vérifiés par contexte/horloge simulés. Écoute sur matériel physique non effectuée.</x:v>
       </x:c>
       <x:c r="H165" s="19" t="str">
-        <x:v>Move list pauses and resumes the current encounter</x:v>
+        <x:v>Chaque arène possède son thème ; la musique suit le réglage, se suspend pendant la pause et n’empile pas de boucles à la reprise.</x:v>
       </x:c>
       <x:c r="I165" s="20" t="str"/>
     </x:row>
-    <x:row r="166" ht="29" customHeight="1">
+    <x:row r="166" ht="32" customHeight="1">
       <x:c r="A166" s="18" t="str">
-        <x:v>QA-UI-08</x:v>
+        <x:v>QA-training</x:v>
       </x:c>
       <x:c r="B166" s="18" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Parcours</x:v>
       </x:c>
       <x:c r="C166" s="18" t="str">
-        <x:v>Player 2 has independent local controls</x:v>
+        <x:v>Tester chaque dummy d’entraînement</x:v>
       </x:c>
       <x:c r="D166" s="18" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E166" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F166" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs / node tests/combat-engine.test.mjs</x:v>
       </x:c>
       <x:c r="G166" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Clavier, attaque, garde du dummy et hitboxes utilisés dans le navigateur. Les six comportements sont couverts par le moteur ; leur parcours UI complet reste à vérifier.</x:v>
       </x:c>
       <x:c r="H166" s="18" t="str">
-        <x:v>Player 2 has independent local controls</x:v>
+        <x:v>Comportement, réglage et reset réels.</x:v>
       </x:c>
       <x:c r="I166" s="20" t="str"/>
     </x:row>
-    <x:row r="167" ht="29" customHeight="1">
+    <x:row r="167" ht="32" customHeight="1">
       <x:c r="A167" s="19" t="str">
-        <x:v>QA-UI-09</x:v>
+        <x:v>QA-challenges</x:v>
       </x:c>
       <x:c r="B167" s="19" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Parcours</x:v>
       </x:c>
       <x:c r="C167" s="19" t="str">
-        <x:v>Challenge completion persists an earned result</x:v>
+        <x:v>Terminer les six défis</x:v>
       </x:c>
       <x:c r="D167" s="19" t="str">
         <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E167" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F167" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-session.test.mjs / tests/combat-browser.mjs</x:v>
       </x:c>
       <x:c r="G167" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Les six défis sont accomplis depuis les positions initiales dans la simulation. Le défi Spécialiste est aussi gagné et sauvegardé dans le navigateur.</x:v>
       </x:c>
       <x:c r="H167" s="19" t="str">
-        <x:v>Challenge completion persists an earned result</x:v>
+        <x:v>Chaque métrique déclenche uniquement son objectif.</x:v>
       </x:c>
       <x:c r="I167" s="20" t="str"/>
     </x:row>
-    <x:row r="168" ht="29" customHeight="1">
+    <x:row r="168" ht="45" customHeight="1">
       <x:c r="A168" s="18" t="str">
-        <x:v>QA-UI-10</x:v>
+        <x:v>QA-save</x:v>
       </x:c>
       <x:c r="B168" s="18" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Persistance</x:v>
       </x:c>
       <x:c r="C168" s="18" t="str">
-        <x:v>CainOS desktop launches the shared game and minimizing pauses it</x:v>
+        <x:v>Exporter puis importer un profil</x:v>
       </x:c>
       <x:c r="D168" s="18" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E168" s="18" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F168" s="18" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>tests/combat-progression-browser.mjs / tests/combat-encore-browser.mjs / tests/combat-session.test.mjs</x:v>
       </x:c>
       <x:c r="G168" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Export UI réel conservant deux récompenses malgré un stockage refusé ; import UI d’un profil de tournoi neuf validé par confirmation et comparaison complète ; progression/rechargement conservés. Réimporter dans le navigateur exactement le fichier qui vient d’être exporté reste une vérification séparée.</x:v>
       </x:c>
       <x:c r="H168" s="18" t="str">
-        <x:v>CainOS desktop launches the shared game and minimizing pauses it</x:v>
+        <x:v>Les réglages et statistiques sont restaurés.</x:v>
       </x:c>
       <x:c r="I168" s="20" t="str"/>
     </x:row>
-    <x:row r="169" ht="29" customHeight="1">
+    <x:row r="169" ht="32" customHeight="1">
       <x:c r="A169" s="19" t="str">
-        <x:v>QA-UI-11</x:v>
+        <x:v>QA-replay</x:v>
       </x:c>
       <x:c r="B169" s="19" t="str">
-        <x:v>Interface réelle</x:v>
+        <x:v>Persistance</x:v>
       </x:c>
       <x:c r="C169" s="19" t="str">
-        <x:v>390px mobile layout and touch attack work without horizontal overflow</x:v>
+        <x:v>Enregistrer puis relire un match</x:v>
       </x:c>
       <x:c r="D169" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44626,25 +44688,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F169" s="19" t="str">
-        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G169" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Le replay reproduit exactement tout le snapshot final du duel réel sans modifier les statistiques ni l’historique. La régression de profil version 1 et les apparences valides sont couvertes par Node.</x:v>
       </x:c>
       <x:c r="H169" s="19" t="str">
-        <x:v>390px mobile layout and touch attack work without horizontal overflow</x:v>
+        <x:v>Gagnant, vie et positions finales concordent.</x:v>
       </x:c>
       <x:c r="I169" s="20" t="str"/>
     </x:row>
-    <x:row r="170" ht="29" customHeight="1">
+    <x:row r="170" ht="32" customHeight="1">
       <x:c r="A170" s="18" t="str">
-        <x:v>QA-PRG-01</x:v>
+        <x:v>QA-bad-save</x:v>
       </x:c>
       <x:c r="B170" s="18" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Persistance</x:v>
       </x:c>
       <x:c r="C170" s="18" t="str">
-        <x:v>A real local match saves its result and replay</x:v>
+        <x:v>Importer JSON invalide et mauvais format</x:v>
       </x:c>
       <x:c r="D170" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44656,211 +44718,203 @@
         <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G170" s="18" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · 2282 simulation frames, 611 input runs</x:v>
+        <x:v>Profil au mauvais format, JSON malformé et bits invalides du replay refusés sans perte du profil existant. Les importations de programme/tournoi corrompues sont aussi rejetées dans les contrats Node.</x:v>
       </x:c>
       <x:c r="H170" s="18" t="str">
-        <x:v>A real local match saves its result and replay</x:v>
+        <x:v>Message clair, profil existant préservé.</x:v>
       </x:c>
       <x:c r="I170" s="20" t="str"/>
     </x:row>
-    <x:row r="171" ht="29" customHeight="1">
+    <x:row r="171" ht="45" customHeight="1">
       <x:c r="A171" s="19" t="str">
-        <x:v>QA-PRG-02</x:v>
+        <x:v>QA-mobile-layout</x:v>
       </x:c>
       <x:c r="B171" s="19" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Accessibilité</x:v>
       </x:c>
       <x:c r="C171" s="19" t="str">
-        <x:v>UI replay reproduces the full terminal snapshot without changing profile</x:v>
+        <x:v>Parcourir le jeu en petit viewport</x:v>
       </x:c>
       <x:c r="D171" s="19" t="str">
         <x:v>Réussi</x:v>
       </x:c>
       <x:c r="E171" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F171" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs / tests/combat-offline-browser.mjs · émulation Chromium</x:v>
       </x:c>
       <x:c r="G171" s="19" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Accueil et combat 390 × 844 sans débordement horizontal ; tactiles détectés automatiquement et attaque par vrai événement tap. Les réglages étendus et le remappage tiennent aussi à 390 px. Aucun appareil physique testé.</x:v>
       </x:c>
       <x:c r="H171" s="19" t="str">
-        <x:v>UI replay reproduces the full terminal snapshot without changing profile</x:v>
+        <x:v>Aucun contrôle essentiel hors écran.</x:v>
       </x:c>
       <x:c r="I171" s="20" t="str"/>
     </x:row>
     <x:row r="172" ht="29" customHeight="1">
       <x:c r="A172" s="18" t="str">
-        <x:v>QA-PRG-03</x:v>
+        <x:v>QA-mobile-device</x:v>
       </x:c>
       <x:c r="B172" s="18" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Matériel</x:v>
       </x:c>
       <x:c r="C172" s="18" t="str">
-        <x:v>arcade: earned first win opens encounter 2/6</x:v>
+        <x:v>Jouer sur téléphone physique</x:v>
       </x:c>
       <x:c r="D172" s="18" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>Non exécuté</x:v>
       </x:c>
       <x:c r="E172" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F172" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
-      </x:c>
-      <x:c r="G172" s="18" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · abstractedkaufmo → gangle, player HP 8189 → 10000</x:v>
-      </x:c>
+        <x:v>Parcours navigateur ou matériel réel</x:v>
+      </x:c>
+      <x:c r="G172" s="18" t="str"/>
       <x:c r="H172" s="18" t="str">
-        <x:v>arcade: earned first win opens encounter 2/6</x:v>
+        <x:v>Gestes multiples, rotation et volume fonctionnent.</x:v>
       </x:c>
       <x:c r="I172" s="20" t="str"/>
     </x:row>
     <x:row r="173" ht="29" customHeight="1">
       <x:c r="A173" s="19" t="str">
-        <x:v>QA-PRG-04</x:v>
+        <x:v>QA-gamepads</x:v>
       </x:c>
       <x:c r="B173" s="19" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Matériel</x:v>
       </x:c>
       <x:c r="C173" s="19" t="str">
-        <x:v>boss: earned first win opens encounter 2/4</x:v>
+        <x:v>Jouer avec deux manettes physiques</x:v>
       </x:c>
       <x:c r="D173" s="19" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>Non exécuté</x:v>
       </x:c>
       <x:c r="E173" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F173" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
-      </x:c>
-      <x:c r="G173" s="19" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · gloinkqueen → fudge, player HP 6864 → 10000</x:v>
-      </x:c>
+        <x:v>Parcours navigateur ou matériel réel</x:v>
+      </x:c>
+      <x:c r="G173" s="19" t="str"/>
       <x:c r="H173" s="19" t="str">
-        <x:v>boss: earned first win opens encounter 2/4</x:v>
+        <x:v>Assignation et déconnexion testées.</x:v>
       </x:c>
       <x:c r="I173" s="20" t="str"/>
     </x:row>
     <x:row r="174" ht="29" customHeight="1">
       <x:c r="A174" s="18" t="str">
-        <x:v>QA-PRG-05</x:v>
+        <x:v>QA-focus</x:v>
       </x:c>
       <x:c r="B174" s="18" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Accessibilité</x:v>
       </x:c>
       <x:c r="C174" s="18" t="str">
-        <x:v>survival: earned first win opens encounter 2/10</x:v>
+        <x:v>Naviguer dans tous les menus au clavier</x:v>
       </x:c>
       <x:c r="D174" s="18" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>Non exécuté</x:v>
       </x:c>
       <x:c r="E174" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F174" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
-      </x:c>
-      <x:c r="G174" s="18" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · baronmildenhall → loolilalu, player HP 6921 → 8121</x:v>
-      </x:c>
+        <x:v>Parcours navigateur ou matériel réel</x:v>
+      </x:c>
+      <x:c r="G174" s="18" t="str"/>
       <x:c r="H174" s="18" t="str">
-        <x:v>survival: earned first win opens encounter 2/10</x:v>
+        <x:v>Focus visible et ordre cohérent.</x:v>
       </x:c>
       <x:c r="I174" s="20" t="str"/>
     </x:row>
-    <x:row r="175" ht="29" customHeight="1">
+    <x:row r="175" ht="32" customHeight="1">
       <x:c r="A175" s="19" t="str">
-        <x:v>QA-PRG-06</x:v>
+        <x:v>QA-motion</x:v>
       </x:c>
       <x:c r="B175" s="19" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Accessibilité</x:v>
       </x:c>
       <x:c r="C175" s="19" t="str">
-        <x:v>Earned progression and settings survive a page reload</x:v>
+        <x:v>Activer réduction des mouvements</x:v>
       </x:c>
       <x:c r="D175" s="19" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E175" s="19" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F175" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>Réglage sauvegardé et implémentation du renderer</x:v>
       </x:c>
       <x:c r="G175" s="19" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>Le réglage réduit les oscillations et tremblements dans le code. Comparaison visuelle complète encore à mener.</x:v>
       </x:c>
       <x:c r="H175" s="19" t="str">
-        <x:v>Earned progression and settings survive a page reload</x:v>
+        <x:v>Effets réduits sans perte de signaux de combat.</x:v>
       </x:c>
       <x:c r="I175" s="20" t="str"/>
     </x:row>
     <x:row r="176" ht="29" customHeight="1">
       <x:c r="A176" s="18" t="str">
-        <x:v>QA-PRG-07</x:v>
+        <x:v>QA-fps</x:v>
       </x:c>
       <x:c r="B176" s="18" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Performance</x:v>
       </x:c>
       <x:c r="C176" s="18" t="str">
-        <x:v>Malformed profile, JSON and packed replay inputs are rejected without data loss</x:v>
+        <x:v>Mesurer plusieurs matchs sur matériel modeste</x:v>
       </x:c>
       <x:c r="D176" s="18" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>Non exécuté</x:v>
       </x:c>
       <x:c r="E176" s="18" t="str">
-        <x:v>P0</x:v>
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="F176" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
-      </x:c>
-      <x:c r="G176" s="18" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP</x:v>
-      </x:c>
+        <x:v>Parcours navigateur ou matériel réel</x:v>
+      </x:c>
+      <x:c r="G176" s="18" t="str"/>
       <x:c r="H176" s="18" t="str">
-        <x:v>Malformed profile, JSON and packed replay inputs are rejected without data loss</x:v>
+        <x:v>Cadence et mémoire stables après plusieurs reprises.</x:v>
       </x:c>
       <x:c r="I176" s="20" t="str"/>
     </x:row>
     <x:row r="177" ht="32" customHeight="1">
       <x:c r="A177" s="19" t="str">
-        <x:v>QA-PRG-08</x:v>
+        <x:v>QA-build</x:v>
       </x:c>
       <x:c r="B177" s="19" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Distribution</x:v>
       </x:c>
       <x:c r="C177" s="19" t="str">
-        <x:v>Pure scheduling contract: 6 Arcade, 4 Boss and 10 Survival encounters</x:v>
+        <x:v>Servir les deux builds générés</x:v>
       </x:c>
       <x:c r="D177" s="19" t="str">
-        <x:v>Réussi</x:v>
+        <x:v>À vérifier</x:v>
       </x:c>
       <x:c r="E177" s="19" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F177" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>npm run qa / tests/combat-progression-browser.mjs / tests/combat-offline-browser.mjs</x:v>
       </x:c>
       <x:c r="G177" s="19" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · Not a claim that all final medals were earned through UI</x:v>
+        <x:v>Deux builds générés. Le standalone compilé est servi sur une origine séparée, testé en ligne puis hors ligne. CainOS est vérifié depuis le répertoire source ; le dossier dist OS reste à servir séparément.</x:v>
       </x:c>
       <x:c r="H177" s="19" t="str">
-        <x:v>Contrat de longueur des parcours. Les parcours classiques ne sont pas revendiqués comme terminés intégralement dans le navigateur.</x:v>
+        <x:v>Aucune ressource requise absente.</x:v>
       </x:c>
       <x:c r="I177" s="20" t="str"/>
     </x:row>
-    <x:row r="178" ht="29" customHeight="1">
+    <x:row r="178" ht="32" customHeight="1">
       <x:c r="A178" s="18" t="str">
-        <x:v>QA-PRG-09</x:v>
+        <x:v>QA-regression</x:v>
       </x:c>
       <x:c r="B178" s="18" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Régression</x:v>
       </x:c>
       <x:c r="C178" s="18" t="str">
-        <x:v>Built standalone plays on a second origin without the OS runtime</x:v>
+        <x:v>Exécuter les audits CainOS existants</x:v>
       </x:c>
       <x:c r="D178" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44869,25 +44923,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F178" s="18" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>npm run qa + sept TAP canoniques audit-combat/combat-*.test.tap</x:v>
       </x:c>
       <x:c r="G178" s="18" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · 26 local resources</x:v>
+        <x:v>22 octobre 2026 : audits CainOS et deux builds réexécutés avec succès après correction ; 141 cas Node réussis dans sept suites. Pack hors ligne : 42 planches originales, 47 345 031 octets.</x:v>
       </x:c>
       <x:c r="H178" s="18" t="str">
-        <x:v>Built standalone plays on a second origin without the OS runtime</x:v>
+        <x:v>Aucune régression des contrats existants.</x:v>
       </x:c>
       <x:c r="I178" s="20" t="str"/>
     </x:row>
-    <x:row r="179" ht="32" customHeight="1">
+    <x:row r="179" ht="45" customHeight="1">
       <x:c r="A179" s="19" t="str">
-        <x:v>QA-PRG-10</x:v>
+        <x:v>QA-tracker-proof</x:v>
       </x:c>
       <x:c r="B179" s="19" t="str">
-        <x:v>Progression réelle</x:v>
+        <x:v>Production du suivi</x:v>
       </x:c>
       <x:c r="C179" s="19" t="str">
-        <x:v>Denied storage retains two rewards for export; terminal dialogs survive Escape</x:v>
+        <x:v>Refuser une preuve corrompue avant génération</x:v>
       </x:c>
       <x:c r="D179" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44896,25 +44950,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F179" s="19" t="str">
-        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+        <x:v>Builder exécuté avec un répertoire temporaire isolé et un classeur sentinelle existant</x:v>
       </x:c>
       <x:c r="G179" s="19" t="str">
-        <x:v>22 octobre 2026 · 10/10 contrôles, 0 erreur JS/HTTP · Specialist → Super via real controls; sound and both rewards survive setItem failure; Escape preserves the result actions twice</x:v>
+        <x:v>22 octobre 2026 : JSON malformé (SyntaxError), valeur null (schéma invalide) et lecture d’un répertoire (EISDIR) rejetés. Le fichier Excel préexistant est inchangé dans les trois cas. Seule l’absence ENOENT est facultative.</x:v>
       </x:c>
       <x:c r="H179" s="19" t="str">
-        <x:v>Denied storage retains two rewards for export; terminal dialogs survive Escape</x:v>
+        <x:v>JSON invalide, type invalide et erreurs de lecture sont rejetés ; le fichier Excel existant est préservé.</x:v>
       </x:c>
       <x:c r="I179" s="20" t="str"/>
     </x:row>
-    <x:row r="180" ht="32" customHeight="1">
+    <x:row r="180" ht="29" customHeight="1">
       <x:c r="A180" s="18" t="str">
-        <x:v>QA-ENC-01</x:v>
+        <x:v>QA-UI-01</x:v>
       </x:c>
       <x:c r="B180" s="18" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C180" s="18" t="str">
-        <x:v>Story victory checkpoint reloads into chapter 2 without a duplicate reward</x:v>
+        <x:v>Nine modes and standalone home render</x:v>
       </x:c>
       <x:c r="D180" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44923,25 +44977,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F180" s="18" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G180" s="18" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · Jax’s first duel is genuinely won; the second scene and its original starting health survive reload</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H180" s="18" t="str">
-        <x:v>Story victory checkpoint reloads into chapter 2 without a duplicate reward</x:v>
+        <x:v>Nine modes and standalone home render</x:v>
       </x:c>
       <x:c r="I180" s="20" t="str"/>
     </x:row>
-    <x:row r="181" ht="32" customHeight="1">
+    <x:row r="181" ht="29" customHeight="1">
       <x:c r="A181" s="19" t="str">
-        <x:v>QA-ENC-02</x:v>
+        <x:v>QA-UI-02</x:v>
       </x:c>
       <x:c r="B181" s="19" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C181" s="19" t="str">
-        <x:v>Four genuine Jax story wins show all authored scenes, unique ending and earned story medal</x:v>
+        <x:v>Codex changes fighter and shows ten authored moves</x:v>
       </x:c>
       <x:c r="D181" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -44950,25 +45004,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F181" s="19" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G181" s="19" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · Gangle → Zooble → Ragatha → Caine; profile records four wins, one completed route and no remaining checkpoint</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H181" s="19" t="str">
-        <x:v>Four genuine Jax story wins show all authored scenes, unique ending and earned story medal</x:v>
+        <x:v>Codex changes fighter and shows ten authored moves</x:v>
       </x:c>
       <x:c r="I181" s="20" t="str"/>
     </x:row>
-    <x:row r="182" ht="32" customHeight="1">
+    <x:row r="182" ht="29" customHeight="1">
       <x:c r="A182" s="18" t="str">
-        <x:v>QA-ENC-03</x:v>
+        <x:v>QA-UI-03</x:v>
       </x:c>
       <x:c r="B182" s="18" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C182" s="18" t="str">
-        <x:v>Seeded tournament import displays eight artists and seven real bracket slots</x:v>
+        <x:v>Archive search filters real records</x:v>
       </x:c>
       <x:c r="D182" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -44977,25 +45031,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F182" s="18" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G182" s="18" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · Fixture has zero player results; three quarter-finals are explicitly identified as CPU simulations</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H182" s="18" t="str">
-        <x:v>Seeded tournament import displays eight artists and seven real bracket slots</x:v>
+        <x:v>Archive search filters real records</x:v>
       </x:c>
       <x:c r="I182" s="20" t="str"/>
     </x:row>
-    <x:row r="183" ht="32" customHeight="1">
+    <x:row r="183" ht="29" customHeight="1">
       <x:c r="A183" s="19" t="str">
-        <x:v>QA-ENC-04</x:v>
+        <x:v>QA-UI-04</x:v>
       </x:c>
       <x:c r="B183" s="19" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C183" s="19" t="str">
-        <x:v>Tournament bracket and semifinal resume after a real quarter-final win</x:v>
+        <x:v>Settings persist across reload</x:v>
       </x:c>
       <x:c r="D183" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45004,25 +45058,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F183" s="19" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G183" s="19" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · Same participants, CPU outcomes, next rival and rules; profile match count remains unchanged by reload</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H183" s="19" t="str">
-        <x:v>Tournament bracket and semifinal resume after a real quarter-final win</x:v>
+        <x:v>Settings persist across reload</x:v>
       </x:c>
       <x:c r="I183" s="20" t="str"/>
     </x:row>
-    <x:row r="184" ht="32" customHeight="1">
+    <x:row r="184" ht="29" customHeight="1">
       <x:c r="A184" s="18" t="str">
-        <x:v>QA-ENC-05</x:v>
+        <x:v>QA-UI-05</x:v>
       </x:c>
       <x:c r="B184" s="18" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C184" s="18" t="str">
-        <x:v>Three genuine tournament wins earn the cup and the tournament medal</x:v>
+        <x:v>Training loads and responds to keyboard movement/attack</x:v>
       </x:c>
       <x:c r="D184" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45031,25 +45085,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F184" s="18" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G184" s="18" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · Seven resolved matches: three played by the keyboard user and four explicitly simulated CPU matches</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H184" s="18" t="str">
-        <x:v>Three genuine tournament wins earn the cup and the tournament medal</x:v>
+        <x:v>Training loads and responds to keyboard movement/attack</x:v>
       </x:c>
       <x:c r="I184" s="20" t="str"/>
     </x:row>
-    <x:row r="185" ht="32" customHeight="1">
+    <x:row r="185" ht="29" customHeight="1">
       <x:c r="A185" s="19" t="str">
-        <x:v>QA-ENC-06</x:v>
+        <x:v>QA-UI-06</x:v>
       </x:c>
       <x:c r="B185" s="19" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C185" s="19" t="str">
-        <x:v>Tournament loss eliminates without a medal; replay starts a fresh bracket attempt</x:v>
+        <x:v>Pause stops simulation and resume restarts</x:v>
       </x:c>
       <x:c r="D185" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45058,25 +45112,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F185" s="19" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G185" s="19" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · The real CPU wins; remaining results are simulated and retry resets index/results while preserving the recorded loss</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H185" s="19" t="str">
-        <x:v>Tournament loss eliminates without a medal; replay starts a fresh bracket attempt</x:v>
+        <x:v>Pause stops simulation and resume restarts</x:v>
       </x:c>
       <x:c r="I185" s="20" t="str"/>
     </x:row>
-    <x:row r="186" ht="32" customHeight="1">
+    <x:row r="186" ht="29" customHeight="1">
       <x:c r="A186" s="18" t="str">
-        <x:v>QA-ENC-07</x:v>
+        <x:v>QA-UI-07</x:v>
       </x:c>
       <x:c r="B186" s="18" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C186" s="18" t="str">
-        <x:v>Story defeat and retry retain the genuinely earned previous chapter, including after reload</x:v>
+        <x:v>Move list pauses and resumes the current encounter</x:v>
       </x:c>
       <x:c r="D186" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45085,25 +45139,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F186" s="18" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G186" s="18" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · The second chapter restarts with unchanged seed/rival/full health; the first victory and the later loss are each counted once</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H186" s="18" t="str">
-        <x:v>Story defeat and retry retain the genuinely earned previous chapter, including after reload</x:v>
+        <x:v>Move list pauses and resumes the current encounter</x:v>
       </x:c>
       <x:c r="I186" s="20" t="str"/>
     </x:row>
-    <x:row r="187" ht="32" customHeight="1">
+    <x:row r="187" ht="29" customHeight="1">
       <x:c r="A187" s="19" t="str">
-        <x:v>QA-ENC-08</x:v>
+        <x:v>QA-UI-08</x:v>
       </x:c>
       <x:c r="B187" s="19" t="str">
-        <x:v>Histoires et tournoi</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C187" s="19" t="str">
-        <x:v>Replacing a saved programme requires the visible UI choice and preserves the existing record</x:v>
+        <x:v>Player 2 has independent local controls</x:v>
       </x:c>
       <x:c r="D187" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45112,25 +45166,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F187" s="19" t="str">
-        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G187" s="19" t="str">
-        <x:v>22 octobre 2026 · 8/8 contrôles, 0 erreur JS/HTTP, 9 duels joués · Cancel leaves the story checkpoint intact; start-new replaces only the active route</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H187" s="19" t="str">
-        <x:v>Replacing a saved programme requires the visible UI choice and preserves the existing record</x:v>
+        <x:v>Player 2 has independent local controls</x:v>
       </x:c>
       <x:c r="I187" s="20" t="str"/>
     </x:row>
     <x:row r="188" ht="29" customHeight="1">
       <x:c r="A188" s="18" t="str">
-        <x:v>QA-OFF-01</x:v>
+        <x:v>QA-UI-09</x:v>
       </x:c>
       <x:c r="B188" s="18" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C188" s="18" t="str">
-        <x:v>Custom keys reject conflicts and reserved shortcuts, allow alternatives, and persist</x:v>
+        <x:v>Challenge completion persists an earned result</x:v>
       </x:c>
       <x:c r="D188" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45139,25 +45193,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F188" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G188" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP · J1 light = F; labels follow AZERTY/QWERTY</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H188" s="18" t="str">
-        <x:v>Custom keys reject conflicts and reserved shortcuts, allow alternatives, and persist</x:v>
+        <x:v>Challenge completion persists an earned result</x:v>
       </x:c>
       <x:c r="I188" s="20" t="str"/>
     </x:row>
     <x:row r="189" ht="29" customHeight="1">
       <x:c r="A189" s="19" t="str">
-        <x:v>QA-OFF-02</x:v>
+        <x:v>QA-UI-10</x:v>
       </x:c>
       <x:c r="B189" s="19" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C189" s="19" t="str">
-        <x:v>Original procedural music starts from a gesture with an independent mute</x:v>
+        <x:v>CainOS desktop launches the shared game and minimizing pauses it</x:v>
       </x:c>
       <x:c r="D189" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45166,25 +45220,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F189" s="19" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G189" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP · Effects off; music on; bounded voices</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H189" s="19" t="str">
-        <x:v>Original procedural music starts from a gesture with an independent mute</x:v>
+        <x:v>CainOS desktop launches the shared game and minimizing pauses it</x:v>
       </x:c>
       <x:c r="I189" s="20" t="str"/>
     </x:row>
     <x:row r="190" ht="29" customHeight="1">
       <x:c r="A190" s="18" t="str">
-        <x:v>QA-OFF-03</x:v>
+        <x:v>QA-UI-11</x:v>
       </x:c>
       <x:c r="B190" s="18" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Interface réelle</x:v>
       </x:c>
       <x:c r="C190" s="18" t="str">
-        <x:v>Remapped attack reaches the engine and move list while the old key stays inactive</x:v>
+        <x:v>390px mobile layout and touch attack work without horizontal overflow</x:v>
       </x:c>
       <x:c r="D190" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45193,25 +45247,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F190" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G190" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H190" s="18" t="str">
-        <x:v>Remapped attack reaches the engine and move list while the old key stays inactive</x:v>
+        <x:v>390px mobile layout and touch attack work without horizontal overflow</x:v>
       </x:c>
       <x:c r="I190" s="20" t="str"/>
     </x:row>
-    <x:row r="191" ht="29" customHeight="1">
+    <x:row r="191" ht="32" customHeight="1">
       <x:c r="A191" s="19" t="str">
-        <x:v>QA-OFF-04</x:v>
+        <x:v>QA-PRG-01</x:v>
       </x:c>
       <x:c r="B191" s="19" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C191" s="19" t="str">
-        <x:v>Live combo label clears after recovery while the best result combo remains</x:v>
+        <x:v>A real local match saves its result and replay</x:v>
       </x:c>
       <x:c r="D191" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45220,25 +45274,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F191" s="19" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G191" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · 2282 simulation frames, 611 input runs</x:v>
       </x:c>
       <x:c r="H191" s="19" t="str">
-        <x:v>Live combo label clears after recovery while the best result combo remains</x:v>
+        <x:v>A real local match saves its result and replay</x:v>
       </x:c>
       <x:c r="I191" s="20" t="str"/>
     </x:row>
     <x:row r="192" ht="29" customHeight="1">
       <x:c r="A192" s="18" t="str">
-        <x:v>QA-OFF-05</x:v>
+        <x:v>QA-PRG-02</x:v>
       </x:c>
       <x:c r="B192" s="18" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C192" s="18" t="str">
-        <x:v>Pause stops simulation and releases audio voices; resume restores the stage theme</x:v>
+        <x:v>UI replay reproduces the full terminal snapshot without changing profile</x:v>
       </x:c>
       <x:c r="D192" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45247,25 +45301,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F192" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G192" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H192" s="18" t="str">
-        <x:v>Pause stops simulation and releases audio voices; resume restores the stage theme</x:v>
+        <x:v>UI replay reproduces the full terminal snapshot without changing profile</x:v>
       </x:c>
       <x:c r="I192" s="20" t="str"/>
     </x:row>
     <x:row r="193" ht="32" customHeight="1">
       <x:c r="A193" s="19" t="str">
-        <x:v>QA-OFF-06</x:v>
+        <x:v>QA-PRG-03</x:v>
       </x:c>
       <x:c r="B193" s="19" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C193" s="19" t="str">
-        <x:v>The standalone downloads all 42 original sprite sheets</x:v>
+        <x:v>arcade: earned first win opens encounter 2/6</x:v>
       </x:c>
       <x:c r="D193" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45274,25 +45328,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F193" s="19" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G193" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP · 47,345,031 bytes; explicit UI action and completion state</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · bubble → pomni, player HP 8688 → 10000</x:v>
       </x:c>
       <x:c r="H193" s="19" t="str">
-        <x:v>The standalone downloads all 42 original sprite sheets</x:v>
+        <x:v>arcade: earned first win opens encounter 2/6</x:v>
       </x:c>
       <x:c r="I193" s="20" t="str"/>
     </x:row>
     <x:row r="194" ht="32" customHeight="1">
       <x:c r="A194" s="18" t="str">
-        <x:v>QA-OFF-07</x:v>
+        <x:v>QA-PRG-04</x:v>
       </x:c>
       <x:c r="B194" s="18" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C194" s="18" t="str">
-        <x:v>A cold page reload and a different fighter/stage remain playable offline</x:v>
+        <x:v>boss: earned first win opens encounter 2/4</x:v>
       </x:c>
       <x:c r="D194" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45301,25 +45355,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F194" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G194" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP · Network disabled; profile preserved; real keyboard movement</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · gloinkqueen → fudge, player HP 10000 → 10000</x:v>
       </x:c>
       <x:c r="H194" s="18" t="str">
-        <x:v>A cold page reload and a different fighter/stage remain playable offline</x:v>
+        <x:v>boss: earned first win opens encounter 2/4</x:v>
       </x:c>
       <x:c r="I194" s="20" t="str"/>
     </x:row>
     <x:row r="195" ht="32" customHeight="1">
       <x:c r="A195" s="19" t="str">
-        <x:v>QA-OFF-08</x:v>
+        <x:v>QA-PRG-05</x:v>
       </x:c>
       <x:c r="B195" s="19" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C195" s="19" t="str">
-        <x:v>A waiting service worker updates only through the UI and preserves the unchanged art pack</x:v>
+        <x:v>survival: earned first win opens encounter 2/10</x:v>
       </x:c>
       <x:c r="D195" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45328,25 +45382,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F195" s="19" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G195" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP · No automatic reload; all 42 images and the profile survive activation</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · pomni → abstractedkaufmo, player HP 8656 → 9856</x:v>
       </x:c>
       <x:c r="H195" s="19" t="str">
-        <x:v>A waiting service worker updates only through the UI and preserves the unchanged art pack</x:v>
+        <x:v>survival: earned first win opens encounter 2/10</x:v>
       </x:c>
       <x:c r="I195" s="20" t="str"/>
     </x:row>
     <x:row r="196" ht="29" customHeight="1">
       <x:c r="A196" s="18" t="str">
-        <x:v>QA-OFF-09</x:v>
+        <x:v>QA-PRG-06</x:v>
       </x:c>
       <x:c r="B196" s="18" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C196" s="18" t="str">
-        <x:v>The offline worker is limited to /combat/ and leaves other application documents uncontrolled</x:v>
+        <x:v>Earned progression and settings survive a page reload</x:v>
       </x:c>
       <x:c r="D196" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45355,25 +45409,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F196" s="18" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G196" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H196" s="18" t="str">
-        <x:v>The offline worker is limited to /combat/ and leaves other application documents uncontrolled</x:v>
+        <x:v>Earned progression and settings survive a page reload</x:v>
       </x:c>
       <x:c r="I196" s="20" t="str"/>
     </x:row>
     <x:row r="197" ht="29" customHeight="1">
       <x:c r="A197" s="19" t="str">
-        <x:v>QA-OFF-10</x:v>
+        <x:v>QA-PRG-07</x:v>
       </x:c>
       <x:c r="B197" s="19" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C197" s="19" t="str">
-        <x:v>Clearing downloaded illustrations preserves custom keys and all profile data</x:v>
+        <x:v>Malformed profile, JSON and packed replay inputs are rejected without data loss</x:v>
       </x:c>
       <x:c r="D197" s="19" t="str">
         <x:v>Réussi</x:v>
@@ -45382,25 +45436,25 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F197" s="19" t="str">
-        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
       </x:c>
       <x:c r="G197" s="19" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP</x:v>
       </x:c>
       <x:c r="H197" s="19" t="str">
-        <x:v>Clearing downloaded illustrations preserves custom keys and all profile data</x:v>
+        <x:v>Malformed profile, JSON and packed replay inputs are rejected without data loss</x:v>
       </x:c>
       <x:c r="I197" s="20" t="str"/>
     </x:row>
-    <x:row r="198" ht="29" customHeight="1">
+    <x:row r="198" ht="32" customHeight="1">
       <x:c r="A198" s="18" t="str">
-        <x:v>QA-OFF-11</x:v>
+        <x:v>QA-PRG-08</x:v>
       </x:c>
       <x:c r="B198" s="18" t="str">
-        <x:v>Hors ligne et réglages</x:v>
+        <x:v>Progression réelle</x:v>
       </x:c>
       <x:c r="C198" s="18" t="str">
-        <x:v>The expanded settings and key mapper fit a 390-pixel viewport</x:v>
+        <x:v>Pure scheduling contract: 6 Arcade, 4 Boss and 10 Survival encounters</x:v>
       </x:c>
       <x:c r="D198" s="18" t="str">
         <x:v>Réussi</x:v>
@@ -45409,18 +45463,801 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="F198" s="18" t="str">
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G198" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · Not a claim that all final medals were earned through UI</x:v>
+      </x:c>
+      <x:c r="H198" s="18" t="str">
+        <x:v>Contrat de longueur des parcours uniquement. Les médailles finales n’ont pas été jouées dans le navigateur.</x:v>
+      </x:c>
+      <x:c r="I198" s="20" t="str"/>
+    </x:row>
+    <x:row r="199" ht="32" customHeight="1">
+      <x:c r="A199" s="19" t="str">
+        <x:v>QA-PRG-09</x:v>
+      </x:c>
+      <x:c r="B199" s="19" t="str">
+        <x:v>Progression réelle</x:v>
+      </x:c>
+      <x:c r="C199" s="19" t="str">
+        <x:v>Built standalone plays on a second origin without the OS runtime</x:v>
+      </x:c>
+      <x:c r="D199" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E199" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F199" s="19" t="str">
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G199" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · 26 local resources</x:v>
+      </x:c>
+      <x:c r="H199" s="19" t="str">
+        <x:v>Built standalone plays on a second origin without the OS runtime</x:v>
+      </x:c>
+      <x:c r="I199" s="20" t="str"/>
+    </x:row>
+    <x:row r="200" ht="45" customHeight="1">
+      <x:c r="A200" s="18" t="str">
+        <x:v>QA-PRG-10</x:v>
+      </x:c>
+      <x:c r="B200" s="18" t="str">
+        <x:v>Progression réelle</x:v>
+      </x:c>
+      <x:c r="C200" s="18" t="str">
+        <x:v>Denied storage retains two rewards for export; terminal dialogs survive Escape</x:v>
+      </x:c>
+      <x:c r="D200" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E200" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F200" s="18" t="str">
+        <x:v>node tests/combat-progression-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G200" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 10/10 contrôles, 0 erreur JS/HTTP · Specialist → Super via real controls; sound and both rewards survive setItem failure; Escape preserves the result actions twice</x:v>
+      </x:c>
+      <x:c r="H200" s="18" t="str">
+        <x:v>Denied storage retains two rewards for export; terminal dialogs survive Escape</x:v>
+      </x:c>
+      <x:c r="I200" s="20" t="str"/>
+    </x:row>
+    <x:row r="201" ht="32" customHeight="1">
+      <x:c r="A201" s="19" t="str">
+        <x:v>QA-ENC-01</x:v>
+      </x:c>
+      <x:c r="B201" s="19" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C201" s="19" t="str">
+        <x:v>Story victory checkpoint reloads into chapter 2 without a duplicate reward</x:v>
+      </x:c>
+      <x:c r="D201" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E201" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F201" s="19" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G201" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · Jax’s first duel is genuinely won; the second scene and its original starting health survive reload</x:v>
+      </x:c>
+      <x:c r="H201" s="19" t="str">
+        <x:v>Story victory checkpoint reloads into chapter 2 without a duplicate reward</x:v>
+      </x:c>
+      <x:c r="I201" s="20" t="str"/>
+    </x:row>
+    <x:row r="202" ht="32" customHeight="1">
+      <x:c r="A202" s="18" t="str">
+        <x:v>QA-ENC-02</x:v>
+      </x:c>
+      <x:c r="B202" s="18" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C202" s="18" t="str">
+        <x:v>Four genuine Jax story wins show all authored scenes, unique ending and earned story medal</x:v>
+      </x:c>
+      <x:c r="D202" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E202" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F202" s="18" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G202" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · Gangle → Zooble → Ragatha → Caine; profile records four wins, one completed route and no remaining checkpoint</x:v>
+      </x:c>
+      <x:c r="H202" s="18" t="str">
+        <x:v>Four genuine Jax story wins show all authored scenes, unique ending and earned story medal</x:v>
+      </x:c>
+      <x:c r="I202" s="20" t="str"/>
+    </x:row>
+    <x:row r="203" ht="32" customHeight="1">
+      <x:c r="A203" s="19" t="str">
+        <x:v>QA-ENC-03</x:v>
+      </x:c>
+      <x:c r="B203" s="19" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C203" s="19" t="str">
+        <x:v>Seeded tournament import displays eight artists and seven real bracket slots</x:v>
+      </x:c>
+      <x:c r="D203" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E203" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F203" s="19" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G203" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · Fixture has zero player results; three quarter-finals are explicitly identified as CPU simulations</x:v>
+      </x:c>
+      <x:c r="H203" s="19" t="str">
+        <x:v>Seeded tournament import displays eight artists and seven real bracket slots</x:v>
+      </x:c>
+      <x:c r="I203" s="20" t="str"/>
+    </x:row>
+    <x:row r="204" ht="32" customHeight="1">
+      <x:c r="A204" s="18" t="str">
+        <x:v>QA-ENC-04</x:v>
+      </x:c>
+      <x:c r="B204" s="18" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C204" s="18" t="str">
+        <x:v>Tournament bracket and semifinal resume after a real quarter-final win</x:v>
+      </x:c>
+      <x:c r="D204" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E204" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F204" s="18" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G204" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · Same participants, CPU outcomes, next rival and rules; profile match count remains unchanged by reload</x:v>
+      </x:c>
+      <x:c r="H204" s="18" t="str">
+        <x:v>Tournament bracket and semifinal resume after a real quarter-final win</x:v>
+      </x:c>
+      <x:c r="I204" s="20" t="str"/>
+    </x:row>
+    <x:row r="205" ht="32" customHeight="1">
+      <x:c r="A205" s="19" t="str">
+        <x:v>QA-ENC-05</x:v>
+      </x:c>
+      <x:c r="B205" s="19" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C205" s="19" t="str">
+        <x:v>Three genuine tournament wins earn the cup and the tournament medal</x:v>
+      </x:c>
+      <x:c r="D205" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E205" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F205" s="19" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G205" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · Seven resolved matches: three played by the keyboard user and four explicitly simulated CPU matches</x:v>
+      </x:c>
+      <x:c r="H205" s="19" t="str">
+        <x:v>Three genuine tournament wins earn the cup and the tournament medal</x:v>
+      </x:c>
+      <x:c r="I205" s="20" t="str"/>
+    </x:row>
+    <x:row r="206" ht="45" customHeight="1">
+      <x:c r="A206" s="18" t="str">
+        <x:v>QA-ENC-06</x:v>
+      </x:c>
+      <x:c r="B206" s="18" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C206" s="18" t="str">
+        <x:v>Tournament loss eliminates without a medal; replay starts a fresh bracket attempt</x:v>
+      </x:c>
+      <x:c r="D206" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E206" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F206" s="18" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G206" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · The real CPU wins; remaining results are simulated and retry resets index/results while preserving the recorded loss</x:v>
+      </x:c>
+      <x:c r="H206" s="18" t="str">
+        <x:v>Tournament loss eliminates without a medal; replay starts a fresh bracket attempt</x:v>
+      </x:c>
+      <x:c r="I206" s="20" t="str"/>
+    </x:row>
+    <x:row r="207" ht="45" customHeight="1">
+      <x:c r="A207" s="19" t="str">
+        <x:v>QA-ENC-07</x:v>
+      </x:c>
+      <x:c r="B207" s="19" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C207" s="19" t="str">
+        <x:v>Story defeat and retry retain the genuinely earned previous chapter, including after reload</x:v>
+      </x:c>
+      <x:c r="D207" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E207" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F207" s="19" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G207" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · The second chapter restarts with unchanged seed/rival/full health; the first victory and the later loss are each counted once</x:v>
+      </x:c>
+      <x:c r="H207" s="19" t="str">
+        <x:v>Story defeat and retry retain the genuinely earned previous chapter, including after reload</x:v>
+      </x:c>
+      <x:c r="I207" s="20" t="str"/>
+    </x:row>
+    <x:row r="208" ht="32" customHeight="1">
+      <x:c r="A208" s="18" t="str">
+        <x:v>QA-ENC-08</x:v>
+      </x:c>
+      <x:c r="B208" s="18" t="str">
+        <x:v>Histoires et tournoi</x:v>
+      </x:c>
+      <x:c r="C208" s="18" t="str">
+        <x:v>Replacing a saved programme requires the visible UI choice and preserves the existing record</x:v>
+      </x:c>
+      <x:c r="D208" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E208" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F208" s="18" t="str">
+        <x:v>node tests/combat-encore-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G208" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 8/8 contrôles, 0 erreur JS/HTTP · Cancel leaves the story checkpoint intact; start-new replaces only the active route</x:v>
+      </x:c>
+      <x:c r="H208" s="18" t="str">
+        <x:v>Replacing a saved programme requires the visible UI choice and preserves the existing record</x:v>
+      </x:c>
+      <x:c r="I208" s="20" t="str"/>
+    </x:row>
+    <x:row r="209" ht="32" customHeight="1">
+      <x:c r="A209" s="19" t="str">
+        <x:v>QA-OFF-01</x:v>
+      </x:c>
+      <x:c r="B209" s="19" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C209" s="19" t="str">
+        <x:v>Custom keys reject conflicts and reserved shortcuts, allow alternatives, and persist</x:v>
+      </x:c>
+      <x:c r="D209" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E209" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F209" s="19" t="str">
         <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
       </x:c>
-      <x:c r="G198" s="18" t="str">
-        <x:v>22 octobre 2026 · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
-      </x:c>
-      <x:c r="H198" s="18" t="str">
+      <x:c r="G209" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP · J1 light = F; labels follow AZERTY/QWERTY</x:v>
+      </x:c>
+      <x:c r="H209" s="19" t="str">
+        <x:v>Custom keys reject conflicts and reserved shortcuts, allow alternatives, and persist</x:v>
+      </x:c>
+      <x:c r="I209" s="20" t="str"/>
+    </x:row>
+    <x:row r="210" ht="32" customHeight="1">
+      <x:c r="A210" s="18" t="str">
+        <x:v>QA-OFF-02</x:v>
+      </x:c>
+      <x:c r="B210" s="18" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C210" s="18" t="str">
+        <x:v>Original procedural music starts from a gesture with an independent mute</x:v>
+      </x:c>
+      <x:c r="D210" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E210" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F210" s="18" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G210" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP · Effects off; music on; bounded voices</x:v>
+      </x:c>
+      <x:c r="H210" s="18" t="str">
+        <x:v>Original procedural music starts from a gesture with an independent mute</x:v>
+      </x:c>
+      <x:c r="I210" s="20" t="str"/>
+    </x:row>
+    <x:row r="211" ht="29" customHeight="1">
+      <x:c r="A211" s="19" t="str">
+        <x:v>QA-OFF-03</x:v>
+      </x:c>
+      <x:c r="B211" s="19" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C211" s="19" t="str">
+        <x:v>Remapped attack reaches the engine and move list while the old key stays inactive</x:v>
+      </x:c>
+      <x:c r="D211" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E211" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F211" s="19" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G211" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+      </x:c>
+      <x:c r="H211" s="19" t="str">
+        <x:v>Remapped attack reaches the engine and move list while the old key stays inactive</x:v>
+      </x:c>
+      <x:c r="I211" s="20" t="str"/>
+    </x:row>
+    <x:row r="212" ht="29" customHeight="1">
+      <x:c r="A212" s="18" t="str">
+        <x:v>QA-OFF-04</x:v>
+      </x:c>
+      <x:c r="B212" s="18" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C212" s="18" t="str">
+        <x:v>Live combo label clears after recovery while the best result combo remains</x:v>
+      </x:c>
+      <x:c r="D212" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E212" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F212" s="18" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G212" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+      </x:c>
+      <x:c r="H212" s="18" t="str">
+        <x:v>Live combo label clears after recovery while the best result combo remains</x:v>
+      </x:c>
+      <x:c r="I212" s="20" t="str"/>
+    </x:row>
+    <x:row r="213" ht="29" customHeight="1">
+      <x:c r="A213" s="19" t="str">
+        <x:v>QA-OFF-05</x:v>
+      </x:c>
+      <x:c r="B213" s="19" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C213" s="19" t="str">
+        <x:v>Pause stops simulation and releases audio voices; resume restores the stage theme</x:v>
+      </x:c>
+      <x:c r="D213" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E213" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F213" s="19" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G213" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+      </x:c>
+      <x:c r="H213" s="19" t="str">
+        <x:v>Pause stops simulation and releases audio voices; resume restores the stage theme</x:v>
+      </x:c>
+      <x:c r="I213" s="20" t="str"/>
+    </x:row>
+    <x:row r="214" ht="32" customHeight="1">
+      <x:c r="A214" s="18" t="str">
+        <x:v>QA-OFF-06</x:v>
+      </x:c>
+      <x:c r="B214" s="18" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C214" s="18" t="str">
+        <x:v>The standalone downloads all 42 original sprite sheets</x:v>
+      </x:c>
+      <x:c r="D214" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E214" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F214" s="18" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G214" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP · 47,345,031 bytes; explicit UI action and completion state</x:v>
+      </x:c>
+      <x:c r="H214" s="18" t="str">
+        <x:v>The standalone downloads all 42 original sprite sheets</x:v>
+      </x:c>
+      <x:c r="I214" s="20" t="str"/>
+    </x:row>
+    <x:row r="215" ht="32" customHeight="1">
+      <x:c r="A215" s="19" t="str">
+        <x:v>QA-OFF-07</x:v>
+      </x:c>
+      <x:c r="B215" s="19" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C215" s="19" t="str">
+        <x:v>A cold page reload and a different fighter/stage remain playable offline</x:v>
+      </x:c>
+      <x:c r="D215" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E215" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F215" s="19" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G215" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP · Network disabled; profile preserved; real keyboard movement</x:v>
+      </x:c>
+      <x:c r="H215" s="19" t="str">
+        <x:v>A cold page reload and a different fighter/stage remain playable offline</x:v>
+      </x:c>
+      <x:c r="I215" s="20" t="str"/>
+    </x:row>
+    <x:row r="216" ht="32" customHeight="1">
+      <x:c r="A216" s="18" t="str">
+        <x:v>QA-OFF-08</x:v>
+      </x:c>
+      <x:c r="B216" s="18" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C216" s="18" t="str">
+        <x:v>A waiting service worker updates only through the UI and preserves the unchanged art pack</x:v>
+      </x:c>
+      <x:c r="D216" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E216" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F216" s="18" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G216" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP · No automatic reload; all 42 images and the profile survive activation</x:v>
+      </x:c>
+      <x:c r="H216" s="18" t="str">
+        <x:v>A waiting service worker updates only through the UI and preserves the unchanged art pack</x:v>
+      </x:c>
+      <x:c r="I216" s="20" t="str"/>
+    </x:row>
+    <x:row r="217" ht="29" customHeight="1">
+      <x:c r="A217" s="19" t="str">
+        <x:v>QA-OFF-09</x:v>
+      </x:c>
+      <x:c r="B217" s="19" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C217" s="19" t="str">
+        <x:v>The offline worker is limited to /combat/ and leaves other application documents uncontrolled</x:v>
+      </x:c>
+      <x:c r="D217" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E217" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F217" s="19" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G217" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+      </x:c>
+      <x:c r="H217" s="19" t="str">
+        <x:v>The offline worker is limited to /combat/ and leaves other application documents uncontrolled</x:v>
+      </x:c>
+      <x:c r="I217" s="20" t="str"/>
+    </x:row>
+    <x:row r="218" ht="29" customHeight="1">
+      <x:c r="A218" s="18" t="str">
+        <x:v>QA-OFF-10</x:v>
+      </x:c>
+      <x:c r="B218" s="18" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C218" s="18" t="str">
+        <x:v>Clearing downloaded illustrations preserves custom keys and all profile data</x:v>
+      </x:c>
+      <x:c r="D218" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E218" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F218" s="18" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G218" s="18" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+      </x:c>
+      <x:c r="H218" s="18" t="str">
+        <x:v>Clearing downloaded illustrations preserves custom keys and all profile data</x:v>
+      </x:c>
+      <x:c r="I218" s="20" t="str"/>
+    </x:row>
+    <x:row r="219" ht="29" customHeight="1">
+      <x:c r="A219" s="19" t="str">
+        <x:v>QA-OFF-11</x:v>
+      </x:c>
+      <x:c r="B219" s="19" t="str">
+        <x:v>Hors ligne et réglages</x:v>
+      </x:c>
+      <x:c r="C219" s="19" t="str">
         <x:v>The expanded settings and key mapper fit a 390-pixel viewport</x:v>
       </x:c>
-      <x:c r="I198" s="20" t="str"/>
+      <x:c r="D219" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E219" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F219" s="19" t="str">
+        <x:v>node tests/combat-offline-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G219" s="19" t="str">
+        <x:v>22 octobre 2026 · suite complète réexécutée après correction · 11/11 contrôles, 0 erreur JS/HTTP</x:v>
+      </x:c>
+      <x:c r="H219" s="19" t="str">
+        <x:v>The expanded settings and key mapper fit a 390-pixel viewport</x:v>
+      </x:c>
+      <x:c r="I219" s="20" t="str"/>
+    </x:row>
+    <x:row r="220" ht="32" customHeight="1">
+      <x:c r="A220" s="18" t="str">
+        <x:v>QA-REC-01</x:v>
+      </x:c>
+      <x:c r="B220" s="18" t="str">
+        <x:v>Installation web</x:v>
+      </x:c>
+      <x:c r="C220" s="18" t="str">
+        <x:v>A failed first offline-cache installation exits preparation and exposes an enabled retry</x:v>
+      </x:c>
+      <x:c r="D220" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E220" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F220" s="18" t="str">
+        <x:v>node tests/combat-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G220" s="18" t="str">
+        <x:v>22 octobre 2026 · 3/3 contrôles, 0 erreur JS non attendue · Real HTTP 503 during cache.addAll; online settings remain usable</x:v>
+      </x:c>
+      <x:c r="H220" s="18" t="str">
+        <x:v>A failed first offline-cache installation exits preparation and exposes an enabled retry</x:v>
+      </x:c>
+      <x:c r="I220" s="20" t="str"/>
+    </x:row>
+    <x:row r="221" ht="32" customHeight="1">
+      <x:c r="A221" s="19" t="str">
+        <x:v>QA-REC-02</x:v>
+      </x:c>
+      <x:c r="B221" s="19" t="str">
+        <x:v>Installation web</x:v>
+      </x:c>
+      <x:c r="C221" s="19" t="str">
+        <x:v>The retry button registers a working service worker without reloading or losing the profile</x:v>
+      </x:c>
+      <x:c r="D221" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E221" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F221" s="19" t="str">
+        <x:v>node tests/combat-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G221" s="19" t="str">
+        <x:v>22 octobre 2026 · 3/3 contrôles, 0 erreur JS non attendue · Same page and profile; active /combat/ worker; initialization errors cleared</x:v>
+      </x:c>
+      <x:c r="H221" s="19" t="str">
+        <x:v>The retry button registers a working service worker without reloading or losing the profile</x:v>
+      </x:c>
+      <x:c r="I221" s="20" t="str"/>
+    </x:row>
+    <x:row r="222" ht="32" customHeight="1">
+      <x:c r="A222" s="18" t="str">
+        <x:v>QA-REC-03</x:v>
+      </x:c>
+      <x:c r="B222" s="18" t="str">
+        <x:v>Installation web</x:v>
+      </x:c>
+      <x:c r="C222" s="18" t="str">
+        <x:v>The recovered installation downloads the full pack and survives an offline cold reload</x:v>
+      </x:c>
+      <x:c r="D222" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E222" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F222" s="18" t="str">
+        <x:v>node tests/combat-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G222" s="18" t="str">
+        <x:v>22 octobre 2026 · 3/3 contrôles, 0 erreur JS non attendue · 42 illustrations; 47,345,031 bytes; profile preserved</x:v>
+      </x:c>
+      <x:c r="H222" s="18" t="str">
+        <x:v>The recovered installation downloads the full pack and survives an offline cold reload</x:v>
+      </x:c>
+      <x:c r="I222" s="20" t="str"/>
+    </x:row>
+    <x:row r="223" ht="32" customHeight="1">
+      <x:c r="A223" s="19" t="str">
+        <x:v>QA-RPRO-01</x:v>
+      </x:c>
+      <x:c r="B223" s="19" t="str">
+        <x:v>Récupération du profil</x:v>
+      </x:c>
+      <x:c r="C223" s="19" t="str">
+        <x:v>Startup drops only the corrupt checkpoint</x:v>
+      </x:c>
+      <x:c r="D223" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E223" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F223" s="19" t="str">
+        <x:v>node tests/combat-profile-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G223" s="19" t="str">
+        <x:v>22 octobre 2026 · 5/5 contrôles, 0 erreur JS non attendue · A migration fixture retains all statistics, challenges, medals, endings, history, preferences and both custom keyboard maps.</x:v>
+      </x:c>
+      <x:c r="H223" s="19" t="str">
+        <x:v>Startup drops only the corrupt checkpoint</x:v>
+      </x:c>
+      <x:c r="I223" s="20" t="str"/>
+    </x:row>
+    <x:row r="224" ht="32" customHeight="1">
+      <x:c r="A224" s="18" t="str">
+        <x:v>QA-RPRO-02</x:v>
+      </x:c>
+      <x:c r="B224" s="18" t="str">
+        <x:v>Récupération du profil</x:v>
+      </x:c>
+      <x:c r="C224" s="18" t="str">
+        <x:v>A routine preference save and reload preserve the recovered profile</x:v>
+      </x:c>
+      <x:c r="D224" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E224" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F224" s="18" t="str">
+        <x:v>node tests/combat-profile-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G224" s="18" t="str">
+        <x:v>22 octobre 2026 · 5/5 contrôles, 0 erreur JS non attendue · Sound is enabled through the settings UI; the repaired save has program:null and every prior achievement/binding remains.</x:v>
+      </x:c>
+      <x:c r="H224" s="18" t="str">
+        <x:v>A routine preference save and reload preserve the recovered profile</x:v>
+      </x:c>
+      <x:c r="I224" s="20" t="str"/>
+    </x:row>
+    <x:row r="225" ht="32" customHeight="1">
+      <x:c r="A225" s="19" t="str">
+        <x:v>QA-RPRO-03</x:v>
+      </x:c>
+      <x:c r="B225" s="19" t="str">
+        <x:v>Récupération du profil</x:v>
+      </x:c>
+      <x:c r="C225" s="19" t="str">
+        <x:v>A real cross-tab storage event preserves progress despite an obsolete costume</x:v>
+      </x:c>
+      <x:c r="D225" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E225" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F225" s="19" t="str">
+        <x:v>node tests/combat-profile-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G225" s="19" t="str">
+        <x:v>22 octobre 2026 · 5/5 contrôles, 0 erreur JS non attendue · The incoming fixture replaces stats, history, achievements and the J1 binding; only its invalid checkpoint is discarded.</x:v>
+      </x:c>
+      <x:c r="H225" s="19" t="str">
+        <x:v>A real cross-tab storage event preserves progress despite an obsolete costume</x:v>
+      </x:c>
+      <x:c r="I225" s="20" t="str"/>
+    </x:row>
+    <x:row r="226" ht="32" customHeight="1">
+      <x:c r="A226" s="18" t="str">
+        <x:v>QA-RPRO-04</x:v>
+      </x:c>
+      <x:c r="B226" s="18" t="str">
+        <x:v>Récupération du profil</x:v>
+      </x:c>
+      <x:c r="C226" s="18" t="str">
+        <x:v>Reward refresh repairs the incompatible disk checkpoint without erasing the record</x:v>
+      </x:c>
+      <x:c r="D226" s="18" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E226" s="18" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F226" s="18" t="str">
+        <x:v>node tests/combat-profile-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G226" s="18" t="str">
+        <x:v>22 octobre 2026 · 5/5 contrôles, 0 erreur JS non attendue · Specialist is actually completed with four keyboard techniques; only that new reward is added to the migration fixture, and reload preserves it.</x:v>
+      </x:c>
+      <x:c r="H226" s="18" t="str">
+        <x:v>Reward refresh repairs the incompatible disk checkpoint without erasing the record</x:v>
+      </x:c>
+      <x:c r="I226" s="20" t="str"/>
+    </x:row>
+    <x:row r="227" ht="32" customHeight="1">
+      <x:c r="A227" s="19" t="str">
+        <x:v>QA-RPRO-05</x:v>
+      </x:c>
+      <x:c r="B227" s="19" t="str">
+        <x:v>Récupération du profil</x:v>
+      </x:c>
+      <x:c r="C227" s="19" t="str">
+        <x:v>Manual file import remains strict and preserves the existing profile</x:v>
+      </x:c>
+      <x:c r="D227" s="19" t="str">
+        <x:v>Réussi</x:v>
+      </x:c>
+      <x:c r="E227" s="19" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="F227" s="19" t="str">
+        <x:v>node tests/combat-profile-recovery-browser.mjs · Chromium headless</x:v>
+      </x:c>
+      <x:c r="G227" s="19" t="str">
+        <x:v>22 octobre 2026 · 5/5 contrôles, 0 erreur JS non attendue · An invalid costume is rejected with an error before the replacement prompt; neither the in-memory profile nor its stored copy changes.</x:v>
+      </x:c>
+      <x:c r="H227" s="19" t="str">
+        <x:v>Manual file import remains strict and preserves the existing profile</x:v>
+      </x:c>
+      <x:c r="I227" s="20" t="str"/>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D6:D198">
+  <x:conditionalFormatting sqref="D6:D227">
     <x:cfRule type="containsText" dxfId="91" priority="1" operator="containsText" text="Implémenté"/>
     <x:cfRule type="containsText" dxfId="92" priority="2" operator="containsText" text="Partiel"/>
     <x:cfRule type="containsText" dxfId="93" priority="3" operator="containsText" text="Prévu"/>
@@ -45430,13 +46267,13 @@
     <x:cfRule type="containsText" dxfId="97" priority="7" operator="containsText" text="Non exécuté"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="D6:D198">
+    <x:dataValidation type="list" sqref="D6:D227">
       <x:formula1>"Réussi,Échec,Non exécuté,À vérifier"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cbbe394a0894d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R775b519b96514cb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>